--- a/Översikt UDDEVALLA.xlsx
+++ b/Översikt UDDEVALLA.xlsx
@@ -601,7 +601,7 @@
         <v>46266</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45656</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>45432</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         <v>45677</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>45656</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>45107</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>45317</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>45728</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>45656</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>45751</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>46253</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>45922</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>45656</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>45799</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>45990</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>46174</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>45317</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>45740</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>45317</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>45288</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>45653</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         <v>45513</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>45981</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>45754</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>44825</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>46113</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>46124</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>45513</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
         <v>46253</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>46273</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>45352</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>46241</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4178,7 +4178,7 @@
         <v>44472</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         <v>44733</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>44462</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         <v>44930</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>45071</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>44928</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>44627</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>45237</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
         <v>45076</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5136,7 +5136,7 @@
         <v>45600</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>45303</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>46036</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5459,7 +5459,7 @@
         <v>45135</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>45107</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5669,7 +5669,7 @@
         <v>45348</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5779,7 +5779,7 @@
         <v>46251</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
         <v>46071</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
         <v>45791</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
         <v>45832</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>45328</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         <v>44830</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6390,7 +6390,7 @@
         <v>44586</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6463,7 +6463,7 @@
         <v>44536</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6536,7 +6536,7 @@
         <v>44733</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6609,7 +6609,7 @@
         <v>44574</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>44523</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
         <v>44462</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>44489</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         <v>44585</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
         <v>44733</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
         <v>44599</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         <v>44529</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         <v>44480</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         <v>44462</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         <v>44572</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7417,7 +7417,7 @@
         <v>44614</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>44462</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>44516</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7636,7 +7636,7 @@
         <v>44502</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>44494</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>45633</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>45554</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         <v>44900</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8006,7 +8006,7 @@
         <v>45093</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8079,7 +8079,7 @@
         <v>45684</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8152,7 +8152,7 @@
         <v>45089</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8225,7 +8225,7 @@
         <v>44536</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>45548</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>45183</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8444,7 +8444,7 @@
         <v>44960</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
         <v>45162</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8590,7 +8590,7 @@
         <v>45365</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         <v>45568</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
         <v>45602</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8809,7 +8809,7 @@
         <v>44572</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
         <v>45212</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8955,7 +8955,7 @@
         <v>45754</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9028,7 +9028,7 @@
         <v>45596</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         <v>44634</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9174,7 +9174,7 @@
         <v>45551</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9247,7 +9247,7 @@
         <v>44817</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>45226</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9393,7 +9393,7 @@
         <v>45455</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>44592</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9539,7 +9539,7 @@
         <v>45426</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9612,7 +9612,7 @@
         <v>45748</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         <v>45631</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9758,7 +9758,7 @@
         <v>44981</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
         <v>44820</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9909,7 +9909,7 @@
         <v>44991</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9982,7 +9982,7 @@
         <v>45594</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10055,7 +10055,7 @@
         <v>44489</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10128,7 +10128,7 @@
         <v>45772</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10201,7 +10201,7 @@
         <v>44508</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10274,7 +10274,7 @@
         <v>45150</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10347,7 +10347,7 @@
         <v>45572</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10420,7 +10420,7 @@
         <v>44834</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10493,7 +10493,7 @@
         <v>45279</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10566,7 +10566,7 @@
         <v>45560</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10639,7 +10639,7 @@
         <v>46119</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10712,7 +10712,7 @@
         <v>44551</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10785,7 +10785,7 @@
         <v>45656</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10863,7 +10863,7 @@
         <v>45901</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10936,7 +10936,7 @@
         <v>45699</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11009,7 +11009,7 @@
         <v>45112</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>45840</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
         <v>44715</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
         <v>45889</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11301,7 +11301,7 @@
         <v>45302</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>45895</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
         <v>44998</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11520,7 +11520,7 @@
         <v>45580</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11593,7 +11593,7 @@
         <v>45583</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11666,7 +11666,7 @@
         <v>45901</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11739,7 +11739,7 @@
         <v>45638</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11812,7 +11812,7 @@
         <v>45911</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11885,7 +11885,7 @@
         <v>45771</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11958,7 +11958,7 @@
         <v>46139</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12031,7 +12031,7 @@
         <v>45226</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12104,7 +12104,7 @@
         <v>45914</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>45914</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>46141</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12323,7 +12323,7 @@
         <v>45575</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12396,7 +12396,7 @@
         <v>45919</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12469,7 +12469,7 @@
         <v>45553</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12542,7 +12542,7 @@
         <v>45922</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12615,7 +12615,7 @@
         <v>45925</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
         <v>45929</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12761,7 +12761,7 @@
         <v>45257</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12834,7 +12834,7 @@
         <v>44550</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12907,7 +12907,7 @@
         <v>45929</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>45771</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13053,7 +13053,7 @@
         <v>45931</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13126,7 +13126,7 @@
         <v>45656</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13204,7 +13204,7 @@
         <v>45656</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13282,7 +13282,7 @@
         <v>44683</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13355,7 +13355,7 @@
         <v>45440</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13428,7 +13428,7 @@
         <v>45237</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13501,7 +13501,7 @@
         <v>45656</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>45656</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13657,7 +13657,7 @@
         <v>45656</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13735,7 +13735,7 @@
         <v>45646</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13808,7 +13808,7 @@
         <v>45642</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13881,7 +13881,7 @@
         <v>45470</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13959,7 +13959,7 @@
         <v>45656</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14037,7 +14037,7 @@
         <v>45667</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14110,7 +14110,7 @@
         <v>46147</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14188,7 +14188,7 @@
         <v>45939</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14261,7 +14261,7 @@
         <v>45945</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>45945</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         <v>45945</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14480,7 +14480,7 @@
         <v>45945</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14553,7 +14553,7 @@
         <v>45945</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>46148</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14699,7 +14699,7 @@
         <v>45950</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14772,7 +14772,7 @@
         <v>45940</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14845,7 +14845,7 @@
         <v>45167</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14918,7 +14918,7 @@
         <v>45672</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         <v>45664</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15064,7 +15064,7 @@
         <v>45965</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15137,7 +15137,7 @@
         <v>44973</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15210,7 +15210,7 @@
         <v>45764</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15283,7 +15283,7 @@
         <v>45972</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15356,7 +15356,7 @@
         <v>45314</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15429,7 +15429,7 @@
         <v>45975</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15502,7 +15502,7 @@
         <v>45374</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15575,7 +15575,7 @@
         <v>44928</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15648,7 +15648,7 @@
         <v>45456</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15721,7 +15721,7 @@
         <v>44813</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15794,7 +15794,7 @@
         <v>45021</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15867,7 +15867,7 @@
         <v>45985</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15940,7 +15940,7 @@
         <v>45986</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16013,7 +16013,7 @@
         <v>45239</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16086,7 +16086,7 @@
         <v>45309</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16159,7 +16159,7 @@
         <v>45992</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>44551</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16305,7 +16305,7 @@
         <v>44924</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16378,7 +16378,7 @@
         <v>46198</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16456,7 +16456,7 @@
         <v>45141</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16529,7 +16529,7 @@
         <v>46164</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16602,7 +16602,7 @@
         <v>45999</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16675,7 +16675,7 @@
         <v>45994</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>45133</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16821,7 +16821,7 @@
         <v>46007</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16894,7 +16894,7 @@
         <v>45355</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16972,7 +16972,7 @@
         <v>44578</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17045,7 +17045,7 @@
         <v>46026</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17118,7 +17118,7 @@
         <v>46027</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17191,7 +17191,7 @@
         <v>45463</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17264,7 +17264,7 @@
         <v>45495</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17337,7 +17337,7 @@
         <v>45063</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17410,7 +17410,7 @@
         <v>46174</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17483,7 +17483,7 @@
         <v>46174</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17556,7 +17556,7 @@
         <v>46036</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17629,7 +17629,7 @@
         <v>46036</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17702,7 +17702,7 @@
         <v>46036</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17775,7 +17775,7 @@
         <v>46036</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17848,7 +17848,7 @@
         <v>46036</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17921,7 +17921,7 @@
         <v>46036</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17994,7 +17994,7 @@
         <v>46036</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18067,7 +18067,7 @@
         <v>45097</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18140,7 +18140,7 @@
         <v>45349</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18213,7 +18213,7 @@
         <v>45915</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>46044</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18359,7 +18359,7 @@
         <v>45127</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18432,7 +18432,7 @@
         <v>45168</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18505,7 +18505,7 @@
         <v>45097</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18578,7 +18578,7 @@
         <v>46177</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18651,7 +18651,7 @@
         <v>46177</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18724,7 +18724,7 @@
         <v>44956</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18797,7 +18797,7 @@
         <v>46062</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18870,7 +18870,7 @@
         <v>46062</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>46178</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>46177</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19089,7 +19089,7 @@
         <v>45071</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19162,7 +19162,7 @@
         <v>44935</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19235,7 +19235,7 @@
         <v>46181</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19313,7 +19313,7 @@
         <v>45517</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
         <v>44733</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19459,7 +19459,7 @@
         <v>46071</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>46076</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
         <v>46083</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19683,7 +19683,7 @@
         <v>45953</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19761,7 +19761,7 @@
         <v>46090</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19834,7 +19834,7 @@
         <v>45971</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19912,7 +19912,7 @@
         <v>45992</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19990,7 +19990,7 @@
         <v>45400</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20068,7 +20068,7 @@
         <v>45540</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20146,7 +20146,7 @@
         <v>45981</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20224,7 +20224,7 @@
         <v>45981</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>44509</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20375,7 +20375,7 @@
         <v>46090</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20448,7 +20448,7 @@
         <v>46106</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20521,7 +20521,7 @@
         <v>44602</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20594,7 +20594,7 @@
         <v>46113</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20667,7 +20667,7 @@
         <v>46113</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20740,7 +20740,7 @@
         <v>45035</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20813,7 +20813,7 @@
         <v>45035</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20886,7 +20886,7 @@
         <v>46119</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20959,7 +20959,7 @@
         <v>46120</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21032,7 +21032,7 @@
         <v>45365</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21105,7 +21105,7 @@
         <v>45251</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21183,7 +21183,7 @@
         <v>46121</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21256,7 +21256,7 @@
         <v>46125</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21334,7 +21334,7 @@
         <v>46125</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21407,7 +21407,7 @@
         <v>45215</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21480,7 +21480,7 @@
         <v>46128</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21553,7 +21553,7 @@
         <v>46128</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21626,7 +21626,7 @@
         <v>45754</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21699,7 +21699,7 @@
         <v>45635</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21772,7 +21772,7 @@
         <v>45758</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21845,7 +21845,7 @@
         <v>45919</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         <v>44817</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21991,7 +21991,7 @@
         <v>45167</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22064,7 +22064,7 @@
         <v>45907</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22137,7 +22137,7 @@
         <v>45251</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22215,7 +22215,7 @@
         <v>44655</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22288,7 +22288,7 @@
         <v>45238</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22361,7 +22361,7 @@
         <v>45771</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22434,7 +22434,7 @@
         <v>45076</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22507,7 +22507,7 @@
         <v>44984</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22580,7 +22580,7 @@
         <v>45034</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22653,7 +22653,7 @@
         <v>46206</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22726,7 +22726,7 @@
         <v>46251</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22799,7 +22799,7 @@
         <v>45093</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22872,7 +22872,7 @@
         <v>45475</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22945,7 +22945,7 @@
         <v>44531</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23018,7 +23018,7 @@
         <v>45554</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23091,7 +23091,7 @@
         <v>45028</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23164,7 +23164,7 @@
         <v>45255</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23237,7 +23237,7 @@
         <v>45121</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23310,7 +23310,7 @@
         <v>46210</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23388,7 +23388,7 @@
         <v>46210</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23466,7 +23466,7 @@
         <v>45366</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23539,7 +23539,7 @@
         <v>45205</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23612,7 +23612,7 @@
         <v>46211</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23685,7 +23685,7 @@
         <v>46212</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23763,7 +23763,7 @@
         <v>45426</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23836,7 +23836,7 @@
         <v>45484</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23909,7 +23909,7 @@
         <v>44973</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23982,7 +23982,7 @@
         <v>44967</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24055,7 +24055,7 @@
         <v>46258</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24128,7 +24128,7 @@
         <v>44794</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24201,7 +24201,7 @@
         <v>45188</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24274,7 +24274,7 @@
         <v>45197</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24347,7 +24347,7 @@
         <v>44582</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24425,7 +24425,7 @@
         <v>45484</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24498,7 +24498,7 @@
         <v>46222</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24576,7 +24576,7 @@
         <v>45387</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24649,7 +24649,7 @@
         <v>46267</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24722,7 +24722,7 @@
         <v>46267</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24800,7 +24800,7 @@
         <v>45453</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24873,7 +24873,7 @@
         <v>45771</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24946,7 +24946,7 @@
         <v>46267</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25024,7 +25024,7 @@
         <v>45553</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25097,7 +25097,7 @@
         <v>46266</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25170,7 +25170,7 @@
         <v>46267</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25248,7 +25248,7 @@
         <v>44959</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25321,7 +25321,7 @@
         <v>44823</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25394,7 +25394,7 @@
         <v>45644</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25467,7 +25467,7 @@
         <v>45777</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25540,7 +25540,7 @@
         <v>45847</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25613,7 +25613,7 @@
         <v>45700</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25686,7 +25686,7 @@
         <v>45740</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25759,7 +25759,7 @@
         <v>45740</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25832,7 +25832,7 @@
         <v>45537</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25905,7 +25905,7 @@
         <v>44624</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25978,7 +25978,7 @@
         <v>45722</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26051,7 +26051,7 @@
         <v>45551</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26124,7 +26124,7 @@
         <v>45455</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26197,7 +26197,7 @@
         <v>45723</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26270,7 +26270,7 @@
         <v>45826</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26343,7 +26343,7 @@
         <v>45826</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26416,7 +26416,7 @@
         <v>45826</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26489,7 +26489,7 @@
         <v>45826</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26562,7 +26562,7 @@
         <v>45843</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26635,7 +26635,7 @@
         <v>45588</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26708,7 +26708,7 @@
         <v>45455</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26781,7 +26781,7 @@
         <v>45882</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26854,7 +26854,7 @@
         <v>45672</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26927,7 +26927,7 @@
         <v>45771</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27000,7 +27000,7 @@
         <v>45882</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27073,7 +27073,7 @@
         <v>45328</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27146,7 +27146,7 @@
         <v>45526</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27219,7 +27219,7 @@
         <v>44473</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27292,7 +27292,7 @@
         <v>46129</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>

--- a/Översikt UDDEVALLA.xlsx
+++ b/Översikt UDDEVALLA.xlsx
@@ -601,7 +601,7 @@
         <v>46266</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45656</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>45432</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         <v>45677</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>45656</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>45317</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>45107</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>45728</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>45656</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>45751</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>46253</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>45922</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>45799</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>45656</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>45990</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>46174</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>45317</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>45740</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>45754</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>44825</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>45653</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>46124</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>45981</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>45317</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>45513</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>46253</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         <v>46273</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>46241</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         <v>45513</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>45288</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>45352</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>44472</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         <v>44733</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>45135</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>44930</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         <v>45348</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>45600</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>45832</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>44627</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         <v>45107</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>46036</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
         <v>45071</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>46251</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
         <v>45303</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>45237</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5573,7 +5573,7 @@
         <v>46071</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>44928</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         <v>45076</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5888,7 +5888,7 @@
         <v>45791</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>45328</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
         <v>44830</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6179,7 +6179,7 @@
         <v>44586</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
         <v>44536</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>44733</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
         <v>44574</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         <v>44523</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6544,7 +6544,7 @@
         <v>44489</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6617,7 +6617,7 @@
         <v>44585</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         <v>44733</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6763,7 +6763,7 @@
         <v>44599</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         <v>44529</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>44480</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6982,7 +6982,7 @@
         <v>44572</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
         <v>44614</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>44516</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7206,7 +7206,7 @@
         <v>44502</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7279,7 +7279,7 @@
         <v>44494</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7352,7 +7352,7 @@
         <v>44834</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7425,7 +7425,7 @@
         <v>44813</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7498,7 +7498,7 @@
         <v>44794</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7571,7 +7571,7 @@
         <v>44928</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7644,7 +7644,7 @@
         <v>45426</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         <v>45093</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         <v>45374</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7863,7 +7863,7 @@
         <v>45772</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>45453</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8009,7 +8009,7 @@
         <v>45463</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8082,7 +8082,7 @@
         <v>45366</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8155,7 +8155,7 @@
         <v>45672</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         <v>45537</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         <v>44551</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8374,7 +8374,7 @@
         <v>44817</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         <v>46026</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8520,7 +8520,7 @@
         <v>46027</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8593,7 +8593,7 @@
         <v>45771</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         <v>45484</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8739,7 +8739,7 @@
         <v>45840</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8812,7 +8812,7 @@
         <v>46036</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8885,7 +8885,7 @@
         <v>45699</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
         <v>46036</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9031,7 +9031,7 @@
         <v>46036</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9104,7 +9104,7 @@
         <v>45034</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9177,7 +9177,7 @@
         <v>45035</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9250,7 +9250,7 @@
         <v>45035</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>46036</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         <v>45895</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>46044</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>45638</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9615,7 +9615,7 @@
         <v>45594</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
         <v>45517</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9761,7 +9761,7 @@
         <v>45901</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>45097</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         <v>45911</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9980,7 +9980,7 @@
         <v>45914</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10053,7 +10053,7 @@
         <v>45602</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10126,7 +10126,7 @@
         <v>45914</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10199,7 +10199,7 @@
         <v>46062</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10272,7 +10272,7 @@
         <v>46062</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10345,7 +10345,7 @@
         <v>45919</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10418,7 +10418,7 @@
         <v>45922</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
         <v>45548</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>46071</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10637,7 +10637,7 @@
         <v>45925</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         <v>44935</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10783,7 +10783,7 @@
         <v>45560</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10856,7 +10856,7 @@
         <v>46076</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         <v>45197</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11002,7 +11002,7 @@
         <v>45929</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11075,7 +11075,7 @@
         <v>45929</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11148,7 +11148,7 @@
         <v>44592</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11221,7 +11221,7 @@
         <v>46083</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11299,7 +11299,7 @@
         <v>45551</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11372,7 +11372,7 @@
         <v>45633</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11445,7 +11445,7 @@
         <v>44624</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11518,7 +11518,7 @@
         <v>45931</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11591,7 +11591,7 @@
         <v>45646</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11664,7 +11664,7 @@
         <v>45953</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>45642</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11815,7 +11815,7 @@
         <v>45992</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11893,7 +11893,7 @@
         <v>45971</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11971,7 +11971,7 @@
         <v>45981</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>45400</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12127,7 +12127,7 @@
         <v>45656</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12205,7 +12205,7 @@
         <v>45722</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         <v>45455</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12351,7 +12351,7 @@
         <v>45540</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12429,7 +12429,7 @@
         <v>45470</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12507,7 +12507,7 @@
         <v>45656</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12585,7 +12585,7 @@
         <v>45656</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12663,7 +12663,7 @@
         <v>46090</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12736,7 +12736,7 @@
         <v>45440</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12809,7 +12809,7 @@
         <v>45656</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12887,7 +12887,7 @@
         <v>45656</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12965,7 +12965,7 @@
         <v>45656</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13043,7 +13043,7 @@
         <v>46090</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13116,7 +13116,7 @@
         <v>45939</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>45945</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13262,7 +13262,7 @@
         <v>45226</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13335,7 +13335,7 @@
         <v>45945</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13408,7 +13408,7 @@
         <v>45945</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13481,7 +13481,7 @@
         <v>45945</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13554,7 +13554,7 @@
         <v>45945</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13627,7 +13627,7 @@
         <v>45950</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13700,7 +13700,7 @@
         <v>45940</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13773,7 +13773,7 @@
         <v>46106</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13846,7 +13846,7 @@
         <v>45748</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13919,7 +13919,7 @@
         <v>46113</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13992,7 +13992,7 @@
         <v>44634</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14065,7 +14065,7 @@
         <v>45255</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14138,7 +14138,7 @@
         <v>46119</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14211,7 +14211,7 @@
         <v>46120</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14284,7 +14284,7 @@
         <v>44956</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14357,7 +14357,7 @@
         <v>45965</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14430,7 +14430,7 @@
         <v>44991</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         <v>46121</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14576,7 +14576,7 @@
         <v>46125</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14654,7 +14654,7 @@
         <v>46125</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14727,7 +14727,7 @@
         <v>45972</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14800,7 +14800,7 @@
         <v>45723</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14873,7 +14873,7 @@
         <v>45162</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14946,7 +14946,7 @@
         <v>46128</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15019,7 +15019,7 @@
         <v>45975</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15092,7 +15092,7 @@
         <v>46128</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15165,7 +15165,7 @@
         <v>45986</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15238,7 +15238,7 @@
         <v>45985</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15311,7 +15311,7 @@
         <v>44998</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15384,7 +15384,7 @@
         <v>45302</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15457,7 +15457,7 @@
         <v>45992</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15530,7 +15530,7 @@
         <v>45121</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15603,7 +15603,7 @@
         <v>45484</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15676,7 +15676,7 @@
         <v>45889</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15749,7 +15749,7 @@
         <v>45656</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15827,7 +15827,7 @@
         <v>45907</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15900,7 +15900,7 @@
         <v>45999</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15973,7 +15973,7 @@
         <v>45994</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16046,7 +16046,7 @@
         <v>45901</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16119,7 +16119,7 @@
         <v>45919</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16192,7 +16192,7 @@
         <v>46119</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16265,7 +16265,7 @@
         <v>46139</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16338,7 +16338,7 @@
         <v>46007</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>45279</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16484,7 +16484,7 @@
         <v>45583</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16557,7 +16557,7 @@
         <v>44823</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16630,7 +16630,7 @@
         <v>45771</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16703,7 +16703,7 @@
         <v>44509</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16776,7 +16776,7 @@
         <v>45168</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16849,7 +16849,7 @@
         <v>45212</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16922,7 +16922,7 @@
         <v>45764</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16995,7 +16995,7 @@
         <v>45071</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17068,7 +17068,7 @@
         <v>45672</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17141,7 +17141,7 @@
         <v>45226</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17214,7 +17214,7 @@
         <v>45826</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17287,7 +17287,7 @@
         <v>45826</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17360,7 +17360,7 @@
         <v>45826</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17433,7 +17433,7 @@
         <v>45826</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17506,7 +17506,7 @@
         <v>45238</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17579,7 +17579,7 @@
         <v>44550</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17652,7 +17652,7 @@
         <v>45754</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17725,7 +17725,7 @@
         <v>45754</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17798,7 +17798,7 @@
         <v>45551</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17871,7 +17871,7 @@
         <v>44551</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17944,7 +17944,7 @@
         <v>46147</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>46148</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18095,7 +18095,7 @@
         <v>45455</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18168,7 +18168,7 @@
         <v>45063</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18241,7 +18241,7 @@
         <v>45309</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18314,7 +18314,7 @@
         <v>45021</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18387,7 +18387,7 @@
         <v>44900</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18465,7 +18465,7 @@
         <v>46198</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18543,7 +18543,7 @@
         <v>45843</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18616,7 +18616,7 @@
         <v>44508</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18689,7 +18689,7 @@
         <v>46164</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18762,7 +18762,7 @@
         <v>44973</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18835,7 +18835,7 @@
         <v>44531</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18908,7 +18908,7 @@
         <v>45915</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18981,7 +18981,7 @@
         <v>45495</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19054,7 +19054,7 @@
         <v>45588</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19127,7 +19127,7 @@
         <v>45455</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19200,7 +19200,7 @@
         <v>44967</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19273,7 +19273,7 @@
         <v>45150</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19346,7 +19346,7 @@
         <v>45133</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19419,7 +19419,7 @@
         <v>46174</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19492,7 +19492,7 @@
         <v>46174</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
         <v>45097</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19638,7 +19638,7 @@
         <v>46177</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19711,7 +19711,7 @@
         <v>46177</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19784,7 +19784,7 @@
         <v>45475</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19857,7 +19857,7 @@
         <v>45387</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19930,7 +19930,7 @@
         <v>46177</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20003,7 +20003,7 @@
         <v>44572</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20076,7 +20076,7 @@
         <v>45112</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20149,7 +20149,7 @@
         <v>46178</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20222,7 +20222,7 @@
         <v>44489</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20295,7 +20295,7 @@
         <v>46181</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>45167</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
         <v>45771</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20519,7 +20519,7 @@
         <v>44981</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>45771</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20670,7 +20670,7 @@
         <v>45349</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20743,7 +20743,7 @@
         <v>44582</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20821,7 +20821,7 @@
         <v>45575</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20894,7 +20894,7 @@
         <v>44578</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20967,7 +20967,7 @@
         <v>45553</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21040,7 +21040,7 @@
         <v>45882</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21113,7 +21113,7 @@
         <v>44602</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21186,7 +21186,7 @@
         <v>45882</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21259,7 +21259,7 @@
         <v>46206</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21332,7 +21332,7 @@
         <v>46251</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21405,7 +21405,7 @@
         <v>44655</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21478,7 +21478,7 @@
         <v>45456</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21551,7 +21551,7 @@
         <v>46210</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21629,7 +21629,7 @@
         <v>45664</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21702,7 +21702,7 @@
         <v>46210</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21780,7 +21780,7 @@
         <v>46211</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21853,7 +21853,7 @@
         <v>46258</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21926,7 +21926,7 @@
         <v>46212</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22004,7 +22004,7 @@
         <v>45127</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22077,7 +22077,7 @@
         <v>45183</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22150,7 +22150,7 @@
         <v>45572</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22223,7 +22223,7 @@
         <v>45758</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22296,7 +22296,7 @@
         <v>45631</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22369,7 +22369,7 @@
         <v>44733</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22442,7 +22442,7 @@
         <v>44715</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22515,7 +22515,7 @@
         <v>45239</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22588,7 +22588,7 @@
         <v>44820</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22661,7 +22661,7 @@
         <v>44817</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22734,7 +22734,7 @@
         <v>46222</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22812,7 +22812,7 @@
         <v>46266</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22885,7 +22885,7 @@
         <v>45314</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22958,7 +22958,7 @@
         <v>44973</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23031,7 +23031,7 @@
         <v>46267</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23109,7 +23109,7 @@
         <v>46267</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23182,7 +23182,7 @@
         <v>45257</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23255,7 +23255,7 @@
         <v>46267</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23333,7 +23333,7 @@
         <v>46267</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23411,7 +23411,7 @@
         <v>45847</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23484,7 +23484,7 @@
         <v>45365</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23557,7 +23557,7 @@
         <v>44984</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23630,7 +23630,7 @@
         <v>44683</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23703,7 +23703,7 @@
         <v>46288</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23776,7 +23776,7 @@
         <v>45093</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23849,7 +23849,7 @@
         <v>46141</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23922,7 +23922,7 @@
         <v>46036</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23995,7 +23995,7 @@
         <v>44536</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24068,7 +24068,7 @@
         <v>45141</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24141,7 +24141,7 @@
         <v>45365</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24214,7 +24214,7 @@
         <v>45553</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24287,7 +24287,7 @@
         <v>44959</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24360,7 +24360,7 @@
         <v>45028</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24433,7 +24433,7 @@
         <v>45237</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24506,7 +24506,7 @@
         <v>45089</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24579,7 +24579,7 @@
         <v>45554</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24652,7 +24652,7 @@
         <v>45355</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24730,7 +24730,7 @@
         <v>45554</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24803,7 +24803,7 @@
         <v>45167</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24876,7 +24876,7 @@
         <v>45667</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24949,7 +24949,7 @@
         <v>45251</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25027,7 +25027,7 @@
         <v>45205</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25100,7 +25100,7 @@
         <v>45580</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25173,7 +25173,7 @@
         <v>44960</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25246,7 +25246,7 @@
         <v>45076</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25319,7 +25319,7 @@
         <v>45568</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25392,7 +25392,7 @@
         <v>45635</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25465,7 +25465,7 @@
         <v>44924</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25538,7 +25538,7 @@
         <v>45684</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25611,7 +25611,7 @@
         <v>45188</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25684,7 +25684,7 @@
         <v>45251</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25762,7 +25762,7 @@
         <v>45596</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25835,7 +25835,7 @@
         <v>45426</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25908,7 +25908,7 @@
         <v>45771</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25981,7 +25981,7 @@
         <v>45215</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26054,7 +26054,7 @@
         <v>45644</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26127,7 +26127,7 @@
         <v>45777</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26200,7 +26200,7 @@
         <v>45700</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26273,7 +26273,7 @@
         <v>45740</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26346,7 +26346,7 @@
         <v>45740</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26419,7 +26419,7 @@
         <v>45328</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26492,7 +26492,7 @@
         <v>45526</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26565,7 +26565,7 @@
         <v>44473</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26638,7 +26638,7 @@
         <v>46129</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>

--- a/Översikt UDDEVALLA.xlsx
+++ b/Översikt UDDEVALLA.xlsx
@@ -601,7 +601,7 @@
         <v>46266</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45656</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>45432</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         <v>45677</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>45656</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>45317</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>45107</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>45728</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>45656</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>45751</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>46253</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>45922</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>45799</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>45656</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>45990</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>46174</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>45317</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>45740</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>45754</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>44825</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>45653</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>46124</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>45981</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>45317</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>45513</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>46253</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         <v>46273</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>46241</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         <v>45513</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>45288</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>45352</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>44472</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         <v>44733</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>45135</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>44930</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         <v>45348</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>45600</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>45832</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>44627</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         <v>45107</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>46036</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
         <v>45071</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>46251</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
         <v>45303</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>45237</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5573,7 +5573,7 @@
         <v>46071</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>44928</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         <v>45076</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5888,7 +5888,7 @@
         <v>45791</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>45328</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
         <v>44830</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6179,7 +6179,7 @@
         <v>44586</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
         <v>44536</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>44733</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
         <v>44574</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         <v>44523</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6544,7 +6544,7 @@
         <v>44489</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6617,7 +6617,7 @@
         <v>44585</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         <v>44733</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6763,7 +6763,7 @@
         <v>44599</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         <v>44529</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>44480</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6982,7 +6982,7 @@
         <v>44572</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
         <v>44614</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>44516</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7206,7 +7206,7 @@
         <v>44502</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7279,7 +7279,7 @@
         <v>44494</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7352,7 +7352,7 @@
         <v>44834</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7425,7 +7425,7 @@
         <v>44813</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7498,7 +7498,7 @@
         <v>44794</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7571,7 +7571,7 @@
         <v>44928</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7644,7 +7644,7 @@
         <v>45426</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         <v>45093</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         <v>45374</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7863,7 +7863,7 @@
         <v>45772</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>45453</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8009,7 +8009,7 @@
         <v>45463</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8082,7 +8082,7 @@
         <v>45366</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8155,7 +8155,7 @@
         <v>45672</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         <v>45537</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         <v>44551</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8374,7 +8374,7 @@
         <v>44817</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         <v>46026</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8520,7 +8520,7 @@
         <v>46027</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8593,7 +8593,7 @@
         <v>45771</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         <v>45484</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8739,7 +8739,7 @@
         <v>45840</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8812,7 +8812,7 @@
         <v>46036</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8885,7 +8885,7 @@
         <v>45699</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
         <v>46036</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9031,7 +9031,7 @@
         <v>46036</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9104,7 +9104,7 @@
         <v>45034</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9177,7 +9177,7 @@
         <v>45035</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9250,7 +9250,7 @@
         <v>45035</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>46036</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         <v>45895</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>46044</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>45638</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9615,7 +9615,7 @@
         <v>45594</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
         <v>45517</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9761,7 +9761,7 @@
         <v>45901</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>45097</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         <v>45911</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9980,7 +9980,7 @@
         <v>45914</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10053,7 +10053,7 @@
         <v>45602</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10126,7 +10126,7 @@
         <v>45914</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10199,7 +10199,7 @@
         <v>46062</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10272,7 +10272,7 @@
         <v>46062</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10345,7 +10345,7 @@
         <v>45919</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10418,7 +10418,7 @@
         <v>45922</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
         <v>45548</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>46071</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10637,7 +10637,7 @@
         <v>45925</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         <v>44935</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10783,7 +10783,7 @@
         <v>45560</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10856,7 +10856,7 @@
         <v>46076</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         <v>45197</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11002,7 +11002,7 @@
         <v>45929</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11075,7 +11075,7 @@
         <v>45929</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11148,7 +11148,7 @@
         <v>44592</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11221,7 +11221,7 @@
         <v>46083</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11299,7 +11299,7 @@
         <v>45551</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11372,7 +11372,7 @@
         <v>45633</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11445,7 +11445,7 @@
         <v>44624</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11518,7 +11518,7 @@
         <v>45931</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11591,7 +11591,7 @@
         <v>45646</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11664,7 +11664,7 @@
         <v>45953</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>45642</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11815,7 +11815,7 @@
         <v>45992</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11893,7 +11893,7 @@
         <v>45971</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11971,7 +11971,7 @@
         <v>45981</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>45400</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12127,7 +12127,7 @@
         <v>45656</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12205,7 +12205,7 @@
         <v>45722</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         <v>45455</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12351,7 +12351,7 @@
         <v>45540</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12429,7 +12429,7 @@
         <v>45470</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12507,7 +12507,7 @@
         <v>45656</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12585,7 +12585,7 @@
         <v>45656</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12663,7 +12663,7 @@
         <v>46090</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12736,7 +12736,7 @@
         <v>45440</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12809,7 +12809,7 @@
         <v>45656</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12887,7 +12887,7 @@
         <v>45656</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12965,7 +12965,7 @@
         <v>45656</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13043,7 +13043,7 @@
         <v>46090</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13116,7 +13116,7 @@
         <v>45939</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>45945</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13262,7 +13262,7 @@
         <v>45226</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13335,7 +13335,7 @@
         <v>45945</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13408,7 +13408,7 @@
         <v>45945</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13481,7 +13481,7 @@
         <v>45945</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13554,7 +13554,7 @@
         <v>45945</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13627,7 +13627,7 @@
         <v>45950</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13700,7 +13700,7 @@
         <v>45940</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13773,7 +13773,7 @@
         <v>46106</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13846,7 +13846,7 @@
         <v>45748</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13919,7 +13919,7 @@
         <v>46113</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13992,7 +13992,7 @@
         <v>44634</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14065,7 +14065,7 @@
         <v>45255</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14138,7 +14138,7 @@
         <v>46119</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14211,7 +14211,7 @@
         <v>46120</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14284,7 +14284,7 @@
         <v>44956</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14357,7 +14357,7 @@
         <v>45965</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14430,7 +14430,7 @@
         <v>44991</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         <v>46121</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14576,7 +14576,7 @@
         <v>46125</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14654,7 +14654,7 @@
         <v>46125</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14727,7 +14727,7 @@
         <v>45972</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14800,7 +14800,7 @@
         <v>45723</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14873,7 +14873,7 @@
         <v>45162</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14946,7 +14946,7 @@
         <v>46128</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15019,7 +15019,7 @@
         <v>45975</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15092,7 +15092,7 @@
         <v>46128</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15165,7 +15165,7 @@
         <v>45986</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15238,7 +15238,7 @@
         <v>45985</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15311,7 +15311,7 @@
         <v>44998</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15384,7 +15384,7 @@
         <v>45302</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15457,7 +15457,7 @@
         <v>45992</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15530,7 +15530,7 @@
         <v>45121</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15603,7 +15603,7 @@
         <v>45484</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15676,7 +15676,7 @@
         <v>45889</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15749,7 +15749,7 @@
         <v>45656</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15827,7 +15827,7 @@
         <v>45907</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15900,7 +15900,7 @@
         <v>45999</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15973,7 +15973,7 @@
         <v>45994</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16046,7 +16046,7 @@
         <v>45901</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16119,7 +16119,7 @@
         <v>45919</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16192,7 +16192,7 @@
         <v>46119</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16265,7 +16265,7 @@
         <v>46139</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16338,7 +16338,7 @@
         <v>46007</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>45279</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16484,7 +16484,7 @@
         <v>45583</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16557,7 +16557,7 @@
         <v>44823</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16630,7 +16630,7 @@
         <v>45771</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16703,7 +16703,7 @@
         <v>44509</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16776,7 +16776,7 @@
         <v>45168</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16849,7 +16849,7 @@
         <v>45212</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16922,7 +16922,7 @@
         <v>45764</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16995,7 +16995,7 @@
         <v>45071</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17068,7 +17068,7 @@
         <v>45672</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17141,7 +17141,7 @@
         <v>45226</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17214,7 +17214,7 @@
         <v>45826</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17287,7 +17287,7 @@
         <v>45826</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17360,7 +17360,7 @@
         <v>45826</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17433,7 +17433,7 @@
         <v>45826</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17506,7 +17506,7 @@
         <v>45238</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17579,7 +17579,7 @@
         <v>44550</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17652,7 +17652,7 @@
         <v>45754</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17725,7 +17725,7 @@
         <v>45754</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17798,7 +17798,7 @@
         <v>45551</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17871,7 +17871,7 @@
         <v>44551</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17944,7 +17944,7 @@
         <v>46147</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>46148</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18095,7 +18095,7 @@
         <v>45455</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18168,7 +18168,7 @@
         <v>45063</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18241,7 +18241,7 @@
         <v>45309</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18314,7 +18314,7 @@
         <v>45021</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18387,7 +18387,7 @@
         <v>44900</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18465,7 +18465,7 @@
         <v>46198</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18543,7 +18543,7 @@
         <v>45843</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18616,7 +18616,7 @@
         <v>44508</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18689,7 +18689,7 @@
         <v>46164</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18762,7 +18762,7 @@
         <v>44973</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18835,7 +18835,7 @@
         <v>44531</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18908,7 +18908,7 @@
         <v>45915</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18981,7 +18981,7 @@
         <v>45495</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19054,7 +19054,7 @@
         <v>45588</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19127,7 +19127,7 @@
         <v>45455</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19200,7 +19200,7 @@
         <v>44967</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19273,7 +19273,7 @@
         <v>45150</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19346,7 +19346,7 @@
         <v>45133</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19419,7 +19419,7 @@
         <v>46174</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19492,7 +19492,7 @@
         <v>46174</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
         <v>45097</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19638,7 +19638,7 @@
         <v>46177</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19711,7 +19711,7 @@
         <v>46177</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19784,7 +19784,7 @@
         <v>45475</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19857,7 +19857,7 @@
         <v>45387</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19930,7 +19930,7 @@
         <v>46177</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20003,7 +20003,7 @@
         <v>44572</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20076,7 +20076,7 @@
         <v>45112</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20149,7 +20149,7 @@
         <v>46178</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20222,7 +20222,7 @@
         <v>44489</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20295,7 +20295,7 @@
         <v>46181</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>45167</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
         <v>45771</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20519,7 +20519,7 @@
         <v>44981</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>45771</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20670,7 +20670,7 @@
         <v>45349</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20743,7 +20743,7 @@
         <v>44582</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20821,7 +20821,7 @@
         <v>45575</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20894,7 +20894,7 @@
         <v>44578</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20967,7 +20967,7 @@
         <v>45553</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21040,7 +21040,7 @@
         <v>45882</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21113,7 +21113,7 @@
         <v>44602</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21186,7 +21186,7 @@
         <v>45882</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21259,7 +21259,7 @@
         <v>46206</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21332,7 +21332,7 @@
         <v>46251</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21405,7 +21405,7 @@
         <v>44655</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21478,7 +21478,7 @@
         <v>45456</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21551,7 +21551,7 @@
         <v>46210</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21629,7 +21629,7 @@
         <v>45664</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21702,7 +21702,7 @@
         <v>46210</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21780,7 +21780,7 @@
         <v>46211</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21853,7 +21853,7 @@
         <v>46258</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21926,7 +21926,7 @@
         <v>46212</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22004,7 +22004,7 @@
         <v>45127</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22077,7 +22077,7 @@
         <v>45183</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22150,7 +22150,7 @@
         <v>45572</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22223,7 +22223,7 @@
         <v>45758</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22296,7 +22296,7 @@
         <v>45631</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22369,7 +22369,7 @@
         <v>44733</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22442,7 +22442,7 @@
         <v>44715</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22515,7 +22515,7 @@
         <v>45239</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22588,7 +22588,7 @@
         <v>44820</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22661,7 +22661,7 @@
         <v>44817</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22734,7 +22734,7 @@
         <v>46222</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22812,7 +22812,7 @@
         <v>46266</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22885,7 +22885,7 @@
         <v>45314</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22958,7 +22958,7 @@
         <v>44973</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23031,7 +23031,7 @@
         <v>46267</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23109,7 +23109,7 @@
         <v>46267</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23182,7 +23182,7 @@
         <v>45257</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23255,7 +23255,7 @@
         <v>46267</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23333,7 +23333,7 @@
         <v>46267</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23411,7 +23411,7 @@
         <v>45847</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23484,7 +23484,7 @@
         <v>45365</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23557,7 +23557,7 @@
         <v>44984</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23630,7 +23630,7 @@
         <v>44683</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23703,7 +23703,7 @@
         <v>46288</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23776,7 +23776,7 @@
         <v>45093</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23849,7 +23849,7 @@
         <v>46141</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23922,7 +23922,7 @@
         <v>46036</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23995,7 +23995,7 @@
         <v>44536</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24068,7 +24068,7 @@
         <v>45141</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24141,7 +24141,7 @@
         <v>45365</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24214,7 +24214,7 @@
         <v>45553</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24287,7 +24287,7 @@
         <v>44959</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24360,7 +24360,7 @@
         <v>45028</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24433,7 +24433,7 @@
         <v>45237</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24506,7 +24506,7 @@
         <v>45089</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24579,7 +24579,7 @@
         <v>45554</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24652,7 +24652,7 @@
         <v>45355</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24730,7 +24730,7 @@
         <v>45554</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24803,7 +24803,7 @@
         <v>45167</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24876,7 +24876,7 @@
         <v>45667</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24949,7 +24949,7 @@
         <v>45251</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25027,7 +25027,7 @@
         <v>45205</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25100,7 +25100,7 @@
         <v>45580</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25173,7 +25173,7 @@
         <v>44960</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25246,7 +25246,7 @@
         <v>45076</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25319,7 +25319,7 @@
         <v>45568</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25392,7 +25392,7 @@
         <v>45635</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25465,7 +25465,7 @@
         <v>44924</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25538,7 +25538,7 @@
         <v>45684</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25611,7 +25611,7 @@
         <v>45188</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25684,7 +25684,7 @@
         <v>45251</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25762,7 +25762,7 @@
         <v>45596</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25835,7 +25835,7 @@
         <v>45426</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25908,7 +25908,7 @@
         <v>45771</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25981,7 +25981,7 @@
         <v>45215</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26054,7 +26054,7 @@
         <v>45644</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26127,7 +26127,7 @@
         <v>45777</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26200,7 +26200,7 @@
         <v>45700</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26273,7 +26273,7 @@
         <v>45740</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26346,7 +26346,7 @@
         <v>45740</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26419,7 +26419,7 @@
         <v>45328</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26492,7 +26492,7 @@
         <v>45526</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26565,7 +26565,7 @@
         <v>44473</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26638,7 +26638,7 @@
         <v>46129</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>

--- a/Översikt UDDEVALLA.xlsx
+++ b/Översikt UDDEVALLA.xlsx
@@ -601,7 +601,7 @@
         <v>46266</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45656</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>45432</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         <v>45677</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>45656</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>45728</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>45317</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>45107</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>45656</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>45751</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>46253</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>45740</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>45922</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>45656</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         <v>45799</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>45990</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>46174</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>45317</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>45981</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>46124</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>45288</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>45317</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>45513</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>45754</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>44825</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>46253</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         <v>46273</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>46241</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         <v>45653</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>45513</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>45352</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>44472</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         <v>44733</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>44930</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>45791</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         <v>45071</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4614,7 +4614,7 @@
         <v>45348</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>44928</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>44627</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         <v>45237</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>45832</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
         <v>45076</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>45600</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         <v>46036</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>45303</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         <v>45135</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         <v>45107</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>46071</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5887,7 +5887,7 @@
         <v>46292</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>46251</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>45328</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         <v>44586</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         <v>44830</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>44536</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>44733</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>44574</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>44523</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>44489</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         <v>44585</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
         <v>44733</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6873,7 +6873,7 @@
         <v>44599</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
         <v>44529</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>44480</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
         <v>44572</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7170,7 +7170,7 @@
         <v>44614</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>44516</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>44502</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7389,7 +7389,7 @@
         <v>44494</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7462,7 +7462,7 @@
         <v>45633</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7535,7 +7535,7 @@
         <v>45602</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
         <v>44900</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7686,7 +7686,7 @@
         <v>45554</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7759,7 +7759,7 @@
         <v>45212</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7832,7 +7832,7 @@
         <v>45093</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7905,7 +7905,7 @@
         <v>45684</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>45089</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         <v>45183</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
         <v>44536</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>44960</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>45365</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8343,7 +8343,7 @@
         <v>45548</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>45162</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8489,7 +8489,7 @@
         <v>45568</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>44572</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8635,7 +8635,7 @@
         <v>45754</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8708,7 +8708,7 @@
         <v>44634</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         <v>46007</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
         <v>45551</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8927,7 +8927,7 @@
         <v>45596</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9000,7 +9000,7 @@
         <v>44551</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         <v>44817</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>45699</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9219,7 +9219,7 @@
         <v>45226</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9292,7 +9292,7 @@
         <v>46026</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9365,7 +9365,7 @@
         <v>46027</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9438,7 +9438,7 @@
         <v>45740</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9511,7 +9511,7 @@
         <v>45895</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9584,7 +9584,7 @@
         <v>45455</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         <v>45740</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9730,7 +9730,7 @@
         <v>44592</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9803,7 +9803,7 @@
         <v>45901</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9876,7 +9876,7 @@
         <v>46036</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         <v>45426</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         <v>46036</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10095,7 +10095,7 @@
         <v>46036</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10168,7 +10168,7 @@
         <v>46036</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10241,7 +10241,7 @@
         <v>45748</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10314,7 +10314,7 @@
         <v>45631</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>44981</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
         <v>45911</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10538,7 +10538,7 @@
         <v>45537</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10611,7 +10611,7 @@
         <v>46044</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10684,7 +10684,7 @@
         <v>45914</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10757,7 +10757,7 @@
         <v>45914</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10830,7 +10830,7 @@
         <v>44820</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10903,7 +10903,7 @@
         <v>45919</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10976,7 +10976,7 @@
         <v>45572</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11049,7 +11049,7 @@
         <v>45922</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
         <v>44624</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11195,7 +11195,7 @@
         <v>45925</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
         <v>44991</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11341,7 +11341,7 @@
         <v>45929</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11414,7 +11414,7 @@
         <v>45722</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11487,7 +11487,7 @@
         <v>45929</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11560,7 +11560,7 @@
         <v>46062</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11633,7 +11633,7 @@
         <v>46062</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11706,7 +11706,7 @@
         <v>45594</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11779,7 +11779,7 @@
         <v>45931</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11852,7 +11852,7 @@
         <v>45656</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         <v>45656</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
         <v>45440</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12081,7 +12081,7 @@
         <v>45656</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12159,7 +12159,7 @@
         <v>45656</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12237,7 +12237,7 @@
         <v>45656</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12315,7 +12315,7 @@
         <v>45551</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12388,7 +12388,7 @@
         <v>45646</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12461,7 +12461,7 @@
         <v>45642</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12534,7 +12534,7 @@
         <v>45470</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12612,7 +12612,7 @@
         <v>45656</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12690,7 +12690,7 @@
         <v>44489</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12763,7 +12763,7 @@
         <v>44935</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12836,7 +12836,7 @@
         <v>45455</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12909,7 +12909,7 @@
         <v>46071</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
         <v>45939</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
         <v>45945</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13128,7 +13128,7 @@
         <v>45945</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
         <v>45945</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13274,7 +13274,7 @@
         <v>45945</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13347,7 +13347,7 @@
         <v>45945</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13420,7 +13420,7 @@
         <v>46076</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13493,7 +13493,7 @@
         <v>45950</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13566,7 +13566,7 @@
         <v>45940</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13639,7 +13639,7 @@
         <v>45772</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13712,7 +13712,7 @@
         <v>46083</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13790,7 +13790,7 @@
         <v>45953</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13868,7 +13868,7 @@
         <v>46090</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13941,7 +13941,7 @@
         <v>45971</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14019,7 +14019,7 @@
         <v>45992</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
         <v>45400</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14175,7 +14175,7 @@
         <v>45540</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14253,7 +14253,7 @@
         <v>45981</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14331,7 +14331,7 @@
         <v>45723</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14404,7 +14404,7 @@
         <v>44508</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14477,7 +14477,7 @@
         <v>46090</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14550,7 +14550,7 @@
         <v>45965</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>45150</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14696,7 +14696,7 @@
         <v>45972</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14769,7 +14769,7 @@
         <v>45975</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14842,7 +14842,7 @@
         <v>46106</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14915,7 +14915,7 @@
         <v>45985</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14988,7 +14988,7 @@
         <v>46113</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15061,7 +15061,7 @@
         <v>45986</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
         <v>46119</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15207,7 +15207,7 @@
         <v>46120</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
         <v>45992</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15353,7 +15353,7 @@
         <v>44834</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15426,7 +15426,7 @@
         <v>45826</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15499,7 +15499,7 @@
         <v>46121</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15572,7 +15572,7 @@
         <v>46125</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15650,7 +15650,7 @@
         <v>45560</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15723,7 +15723,7 @@
         <v>46125</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15796,7 +15796,7 @@
         <v>45826</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15869,7 +15869,7 @@
         <v>45999</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>45826</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16015,7 +16015,7 @@
         <v>45826</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16088,7 +16088,7 @@
         <v>45994</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16161,7 +16161,7 @@
         <v>46128</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16234,7 +16234,7 @@
         <v>46128</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16307,7 +16307,7 @@
         <v>45112</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16380,7 +16380,7 @@
         <v>44715</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16453,7 +16453,7 @@
         <v>45919</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16526,7 +16526,7 @@
         <v>45907</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16599,7 +16599,7 @@
         <v>44998</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16672,7 +16672,7 @@
         <v>45580</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16745,7 +16745,7 @@
         <v>45843</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16818,7 +16818,7 @@
         <v>45279</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16891,7 +16891,7 @@
         <v>46119</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16964,7 +16964,7 @@
         <v>45656</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17042,7 +17042,7 @@
         <v>45638</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17115,7 +17115,7 @@
         <v>45771</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17188,7 +17188,7 @@
         <v>45901</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17261,7 +17261,7 @@
         <v>45575</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17334,7 +17334,7 @@
         <v>45889</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17407,7 +17407,7 @@
         <v>45553</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17480,7 +17480,7 @@
         <v>45302</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17553,7 +17553,7 @@
         <v>45583</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17626,7 +17626,7 @@
         <v>45257</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17699,7 +17699,7 @@
         <v>45771</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17772,7 +17772,7 @@
         <v>44683</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17845,7 +17845,7 @@
         <v>45237</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17918,7 +17918,7 @@
         <v>45588</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17991,7 +17991,7 @@
         <v>45455</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>46139</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18137,7 +18137,7 @@
         <v>45226</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18210,7 +18210,7 @@
         <v>45667</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18283,7 +18283,7 @@
         <v>44550</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18356,7 +18356,7 @@
         <v>45167</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18429,7 +18429,7 @@
         <v>46147</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18507,7 +18507,7 @@
         <v>45672</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18580,7 +18580,7 @@
         <v>45664</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18653,7 +18653,7 @@
         <v>46148</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18726,7 +18726,7 @@
         <v>44973</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18799,7 +18799,7 @@
         <v>45764</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18872,7 +18872,7 @@
         <v>45309</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18945,7 +18945,7 @@
         <v>45314</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19018,7 +19018,7 @@
         <v>46198</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19096,7 +19096,7 @@
         <v>45374</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19169,7 +19169,7 @@
         <v>44928</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19242,7 +19242,7 @@
         <v>46164</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19315,7 +19315,7 @@
         <v>45456</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19388,7 +19388,7 @@
         <v>44813</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19461,7 +19461,7 @@
         <v>45021</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19534,7 +19534,7 @@
         <v>45239</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19607,7 +19607,7 @@
         <v>45495</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19680,7 +19680,7 @@
         <v>46174</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19753,7 +19753,7 @@
         <v>46174</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19826,7 +19826,7 @@
         <v>45882</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19899,7 +19899,7 @@
         <v>45672</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         <v>45771</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
         <v>45915</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20118,7 +20118,7 @@
         <v>44551</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20191,7 +20191,7 @@
         <v>45882</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20264,7 +20264,7 @@
         <v>46177</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20337,7 +20337,7 @@
         <v>45840</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20410,7 +20410,7 @@
         <v>44924</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20483,7 +20483,7 @@
         <v>46177</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20556,7 +20556,7 @@
         <v>46178</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20629,7 +20629,7 @@
         <v>46177</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20702,7 +20702,7 @@
         <v>46181</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20780,7 +20780,7 @@
         <v>45141</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20853,7 +20853,7 @@
         <v>45133</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20926,7 +20926,7 @@
         <v>45355</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21004,7 +21004,7 @@
         <v>44578</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21077,7 +21077,7 @@
         <v>45463</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21150,7 +21150,7 @@
         <v>45063</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21223,7 +21223,7 @@
         <v>46206</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21296,7 +21296,7 @@
         <v>45097</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21369,7 +21369,7 @@
         <v>46210</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21447,7 +21447,7 @@
         <v>46210</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21525,7 +21525,7 @@
         <v>46211</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21598,7 +21598,7 @@
         <v>46212</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21676,7 +21676,7 @@
         <v>45349</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21749,7 +21749,7 @@
         <v>45127</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21822,7 +21822,7 @@
         <v>46258</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21895,7 +21895,7 @@
         <v>45168</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21968,7 +21968,7 @@
         <v>45097</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22041,7 +22041,7 @@
         <v>44956</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22114,7 +22114,7 @@
         <v>46222</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22192,7 +22192,7 @@
         <v>46267</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22265,7 +22265,7 @@
         <v>45071</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22338,7 +22338,7 @@
         <v>46267</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22416,7 +22416,7 @@
         <v>46267</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22494,7 +22494,7 @@
         <v>46266</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22567,7 +22567,7 @@
         <v>46267</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22645,7 +22645,7 @@
         <v>45517</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22718,7 +22718,7 @@
         <v>44733</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22791,7 +22791,7 @@
         <v>45847</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22864,7 +22864,7 @@
         <v>44509</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22937,7 +22937,7 @@
         <v>46141</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23010,7 +23010,7 @@
         <v>44602</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23083,7 +23083,7 @@
         <v>46036</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23156,7 +23156,7 @@
         <v>46288</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23229,7 +23229,7 @@
         <v>45035</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23302,7 +23302,7 @@
         <v>45035</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23375,7 +23375,7 @@
         <v>45365</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23448,7 +23448,7 @@
         <v>45251</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23526,7 +23526,7 @@
         <v>46251</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23599,7 +23599,7 @@
         <v>45215</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23672,7 +23672,7 @@
         <v>45754</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23745,7 +23745,7 @@
         <v>45635</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23818,7 +23818,7 @@
         <v>46293</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23891,7 +23891,7 @@
         <v>45758</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23964,7 +23964,7 @@
         <v>44817</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24037,7 +24037,7 @@
         <v>45167</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24110,7 +24110,7 @@
         <v>45251</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24188,7 +24188,7 @@
         <v>44655</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24261,7 +24261,7 @@
         <v>45238</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24334,7 +24334,7 @@
         <v>45771</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>45076</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24480,7 +24480,7 @@
         <v>44984</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24553,7 +24553,7 @@
         <v>45034</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24626,7 +24626,7 @@
         <v>45093</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24699,7 +24699,7 @@
         <v>45475</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24772,7 +24772,7 @@
         <v>44531</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24845,7 +24845,7 @@
         <v>45554</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24918,7 +24918,7 @@
         <v>45028</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24991,7 +24991,7 @@
         <v>45255</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25064,7 +25064,7 @@
         <v>45121</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25137,7 +25137,7 @@
         <v>45366</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25210,7 +25210,7 @@
         <v>45205</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25283,7 +25283,7 @@
         <v>45426</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25356,7 +25356,7 @@
         <v>45484</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25429,7 +25429,7 @@
         <v>44973</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25502,7 +25502,7 @@
         <v>44967</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25575,7 +25575,7 @@
         <v>44794</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25648,7 +25648,7 @@
         <v>45188</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25721,7 +25721,7 @@
         <v>45197</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25794,7 +25794,7 @@
         <v>44582</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25872,7 +25872,7 @@
         <v>45484</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25945,7 +25945,7 @@
         <v>45387</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26018,7 +26018,7 @@
         <v>45453</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26091,7 +26091,7 @@
         <v>45771</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26164,7 +26164,7 @@
         <v>45553</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26237,7 +26237,7 @@
         <v>44959</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26310,7 +26310,7 @@
         <v>44823</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26383,7 +26383,7 @@
         <v>45644</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26456,7 +26456,7 @@
         <v>45777</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26529,7 +26529,7 @@
         <v>45700</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26602,7 +26602,7 @@
         <v>45328</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26675,7 +26675,7 @@
         <v>45526</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26748,7 +26748,7 @@
         <v>44473</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26821,7 +26821,7 @@
         <v>46129</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>

--- a/Översikt UDDEVALLA.xlsx
+++ b/Översikt UDDEVALLA.xlsx
@@ -601,7 +601,7 @@
         <v>46266</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45656</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>45432</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         <v>45677</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>45656</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>45728</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>45317</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>45107</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>45656</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>45751</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>46253</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>45740</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>45922</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>45656</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         <v>45799</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>45990</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>46174</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>45317</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>45981</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>46124</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>45288</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>45317</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>45513</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>45754</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>44825</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>46253</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         <v>46273</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>46241</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         <v>45653</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>45513</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>45352</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>44472</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         <v>44733</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>44930</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>45791</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         <v>45071</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4614,7 +4614,7 @@
         <v>45348</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>44928</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>44627</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         <v>45237</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>45832</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
         <v>45076</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>45600</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         <v>46036</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>45303</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         <v>45135</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         <v>45107</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>46071</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5887,7 +5887,7 @@
         <v>46292</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>46251</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>45328</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         <v>44586</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         <v>44830</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>44536</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>44733</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>44574</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>44523</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>44489</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         <v>44585</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
         <v>44733</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6873,7 +6873,7 @@
         <v>44599</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
         <v>44529</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>44480</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
         <v>44572</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7170,7 +7170,7 @@
         <v>44614</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>44516</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>44502</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7389,7 +7389,7 @@
         <v>44494</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7462,7 +7462,7 @@
         <v>45633</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7535,7 +7535,7 @@
         <v>45602</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
         <v>44900</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7686,7 +7686,7 @@
         <v>45554</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7759,7 +7759,7 @@
         <v>45212</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7832,7 +7832,7 @@
         <v>45093</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7905,7 +7905,7 @@
         <v>45684</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>45089</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         <v>45183</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
         <v>44536</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>44960</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>45365</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8343,7 +8343,7 @@
         <v>45548</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>45162</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8489,7 +8489,7 @@
         <v>45568</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>44572</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8635,7 +8635,7 @@
         <v>45754</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8708,7 +8708,7 @@
         <v>44634</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         <v>46007</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
         <v>45551</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8927,7 +8927,7 @@
         <v>45596</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9000,7 +9000,7 @@
         <v>44551</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         <v>44817</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>45699</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9219,7 +9219,7 @@
         <v>45226</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9292,7 +9292,7 @@
         <v>46026</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9365,7 +9365,7 @@
         <v>46027</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9438,7 +9438,7 @@
         <v>45740</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9511,7 +9511,7 @@
         <v>45895</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9584,7 +9584,7 @@
         <v>45455</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         <v>45740</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9730,7 +9730,7 @@
         <v>44592</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9803,7 +9803,7 @@
         <v>45901</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9876,7 +9876,7 @@
         <v>46036</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         <v>45426</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         <v>46036</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10095,7 +10095,7 @@
         <v>46036</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10168,7 +10168,7 @@
         <v>46036</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10241,7 +10241,7 @@
         <v>45748</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10314,7 +10314,7 @@
         <v>45631</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>44981</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
         <v>45911</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10538,7 +10538,7 @@
         <v>45537</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10611,7 +10611,7 @@
         <v>46044</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10684,7 +10684,7 @@
         <v>45914</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10757,7 +10757,7 @@
         <v>45914</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10830,7 +10830,7 @@
         <v>44820</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10903,7 +10903,7 @@
         <v>45919</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10976,7 +10976,7 @@
         <v>45572</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11049,7 +11049,7 @@
         <v>45922</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
         <v>44624</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11195,7 +11195,7 @@
         <v>45925</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
         <v>44991</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11341,7 +11341,7 @@
         <v>45929</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11414,7 +11414,7 @@
         <v>45722</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11487,7 +11487,7 @@
         <v>45929</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11560,7 +11560,7 @@
         <v>46062</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11633,7 +11633,7 @@
         <v>46062</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11706,7 +11706,7 @@
         <v>45594</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11779,7 +11779,7 @@
         <v>45931</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11852,7 +11852,7 @@
         <v>45656</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         <v>45656</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
         <v>45440</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12081,7 +12081,7 @@
         <v>45656</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12159,7 +12159,7 @@
         <v>45656</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12237,7 +12237,7 @@
         <v>45656</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12315,7 +12315,7 @@
         <v>45551</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12388,7 +12388,7 @@
         <v>45646</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12461,7 +12461,7 @@
         <v>45642</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12534,7 +12534,7 @@
         <v>45470</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12612,7 +12612,7 @@
         <v>45656</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12690,7 +12690,7 @@
         <v>44489</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12763,7 +12763,7 @@
         <v>44935</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12836,7 +12836,7 @@
         <v>45455</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12909,7 +12909,7 @@
         <v>46071</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
         <v>45939</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
         <v>45945</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13128,7 +13128,7 @@
         <v>45945</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
         <v>45945</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13274,7 +13274,7 @@
         <v>45945</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13347,7 +13347,7 @@
         <v>45945</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13420,7 +13420,7 @@
         <v>46076</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13493,7 +13493,7 @@
         <v>45950</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13566,7 +13566,7 @@
         <v>45940</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13639,7 +13639,7 @@
         <v>45772</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13712,7 +13712,7 @@
         <v>46083</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13790,7 +13790,7 @@
         <v>45953</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13868,7 +13868,7 @@
         <v>46090</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13941,7 +13941,7 @@
         <v>45971</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14019,7 +14019,7 @@
         <v>45992</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
         <v>45400</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14175,7 +14175,7 @@
         <v>45540</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14253,7 +14253,7 @@
         <v>45981</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14331,7 +14331,7 @@
         <v>45723</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14404,7 +14404,7 @@
         <v>44508</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14477,7 +14477,7 @@
         <v>46090</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14550,7 +14550,7 @@
         <v>45965</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>45150</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14696,7 +14696,7 @@
         <v>45972</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14769,7 +14769,7 @@
         <v>45975</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14842,7 +14842,7 @@
         <v>46106</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14915,7 +14915,7 @@
         <v>45985</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14988,7 +14988,7 @@
         <v>46113</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15061,7 +15061,7 @@
         <v>45986</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
         <v>46119</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15207,7 +15207,7 @@
         <v>46120</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
         <v>45992</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15353,7 +15353,7 @@
         <v>44834</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15426,7 +15426,7 @@
         <v>45826</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15499,7 +15499,7 @@
         <v>46121</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15572,7 +15572,7 @@
         <v>46125</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15650,7 +15650,7 @@
         <v>45560</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15723,7 +15723,7 @@
         <v>46125</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15796,7 +15796,7 @@
         <v>45826</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15869,7 +15869,7 @@
         <v>45999</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>45826</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16015,7 +16015,7 @@
         <v>45826</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16088,7 +16088,7 @@
         <v>45994</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16161,7 +16161,7 @@
         <v>46128</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16234,7 +16234,7 @@
         <v>46128</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16307,7 +16307,7 @@
         <v>45112</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16380,7 +16380,7 @@
         <v>44715</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16453,7 +16453,7 @@
         <v>45919</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16526,7 +16526,7 @@
         <v>45907</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16599,7 +16599,7 @@
         <v>44998</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16672,7 +16672,7 @@
         <v>45580</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16745,7 +16745,7 @@
         <v>45843</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16818,7 +16818,7 @@
         <v>45279</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16891,7 +16891,7 @@
         <v>46119</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16964,7 +16964,7 @@
         <v>45656</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17042,7 +17042,7 @@
         <v>45638</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17115,7 +17115,7 @@
         <v>45771</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17188,7 +17188,7 @@
         <v>45901</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17261,7 +17261,7 @@
         <v>45575</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17334,7 +17334,7 @@
         <v>45889</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17407,7 +17407,7 @@
         <v>45553</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17480,7 +17480,7 @@
         <v>45302</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17553,7 +17553,7 @@
         <v>45583</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17626,7 +17626,7 @@
         <v>45257</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17699,7 +17699,7 @@
         <v>45771</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17772,7 +17772,7 @@
         <v>44683</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17845,7 +17845,7 @@
         <v>45237</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17918,7 +17918,7 @@
         <v>45588</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17991,7 +17991,7 @@
         <v>45455</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>46139</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18137,7 +18137,7 @@
         <v>45226</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18210,7 +18210,7 @@
         <v>45667</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18283,7 +18283,7 @@
         <v>44550</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18356,7 +18356,7 @@
         <v>45167</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18429,7 +18429,7 @@
         <v>46147</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18507,7 +18507,7 @@
         <v>45672</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18580,7 +18580,7 @@
         <v>45664</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18653,7 +18653,7 @@
         <v>46148</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18726,7 +18726,7 @@
         <v>44973</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18799,7 +18799,7 @@
         <v>45764</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18872,7 +18872,7 @@
         <v>45309</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18945,7 +18945,7 @@
         <v>45314</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19018,7 +19018,7 @@
         <v>46198</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19096,7 +19096,7 @@
         <v>45374</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19169,7 +19169,7 @@
         <v>44928</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19242,7 +19242,7 @@
         <v>46164</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19315,7 +19315,7 @@
         <v>45456</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19388,7 +19388,7 @@
         <v>44813</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19461,7 +19461,7 @@
         <v>45021</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19534,7 +19534,7 @@
         <v>45239</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19607,7 +19607,7 @@
         <v>45495</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19680,7 +19680,7 @@
         <v>46174</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19753,7 +19753,7 @@
         <v>46174</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19826,7 +19826,7 @@
         <v>45882</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19899,7 +19899,7 @@
         <v>45672</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         <v>45771</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
         <v>45915</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20118,7 +20118,7 @@
         <v>44551</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20191,7 +20191,7 @@
         <v>45882</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20264,7 +20264,7 @@
         <v>46177</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20337,7 +20337,7 @@
         <v>45840</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20410,7 +20410,7 @@
         <v>44924</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20483,7 +20483,7 @@
         <v>46177</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20556,7 +20556,7 @@
         <v>46178</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20629,7 +20629,7 @@
         <v>46177</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20702,7 +20702,7 @@
         <v>46181</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20780,7 +20780,7 @@
         <v>45141</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20853,7 +20853,7 @@
         <v>45133</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20926,7 +20926,7 @@
         <v>45355</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21004,7 +21004,7 @@
         <v>44578</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21077,7 +21077,7 @@
         <v>45463</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21150,7 +21150,7 @@
         <v>45063</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21223,7 +21223,7 @@
         <v>46206</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21296,7 +21296,7 @@
         <v>45097</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21369,7 +21369,7 @@
         <v>46210</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21447,7 +21447,7 @@
         <v>46210</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21525,7 +21525,7 @@
         <v>46211</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21598,7 +21598,7 @@
         <v>46212</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21676,7 +21676,7 @@
         <v>45349</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21749,7 +21749,7 @@
         <v>45127</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21822,7 +21822,7 @@
         <v>46258</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21895,7 +21895,7 @@
         <v>45168</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21968,7 +21968,7 @@
         <v>45097</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22041,7 +22041,7 @@
         <v>44956</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22114,7 +22114,7 @@
         <v>46222</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22192,7 +22192,7 @@
         <v>46267</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22265,7 +22265,7 @@
         <v>45071</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22338,7 +22338,7 @@
         <v>46267</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22416,7 +22416,7 @@
         <v>46267</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22494,7 +22494,7 @@
         <v>46266</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22567,7 +22567,7 @@
         <v>46267</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22645,7 +22645,7 @@
         <v>45517</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22718,7 +22718,7 @@
         <v>44733</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22791,7 +22791,7 @@
         <v>45847</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22864,7 +22864,7 @@
         <v>44509</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22937,7 +22937,7 @@
         <v>46141</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23010,7 +23010,7 @@
         <v>44602</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23083,7 +23083,7 @@
         <v>46036</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23156,7 +23156,7 @@
         <v>46288</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23229,7 +23229,7 @@
         <v>45035</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23302,7 +23302,7 @@
         <v>45035</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23375,7 +23375,7 @@
         <v>45365</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23448,7 +23448,7 @@
         <v>45251</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23526,7 +23526,7 @@
         <v>46251</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23599,7 +23599,7 @@
         <v>45215</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23672,7 +23672,7 @@
         <v>45754</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23745,7 +23745,7 @@
         <v>45635</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23818,7 +23818,7 @@
         <v>46293</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23891,7 +23891,7 @@
         <v>45758</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23964,7 +23964,7 @@
         <v>44817</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24037,7 +24037,7 @@
         <v>45167</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24110,7 +24110,7 @@
         <v>45251</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24188,7 +24188,7 @@
         <v>44655</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24261,7 +24261,7 @@
         <v>45238</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24334,7 +24334,7 @@
         <v>45771</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>45076</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24480,7 +24480,7 @@
         <v>44984</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24553,7 +24553,7 @@
         <v>45034</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24626,7 +24626,7 @@
         <v>45093</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24699,7 +24699,7 @@
         <v>45475</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24772,7 +24772,7 @@
         <v>44531</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24845,7 +24845,7 @@
         <v>45554</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24918,7 +24918,7 @@
         <v>45028</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24991,7 +24991,7 @@
         <v>45255</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25064,7 +25064,7 @@
         <v>45121</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25137,7 +25137,7 @@
         <v>45366</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25210,7 +25210,7 @@
         <v>45205</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25283,7 +25283,7 @@
         <v>45426</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25356,7 +25356,7 @@
         <v>45484</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25429,7 +25429,7 @@
         <v>44973</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25502,7 +25502,7 @@
         <v>44967</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25575,7 +25575,7 @@
         <v>44794</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25648,7 +25648,7 @@
         <v>45188</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25721,7 +25721,7 @@
         <v>45197</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25794,7 +25794,7 @@
         <v>44582</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25872,7 +25872,7 @@
         <v>45484</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25945,7 +25945,7 @@
         <v>45387</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26018,7 +26018,7 @@
         <v>45453</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26091,7 +26091,7 @@
         <v>45771</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26164,7 +26164,7 @@
         <v>45553</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26237,7 +26237,7 @@
         <v>44959</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26310,7 +26310,7 @@
         <v>44823</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26383,7 +26383,7 @@
         <v>45644</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26456,7 +26456,7 @@
         <v>45777</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26529,7 +26529,7 @@
         <v>45700</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26602,7 +26602,7 @@
         <v>45328</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26675,7 +26675,7 @@
         <v>45526</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26748,7 +26748,7 @@
         <v>44473</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26821,7 +26821,7 @@
         <v>46129</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>

--- a/Översikt UDDEVALLA.xlsx
+++ b/Översikt UDDEVALLA.xlsx
@@ -601,7 +601,7 @@
         <v>46266</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45656</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>45432</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         <v>45677</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>45656</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>45107</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>45728</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>45317</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>45656</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>45751</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>46253</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>45317</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>45922</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>45740</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>45799</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>45656</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>45990</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>46174</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>45754</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>44825</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>45288</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>45352</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>45513</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 57654-2025</t>
+          <t>A 51747-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3199,14 +3199,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45981</v>
+        <v>45950</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3219,16 +3219,16 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>4.2</v>
+        <v>1.2</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3255,916 +3255,913 @@
         <v>2</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>Mattlummer
+Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="W25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/artfynd/A 51747-2025 artfynd.xlsx", "A 51747-2025")</f>
+        <v/>
+      </c>
+      <c r="X25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor/A 51747-2025 karta.png", "A 51747-2025")</f>
+        <v/>
+      </c>
+      <c r="Y25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor_geotiff/A 51747-2025 georefererad karta.tif", "A 51747-2025")</f>
+        <v/>
+      </c>
+      <c r="AA25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomål/A 51747-2025 FSC-klagomål.docx", "A 51747-2025")</f>
+        <v/>
+      </c>
+      <c r="AB25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomålsmail/A 51747-2025 FSC-klagomål mail.docx", "A 51747-2025")</f>
+        <v/>
+      </c>
+      <c r="AC25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsyn/A 51747-2025 tillsynsbegäran.docx", "A 51747-2025")</f>
+        <v/>
+      </c>
+      <c r="AD25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsynsmail/A 51747-2025 tillsynsbegäran mail.docx", "A 51747-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A 57654-2025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>45981</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>46306</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>UDDEVALLA</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>Gullpudra
 Lundvårlök</t>
         </is>
       </c>
-      <c r="W25">
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1485/artfynd/A 57654-2025 artfynd.xlsx", "A 57654-2025")</f>
         <v/>
       </c>
-      <c r="X25">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor/A 57654-2025 karta.png", "A 57654-2025")</f>
         <v/>
       </c>
-      <c r="Y25">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor_geotiff/A 57654-2025 georefererad karta.tif", "A 57654-2025")</f>
         <v/>
       </c>
-      <c r="AA25">
+      <c r="AA26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomål/A 57654-2025 FSC-klagomål.docx", "A 57654-2025")</f>
         <v/>
       </c>
-      <c r="AB25">
+      <c r="AB26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomålsmail/A 57654-2025 FSC-klagomål mail.docx", "A 57654-2025")</f>
         <v/>
       </c>
-      <c r="AC25">
+      <c r="AC26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsyn/A 57654-2025 tillsynsbegäran.docx", "A 57654-2025")</f>
         <v/>
       </c>
-      <c r="AD25">
+      <c r="AD26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsynsmail/A 57654-2025 tillsynsbegäran mail.docx", "A 57654-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>A 17995-2026</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
         <v>46124</v>
       </c>
-      <c r="E26" s="1" t="n">
-        <v>46305</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>UDDEVALLA</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
+      <c r="E27" s="1" t="n">
+        <v>46306</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>UDDEVALLA</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
         <v>3.8</v>
       </c>
-      <c r="J26" t="n">
+      <c r="J27" t="n">
         <v>2</v>
       </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
         <v>2</v>
       </c>
-      <c r="T26" t="n">
+      <c r="T27" t="n">
         <v>2</v>
       </c>
-      <c r="U26" t="n">
+      <c r="U27" t="n">
         <v>1</v>
       </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Revlummer</t>
         </is>
       </c>
-      <c r="W26">
+      <c r="W27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1485/artfynd/A 17995-2026 artfynd.xlsx", "A 17995-2026")</f>
         <v/>
       </c>
-      <c r="X26">
+      <c r="X27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor/A 17995-2026 karta.png", "A 17995-2026")</f>
         <v/>
       </c>
-      <c r="Y26">
+      <c r="Y27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor_geotiff/A 17995-2026 georefererad karta.tif", "A 17995-2026")</f>
         <v/>
       </c>
-      <c r="AA26">
+      <c r="AA27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomål/A 17995-2026 FSC-klagomål.docx", "A 17995-2026")</f>
         <v/>
       </c>
-      <c r="AB26">
+      <c r="AB27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomålsmail/A 17995-2026 FSC-klagomål mail.docx", "A 17995-2026")</f>
         <v/>
       </c>
-      <c r="AC26">
+      <c r="AC27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsyn/A 17995-2026 tillsynsbegäran.docx", "A 17995-2026")</f>
         <v/>
       </c>
-      <c r="AD26">
+      <c r="AD27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsynsmail/A 17995-2026 tillsynsbegäran mail.docx", "A 17995-2026")</f>
         <v/>
       </c>
-      <c r="AE26">
+      <c r="AE27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1485/fåglar/A 17995-2026 prioriterade fågelarter.docx", "A 17995-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>A 32528-2024</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
         <v>45513</v>
       </c>
-      <c r="E27" s="1" t="n">
-        <v>46305</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>UDDEVALLA</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
+      <c r="E28" s="1" t="n">
+        <v>46306</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>UDDEVALLA</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
         <v>1.5</v>
       </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
         <v>1</v>
       </c>
-      <c r="L27" t="n">
+      <c r="L28" t="n">
         <v>1</v>
       </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
         <v>1</v>
       </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
         <v>2</v>
       </c>
-      <c r="T27" t="n">
+      <c r="T28" t="n">
         <v>4</v>
       </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>Grönhjon
 Granbarkgnagare</t>
         </is>
       </c>
-      <c r="W27">
+      <c r="W28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1485/artfynd/A 32528-2024 artfynd.xlsx", "A 32528-2024")</f>
         <v/>
       </c>
-      <c r="X27">
+      <c r="X28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor/A 32528-2024 karta.png", "A 32528-2024")</f>
         <v/>
       </c>
-      <c r="Y27">
+      <c r="Y28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor_geotiff/A 32528-2024 georefererad karta.tif", "A 32528-2024")</f>
         <v/>
       </c>
-      <c r="AA27">
+      <c r="AA28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomål/A 32528-2024 FSC-klagomål.docx", "A 32528-2024")</f>
         <v/>
       </c>
-      <c r="AB27">
+      <c r="AB28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomålsmail/A 32528-2024 FSC-klagomål mail.docx", "A 32528-2024")</f>
         <v/>
       </c>
-      <c r="AC27">
+      <c r="AC28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsyn/A 32528-2024 tillsynsbegäran.docx", "A 32528-2024")</f>
         <v/>
       </c>
-      <c r="AD27">
+      <c r="AD28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsynsmail/A 32528-2024 tillsynsbegäran mail.docx", "A 32528-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>A 3432-2024</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="n">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="n">
         <v>45317</v>
       </c>
-      <c r="E28" s="1" t="n">
-        <v>46305</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>UDDEVALLA</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
+      <c r="E29" s="1" t="n">
+        <v>46306</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>UDDEVALLA</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
         <is>
           <t>Kyrkan</t>
         </is>
       </c>
-      <c r="I28" t="n">
+      <c r="I29" t="n">
         <v>3.1</v>
       </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
         <v>2</v>
       </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
         <v>2</v>
       </c>
-      <c r="T28" t="n">
+      <c r="T29" t="n">
         <v>2</v>
       </c>
-      <c r="U28" t="n">
+      <c r="U29" t="n">
         <v>2</v>
       </c>
-      <c r="V28" s="2" t="inlineStr">
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>Klippfrullania
 Västlig hakmossa</t>
         </is>
       </c>
-      <c r="W28">
+      <c r="W29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1485/artfynd/A 3432-2024 artfynd.xlsx", "A 3432-2024")</f>
         <v/>
       </c>
-      <c r="X28">
+      <c r="X29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor/A 3432-2024 karta.png", "A 3432-2024")</f>
         <v/>
       </c>
-      <c r="Y28">
+      <c r="Y29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor_geotiff/A 3432-2024 georefererad karta.tif", "A 3432-2024")</f>
         <v/>
       </c>
-      <c r="AA28">
+      <c r="AA29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomål/A 3432-2024 FSC-klagomål.docx", "A 3432-2024")</f>
         <v/>
       </c>
-      <c r="AB28">
+      <c r="AB29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomålsmail/A 3432-2024 FSC-klagomål mail.docx", "A 3432-2024")</f>
         <v/>
       </c>
-      <c r="AC28">
+      <c r="AC29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsyn/A 3432-2024 tillsynsbegäran.docx", "A 3432-2024")</f>
         <v/>
       </c>
-      <c r="AD28">
+      <c r="AD29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsynsmail/A 3432-2024 tillsynsbegäran mail.docx", "A 3432-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>A 36880-2026</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="n">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="n">
         <v>46273</v>
       </c>
-      <c r="E29" s="1" t="n">
-        <v>46305</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>UDDEVALLA</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
+      <c r="E30" s="1" t="n">
+        <v>46306</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>UDDEVALLA</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
         <v>0.5</v>
       </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
         <v>1</v>
       </c>
-      <c r="L29" t="n">
+      <c r="L30" t="n">
         <v>1</v>
       </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
         <v>1</v>
       </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
         <v>2</v>
       </c>
-      <c r="T29" t="n">
+      <c r="T30" t="n">
         <v>2</v>
       </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t>Luddfingersvamp
 Brandticka</t>
         </is>
       </c>
-      <c r="W29">
+      <c r="W30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1485/artfynd/A 36880-2026 artfynd.xlsx", "A 36880-2026")</f>
         <v/>
       </c>
-      <c r="X29">
+      <c r="X30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor/A 36880-2026 karta.png", "A 36880-2026")</f>
         <v/>
       </c>
-      <c r="Y29">
+      <c r="Y30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor_geotiff/A 36880-2026 georefererad karta.tif", "A 36880-2026")</f>
         <v/>
       </c>
-      <c r="AA29">
+      <c r="AA30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomål/A 36880-2026 FSC-klagomål.docx", "A 36880-2026")</f>
         <v/>
       </c>
-      <c r="AB29">
+      <c r="AB30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomålsmail/A 36880-2026 FSC-klagomål mail.docx", "A 36880-2026")</f>
         <v/>
       </c>
-      <c r="AC29">
+      <c r="AC30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsyn/A 36880-2026 tillsynsbegäran.docx", "A 36880-2026")</f>
         <v/>
       </c>
-      <c r="AD29">
+      <c r="AD30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsynsmail/A 36880-2026 tillsynsbegäran mail.docx", "A 36880-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>A 32808-2026</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D30" s="1" t="n">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="n">
         <v>46241</v>
       </c>
-      <c r="E30" s="1" t="n">
-        <v>46305</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>UDDEVALLA</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
+      <c r="E31" s="1" t="n">
+        <v>46306</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>UDDEVALLA</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
         <is>
           <t>Kyrkan</t>
         </is>
       </c>
-      <c r="I30" t="n">
+      <c r="I31" t="n">
         <v>5.9</v>
       </c>
-      <c r="J30" t="n">
+      <c r="J31" t="n">
         <v>2</v>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
         <v>1</v>
       </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
         <v>1</v>
       </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
         <v>2</v>
       </c>
-      <c r="T30" t="n">
+      <c r="T31" t="n">
         <v>2</v>
       </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
         <is>
           <t>Nordfladdermus
 Revlummer</t>
         </is>
       </c>
-      <c r="W30">
+      <c r="W31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1485/artfynd/A 32808-2026 artfynd.xlsx", "A 32808-2026")</f>
         <v/>
       </c>
-      <c r="X30">
+      <c r="X31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor/A 32808-2026 karta.png", "A 32808-2026")</f>
         <v/>
       </c>
-      <c r="Y30">
+      <c r="Y31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor_geotiff/A 32808-2026 georefererad karta.tif", "A 32808-2026")</f>
         <v/>
       </c>
-      <c r="AA30">
+      <c r="AA31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomål/A 32808-2026 FSC-klagomål.docx", "A 32808-2026")</f>
         <v/>
       </c>
-      <c r="AB30">
+      <c r="AB31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomålsmail/A 32808-2026 FSC-klagomål mail.docx", "A 32808-2026")</f>
         <v/>
       </c>
-      <c r="AC30">
+      <c r="AC31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsyn/A 32808-2026 tillsynsbegäran.docx", "A 32808-2026")</f>
         <v/>
       </c>
-      <c r="AD30">
+      <c r="AD31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsynsmail/A 32808-2026 tillsynsbegäran mail.docx", "A 32808-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>A 266-2025</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="n">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="n">
         <v>45653</v>
       </c>
-      <c r="E31" s="1" t="n">
-        <v>46305</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>UDDEVALLA</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
+      <c r="E32" s="1" t="n">
+        <v>46306</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>UDDEVALLA</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
         <v>3.4</v>
       </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
         <v>1</v>
       </c>
-      <c r="L31" t="n">
+      <c r="L32" t="n">
         <v>1</v>
       </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
         <v>1</v>
       </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
         <v>2</v>
       </c>
-      <c r="T31" t="n">
+      <c r="T32" t="n">
         <v>2</v>
       </c>
-      <c r="U31" t="n">
+      <c r="U32" t="n">
         <v>2</v>
       </c>
-      <c r="V31" s="2" t="inlineStr">
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>Brunpudrad nållav
 Blåmossa</t>
         </is>
       </c>
-      <c r="W31">
+      <c r="W32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1485/artfynd/A 266-2025 artfynd.xlsx", "A 266-2025")</f>
         <v/>
       </c>
-      <c r="X31">
+      <c r="X32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor/A 266-2025 karta.png", "A 266-2025")</f>
         <v/>
       </c>
-      <c r="Y31">
+      <c r="Y32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor_geotiff/A 266-2025 georefererad karta.tif", "A 266-2025")</f>
         <v/>
       </c>
-      <c r="AA31">
+      <c r="AA32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomål/A 266-2025 FSC-klagomål.docx", "A 266-2025")</f>
         <v/>
       </c>
-      <c r="AB31">
+      <c r="AB32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomålsmail/A 266-2025 FSC-klagomål mail.docx", "A 266-2025")</f>
         <v/>
       </c>
-      <c r="AC31">
+      <c r="AC32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsyn/A 266-2025 tillsynsbegäran.docx", "A 266-2025")</f>
         <v/>
       </c>
-      <c r="AD31">
+      <c r="AD32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsynsmail/A 266-2025 tillsynsbegäran mail.docx", "A 266-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>A 34390-2026</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D32" s="1" t="n">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D33" s="1" t="n">
         <v>46253</v>
       </c>
-      <c r="E32" s="1" t="n">
-        <v>46305</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>UDDEVALLA</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
+      <c r="E33" s="1" t="n">
+        <v>46306</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>UDDEVALLA</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
         <v>2.5</v>
       </c>
-      <c r="J32" t="n">
+      <c r="J33" t="n">
         <v>1</v>
       </c>
-      <c r="K32" t="n">
+      <c r="K33" t="n">
         <v>1</v>
       </c>
-      <c r="L32" t="n">
+      <c r="L33" t="n">
         <v>1</v>
       </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
         <v>1</v>
       </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
         <v>2</v>
       </c>
-      <c r="T32" t="n">
+      <c r="T33" t="n">
         <v>2</v>
       </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
         <is>
           <t>Mindre hackspett
 Större träfjäril</t>
         </is>
       </c>
-      <c r="W32">
+      <c r="W33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1485/artfynd/A 34390-2026 artfynd.xlsx", "A 34390-2026")</f>
         <v/>
       </c>
-      <c r="X32">
+      <c r="X33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor/A 34390-2026 karta.png", "A 34390-2026")</f>
         <v/>
       </c>
-      <c r="Y32">
+      <c r="Y33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor_geotiff/A 34390-2026 georefererad karta.tif", "A 34390-2026")</f>
         <v/>
       </c>
-      <c r="AA32">
+      <c r="AA33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomål/A 34390-2026 FSC-klagomål.docx", "A 34390-2026")</f>
         <v/>
       </c>
-      <c r="AB32">
+      <c r="AB33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomålsmail/A 34390-2026 FSC-klagomål mail.docx", "A 34390-2026")</f>
         <v/>
       </c>
-      <c r="AC32">
+      <c r="AC33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsyn/A 34390-2026 tillsynsbegäran.docx", "A 34390-2026")</f>
         <v/>
       </c>
-      <c r="AD32">
+      <c r="AD33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsynsmail/A 34390-2026 tillsynsbegäran mail.docx", "A 34390-2026")</f>
         <v/>
       </c>
-      <c r="AE32">
+      <c r="AE33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1485/fåglar/A 34390-2026 prioriterade fågelarter.docx", "A 34390-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>A 25806-2022</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D33" s="1" t="n">
-        <v>44733</v>
-      </c>
-      <c r="E33" s="1" t="n">
-        <v>46305</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>UDDEVALLA</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="J33" t="n">
-        <v>1</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>1</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>1</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>1</v>
-      </c>
-      <c r="T33" t="n">
-        <v>1</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1</v>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
-        <is>
-          <t>Duvhök</t>
-        </is>
-      </c>
-      <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/artfynd/A 25806-2022 artfynd.xlsx", "A 25806-2022")</f>
-        <v/>
-      </c>
-      <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor/A 25806-2022 karta.png", "A 25806-2022")</f>
-        <v/>
-      </c>
-      <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor_geotiff/A 25806-2022 georefererad karta.tif", "A 25806-2022")</f>
-        <v/>
-      </c>
-      <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomål/A 25806-2022 FSC-klagomål.docx", "A 25806-2022")</f>
-        <v/>
-      </c>
-      <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomålsmail/A 25806-2022 FSC-klagomål mail.docx", "A 25806-2022")</f>
-        <v/>
-      </c>
-      <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsyn/A 25806-2022 tillsynsbegäran.docx", "A 25806-2022")</f>
-        <v/>
-      </c>
-      <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsynsmail/A 25806-2022 tillsynsbegäran mail.docx", "A 25806-2022")</f>
-        <v/>
-      </c>
-      <c r="AE33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/fåglar/A 25806-2022 prioriterade fågelarter.docx", "A 25806-2022")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 10865-2022</t>
+          <t>A 25806-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4178,10 +4175,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44627</v>
+        <v>44733</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4194,7 +4191,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.9</v>
+        <v>31.2</v>
       </c>
       <c r="J34" t="n">
         <v>1</v>
@@ -4203,7 +4200,7 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -4218,7 +4215,7 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -4230,46 +4227,50 @@
         <v>1</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/artfynd/A 10865-2022 artfynd.xlsx", "A 10865-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/artfynd/A 25806-2022 artfynd.xlsx", "A 25806-2022")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor/A 10865-2022 karta.png", "A 10865-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor/A 25806-2022 karta.png", "A 25806-2022")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor_geotiff/A 10865-2022 georefererad karta.tif", "A 10865-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor_geotiff/A 25806-2022 georefererad karta.tif", "A 25806-2022")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomål/A 10865-2022 FSC-klagomål.docx", "A 10865-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomål/A 25806-2022 FSC-klagomål.docx", "A 25806-2022")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomålsmail/A 10865-2022 FSC-klagomål mail.docx", "A 10865-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomålsmail/A 25806-2022 FSC-klagomål mail.docx", "A 25806-2022")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsyn/A 10865-2022 tillsynsbegäran.docx", "A 10865-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsyn/A 25806-2022 tillsynsbegäran.docx", "A 25806-2022")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsynsmail/A 10865-2022 tillsynsbegäran mail.docx", "A 10865-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsynsmail/A 25806-2022 tillsynsbegäran mail.docx", "A 25806-2022")</f>
+        <v/>
+      </c>
+      <c r="AE34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/fåglar/A 25806-2022 prioriterade fågelarter.docx", "A 25806-2022")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 29691-2023</t>
+          <t>A 10865-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4283,10 +4284,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45107</v>
+        <v>44627</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4299,7 +4300,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>3.9</v>
       </c>
       <c r="J35" t="n">
         <v>1</v>
@@ -4335,46 +4336,46 @@
         <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/artfynd/A 29691-2023 artfynd.xlsx", "A 29691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/artfynd/A 10865-2022 artfynd.xlsx", "A 10865-2022")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor/A 29691-2023 karta.png", "A 29691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor/A 10865-2022 karta.png", "A 10865-2022")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor_geotiff/A 29691-2023 georefererad karta.tif", "A 29691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor_geotiff/A 10865-2022 georefererad karta.tif", "A 10865-2022")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomål/A 29691-2023 FSC-klagomål.docx", "A 29691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomål/A 10865-2022 FSC-klagomål.docx", "A 10865-2022")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomålsmail/A 29691-2023 FSC-klagomål mail.docx", "A 29691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomålsmail/A 10865-2022 FSC-klagomål mail.docx", "A 10865-2022")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsyn/A 29691-2023 tillsynsbegäran.docx", "A 29691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsyn/A 10865-2022 tillsynsbegäran.docx", "A 10865-2022")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsynsmail/A 29691-2023 tillsynsbegäran mail.docx", "A 29691-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsynsmail/A 10865-2022 tillsynsbegäran mail.docx", "A 10865-2022")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 236-2023</t>
+          <t>A 29691-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4388,10 +4389,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44928</v>
+        <v>45107</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4404,13 +4405,13 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>16.7</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -4440,46 +4441,46 @@
         <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/artfynd/A 236-2023 artfynd.xlsx", "A 236-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/artfynd/A 29691-2023 artfynd.xlsx", "A 29691-2023")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor/A 236-2023 karta.png", "A 236-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor/A 29691-2023 karta.png", "A 29691-2023")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor_geotiff/A 236-2023 georefererad karta.tif", "A 236-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor_geotiff/A 29691-2023 georefererad karta.tif", "A 29691-2023")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomål/A 236-2023 FSC-klagomål.docx", "A 236-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomål/A 29691-2023 FSC-klagomål.docx", "A 29691-2023")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomålsmail/A 236-2023 FSC-klagomål mail.docx", "A 236-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomålsmail/A 29691-2023 FSC-klagomål mail.docx", "A 29691-2023")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsyn/A 236-2023 tillsynsbegäran.docx", "A 236-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsyn/A 29691-2023 tillsynsbegäran.docx", "A 29691-2023")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsynsmail/A 236-2023 tillsynsbegäran mail.docx", "A 236-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsynsmail/A 29691-2023 tillsynsbegäran mail.docx", "A 29691-2023")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 23401-2023</t>
+          <t>A 236-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4493,10 +4494,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45076</v>
+        <v>44928</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4509,7 +4510,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.3</v>
+        <v>16.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4545,46 +4546,46 @@
         <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/artfynd/A 23401-2023 artfynd.xlsx", "A 23401-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/artfynd/A 236-2023 artfynd.xlsx", "A 236-2023")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor/A 23401-2023 karta.png", "A 23401-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor/A 236-2023 karta.png", "A 236-2023")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor_geotiff/A 23401-2023 georefererad karta.tif", "A 23401-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor_geotiff/A 236-2023 georefererad karta.tif", "A 236-2023")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomål/A 23401-2023 FSC-klagomål.docx", "A 23401-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomål/A 236-2023 FSC-klagomål.docx", "A 236-2023")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomålsmail/A 23401-2023 FSC-klagomål mail.docx", "A 23401-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomålsmail/A 236-2023 FSC-klagomål mail.docx", "A 236-2023")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsyn/A 23401-2023 tillsynsbegäran.docx", "A 23401-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsyn/A 236-2023 tillsynsbegäran.docx", "A 236-2023")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsynsmail/A 23401-2023 tillsynsbegäran mail.docx", "A 23401-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsynsmail/A 236-2023 tillsynsbegäran mail.docx", "A 236-2023")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 34058-2023</t>
+          <t>A 23401-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4598,10 +4599,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45135</v>
+        <v>45076</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4614,19 +4615,19 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -4638,58 +4639,58 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
       </c>
       <c r="T38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Lundvaxskivling</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/artfynd/A 34058-2023 artfynd.xlsx", "A 34058-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/artfynd/A 23401-2023 artfynd.xlsx", "A 23401-2023")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor/A 34058-2023 karta.png", "A 34058-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor/A 23401-2023 karta.png", "A 23401-2023")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor_geotiff/A 34058-2023 georefererad karta.tif", "A 34058-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor_geotiff/A 23401-2023 georefererad karta.tif", "A 23401-2023")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomål/A 34058-2023 FSC-klagomål.docx", "A 34058-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomål/A 23401-2023 FSC-klagomål.docx", "A 23401-2023")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomålsmail/A 34058-2023 FSC-klagomål mail.docx", "A 34058-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomålsmail/A 23401-2023 FSC-klagomål mail.docx", "A 23401-2023")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsyn/A 34058-2023 tillsynsbegäran.docx", "A 34058-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsyn/A 23401-2023 tillsynsbegäran.docx", "A 23401-2023")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsynsmail/A 34058-2023 tillsynsbegäran mail.docx", "A 34058-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsynsmail/A 23401-2023 tillsynsbegäran mail.docx", "A 23401-2023")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 495-2023</t>
+          <t>A 34058-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4703,10 +4704,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44930</v>
+        <v>45135</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4718,25 +4719,20 @@
           <t>UDDEVALLA</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>3.7</v>
+        <v>1.3</v>
       </c>
       <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
         <v>1</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
-        <v>1</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -4751,59 +4747,55 @@
         <v>1</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
       </c>
       <c r="T39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Lundvaxskivling</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/artfynd/A 495-2023 artfynd.xlsx", "A 495-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/artfynd/A 34058-2023 artfynd.xlsx", "A 34058-2023")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor/A 495-2023 karta.png", "A 495-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor/A 34058-2023 karta.png", "A 34058-2023")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor_geotiff/A 495-2023 georefererad karta.tif", "A 495-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor_geotiff/A 34058-2023 georefererad karta.tif", "A 34058-2023")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomål/A 495-2023 FSC-klagomål.docx", "A 495-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomål/A 34058-2023 FSC-klagomål.docx", "A 34058-2023")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomålsmail/A 495-2023 FSC-klagomål mail.docx", "A 495-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomålsmail/A 34058-2023 FSC-klagomål mail.docx", "A 34058-2023")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsyn/A 495-2023 tillsynsbegäran.docx", "A 495-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsyn/A 34058-2023 tillsynsbegäran.docx", "A 34058-2023")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsynsmail/A 495-2023 tillsynsbegäran mail.docx", "A 495-2023")</f>
-        <v/>
-      </c>
-      <c r="AE39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/fåglar/A 495-2023 prioriterade fågelarter.docx", "A 495-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsynsmail/A 34058-2023 tillsynsbegäran mail.docx", "A 34058-2023")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 23322-2025</t>
+          <t>A 495-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4817,10 +4809,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45791</v>
+        <v>44930</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4832,8 +4824,13 @@
           <t>UDDEVALLA</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="J40" t="n">
         <v>1</v>
@@ -4869,50 +4866,50 @@
         <v>1</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Kungsörn</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/artfynd/A 23322-2025 artfynd.xlsx", "A 23322-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/artfynd/A 495-2023 artfynd.xlsx", "A 495-2023")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor/A 23322-2025 karta.png", "A 23322-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor/A 495-2023 karta.png", "A 495-2023")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor_geotiff/A 23322-2025 georefererad karta.tif", "A 23322-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor_geotiff/A 495-2023 georefererad karta.tif", "A 495-2023")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomål/A 23322-2025 FSC-klagomål.docx", "A 23322-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomål/A 495-2023 FSC-klagomål.docx", "A 495-2023")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomålsmail/A 23322-2025 FSC-klagomål mail.docx", "A 23322-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomålsmail/A 495-2023 FSC-klagomål mail.docx", "A 495-2023")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsyn/A 23322-2025 tillsynsbegäran.docx", "A 23322-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsyn/A 495-2023 tillsynsbegäran.docx", "A 495-2023")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsynsmail/A 23322-2025 tillsynsbegäran mail.docx", "A 23322-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsynsmail/A 495-2023 tillsynsbegäran mail.docx", "A 495-2023")</f>
         <v/>
       </c>
       <c r="AE40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/fåglar/A 23322-2025 prioriterade fågelarter.docx", "A 23322-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/fåglar/A 495-2023 prioriterade fågelarter.docx", "A 495-2023")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 22603-2023</t>
+          <t>A 23322-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4926,10 +4923,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45071</v>
+        <v>45791</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4942,7 +4939,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="J41" t="n">
         <v>1</v>
@@ -4951,7 +4948,7 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -4966,7 +4963,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -4978,46 +4975,50 @@
         <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Kungsörn</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/artfynd/A 22603-2023 artfynd.xlsx", "A 22603-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/artfynd/A 23322-2025 artfynd.xlsx", "A 23322-2025")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor/A 22603-2023 karta.png", "A 22603-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor/A 23322-2025 karta.png", "A 23322-2025")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor_geotiff/A 22603-2023 georefererad karta.tif", "A 22603-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor_geotiff/A 23322-2025 georefererad karta.tif", "A 23322-2025")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomål/A 22603-2023 FSC-klagomål.docx", "A 22603-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomål/A 23322-2025 FSC-klagomål.docx", "A 23322-2025")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomålsmail/A 22603-2023 FSC-klagomål mail.docx", "A 22603-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomålsmail/A 23322-2025 FSC-klagomål mail.docx", "A 23322-2025")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsyn/A 22603-2023 tillsynsbegäran.docx", "A 22603-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsyn/A 23322-2025 tillsynsbegäran.docx", "A 23322-2025")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsynsmail/A 22603-2023 tillsynsbegäran mail.docx", "A 22603-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsynsmail/A 23322-2025 tillsynsbegäran mail.docx", "A 23322-2025")</f>
+        <v/>
+      </c>
+      <c r="AE41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/fåglar/A 23322-2025 prioriterade fågelarter.docx", "A 23322-2025")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 30954-2025</t>
+          <t>A 22603-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5031,10 +5032,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45832</v>
+        <v>45071</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5047,16 +5048,16 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>11</v>
+        <v>2.7</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -5071,7 +5072,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -5083,46 +5084,46 @@
         <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/artfynd/A 30954-2025 artfynd.xlsx", "A 30954-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/artfynd/A 22603-2023 artfynd.xlsx", "A 22603-2023")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor/A 30954-2025 karta.png", "A 30954-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor/A 22603-2023 karta.png", "A 22603-2023")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor_geotiff/A 30954-2025 georefererad karta.tif", "A 30954-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor_geotiff/A 22603-2023 georefererad karta.tif", "A 22603-2023")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomål/A 30954-2025 FSC-klagomål.docx", "A 30954-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomål/A 22603-2023 FSC-klagomål.docx", "A 22603-2023")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomålsmail/A 30954-2025 FSC-klagomål mail.docx", "A 30954-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomålsmail/A 22603-2023 FSC-klagomål mail.docx", "A 22603-2023")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsyn/A 30954-2025 tillsynsbegäran.docx", "A 30954-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsyn/A 22603-2023 tillsynsbegäran.docx", "A 22603-2023")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsynsmail/A 30954-2025 tillsynsbegäran mail.docx", "A 30954-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsynsmail/A 22603-2023 tillsynsbegäran mail.docx", "A 22603-2023")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 1293-2024</t>
+          <t>A 30954-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5136,10 +5137,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45303</v>
+        <v>45832</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5152,19 +5153,19 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.2</v>
+        <v>11</v>
       </c>
       <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
         <v>1</v>
       </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
       <c r="M43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -5179,7 +5180,7 @@
         <v>1</v>
       </c>
       <c r="R43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -5188,50 +5189,46 @@
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/artfynd/A 1293-2024 artfynd.xlsx", "A 1293-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/artfynd/A 30954-2025 artfynd.xlsx", "A 30954-2025")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor/A 1293-2024 karta.png", "A 1293-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor/A 30954-2025 karta.png", "A 30954-2025")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor_geotiff/A 1293-2024 georefererad karta.tif", "A 1293-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor_geotiff/A 30954-2025 georefererad karta.tif", "A 30954-2025")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomål/A 1293-2024 FSC-klagomål.docx", "A 1293-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomål/A 30954-2025 FSC-klagomål.docx", "A 30954-2025")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomålsmail/A 1293-2024 FSC-klagomål mail.docx", "A 1293-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomålsmail/A 30954-2025 FSC-klagomål mail.docx", "A 30954-2025")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsyn/A 1293-2024 tillsynsbegäran.docx", "A 1293-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsyn/A 30954-2025 tillsynsbegäran.docx", "A 30954-2025")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsynsmail/A 1293-2024 tillsynsbegäran mail.docx", "A 1293-2024")</f>
-        <v/>
-      </c>
-      <c r="AE43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/fåglar/A 1293-2024 prioriterade fågelarter.docx", "A 1293-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsynsmail/A 30954-2025 tillsynsbegäran mail.docx", "A 30954-2025")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 55288-2023</t>
+          <t>A 1293-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5245,10 +5242,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45237</v>
+        <v>45303</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5261,7 +5258,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>5.2</v>
+        <v>2.2</v>
       </c>
       <c r="J44" t="n">
         <v>1</v>
@@ -5273,7 +5270,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
@@ -5285,10 +5282,10 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
@@ -5297,46 +5294,50 @@
         <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/artfynd/A 55288-2023 artfynd.xlsx", "A 55288-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/artfynd/A 1293-2024 artfynd.xlsx", "A 1293-2024")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor/A 55288-2023 karta.png", "A 55288-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor/A 1293-2024 karta.png", "A 1293-2024")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor_geotiff/A 55288-2023 georefererad karta.tif", "A 55288-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor_geotiff/A 1293-2024 georefererad karta.tif", "A 1293-2024")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomål/A 55288-2023 FSC-klagomål.docx", "A 55288-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomål/A 1293-2024 FSC-klagomål.docx", "A 1293-2024")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomålsmail/A 55288-2023 FSC-klagomål mail.docx", "A 55288-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomålsmail/A 1293-2024 FSC-klagomål mail.docx", "A 1293-2024")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsyn/A 55288-2023 tillsynsbegäran.docx", "A 55288-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsyn/A 1293-2024 tillsynsbegäran.docx", "A 1293-2024")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsynsmail/A 55288-2023 tillsynsbegäran mail.docx", "A 55288-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsynsmail/A 1293-2024 tillsynsbegäran mail.docx", "A 1293-2024")</f>
+        <v/>
+      </c>
+      <c r="AE44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/fåglar/A 1293-2024 prioriterade fågelarter.docx", "A 1293-2024")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 50274-2024</t>
+          <t>A 55288-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5350,10 +5351,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45600</v>
+        <v>45237</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5366,7 +5367,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>20.1</v>
+        <v>5.2</v>
       </c>
       <c r="J45" t="n">
         <v>1</v>
@@ -5375,7 +5376,7 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -5390,7 +5391,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -5406,46 +5407,42 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/artfynd/A 50274-2024 artfynd.xlsx", "A 50274-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/artfynd/A 55288-2023 artfynd.xlsx", "A 55288-2023")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor/A 50274-2024 karta.png", "A 50274-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor/A 55288-2023 karta.png", "A 55288-2023")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor_geotiff/A 50274-2024 georefererad karta.tif", "A 50274-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor_geotiff/A 55288-2023 georefererad karta.tif", "A 55288-2023")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomål/A 50274-2024 FSC-klagomål.docx", "A 50274-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomål/A 55288-2023 FSC-klagomål.docx", "A 55288-2023")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomålsmail/A 50274-2024 FSC-klagomål mail.docx", "A 50274-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomålsmail/A 55288-2023 FSC-klagomål mail.docx", "A 55288-2023")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsyn/A 50274-2024 tillsynsbegäran.docx", "A 50274-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsyn/A 55288-2023 tillsynsbegäran.docx", "A 55288-2023")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsynsmail/A 50274-2024 tillsynsbegäran mail.docx", "A 50274-2024")</f>
-        <v/>
-      </c>
-      <c r="AE45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/fåglar/A 50274-2024 prioriterade fågelarter.docx", "A 50274-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsynsmail/A 55288-2023 tillsynsbegäran mail.docx", "A 55288-2023")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 7770-2024</t>
+          <t>A 50274-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5459,10 +5456,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45348</v>
+        <v>45600</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5474,13 +5471,8 @@
           <t>UDDEVALLA</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>6.2</v>
+        <v>20.1</v>
       </c>
       <c r="J46" t="n">
         <v>1</v>
@@ -5489,7 +5481,7 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -5504,7 +5496,7 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -5516,46 +5508,50 @@
         <v>1</v>
       </c>
       <c r="U46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/artfynd/A 7770-2024 artfynd.xlsx", "A 7770-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/artfynd/A 50274-2024 artfynd.xlsx", "A 50274-2024")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor/A 7770-2024 karta.png", "A 7770-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor/A 50274-2024 karta.png", "A 50274-2024")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor_geotiff/A 7770-2024 georefererad karta.tif", "A 7770-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor_geotiff/A 50274-2024 georefererad karta.tif", "A 50274-2024")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomål/A 7770-2024 FSC-klagomål.docx", "A 7770-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomål/A 50274-2024 FSC-klagomål.docx", "A 50274-2024")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomålsmail/A 7770-2024 FSC-klagomål mail.docx", "A 7770-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomålsmail/A 50274-2024 FSC-klagomål mail.docx", "A 50274-2024")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsyn/A 7770-2024 tillsynsbegäran.docx", "A 7770-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsyn/A 50274-2024 tillsynsbegäran.docx", "A 50274-2024")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsynsmail/A 7770-2024 tillsynsbegäran mail.docx", "A 7770-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsynsmail/A 50274-2024 tillsynsbegäran mail.docx", "A 50274-2024")</f>
+        <v/>
+      </c>
+      <c r="AE46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/fåglar/A 50274-2024 prioriterade fågelarter.docx", "A 50274-2024")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 2429-2026</t>
+          <t>A 7770-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5569,10 +5565,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46036</v>
+        <v>45348</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5584,11 +5580,16 @@
           <t>UDDEVALLA</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -5597,7 +5598,7 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
@@ -5609,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>1</v>
@@ -5621,46 +5622,46 @@
         <v>1</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/artfynd/A 2429-2026 artfynd.xlsx", "A 2429-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/artfynd/A 7770-2024 artfynd.xlsx", "A 7770-2024")</f>
         <v/>
       </c>
       <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor/A 2429-2026 karta.png", "A 2429-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor/A 7770-2024 karta.png", "A 7770-2024")</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor_geotiff/A 2429-2026 georefererad karta.tif", "A 2429-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor_geotiff/A 7770-2024 georefererad karta.tif", "A 7770-2024")</f>
         <v/>
       </c>
       <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomål/A 2429-2026 FSC-klagomål.docx", "A 2429-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomål/A 7770-2024 FSC-klagomål.docx", "A 7770-2024")</f>
         <v/>
       </c>
       <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomålsmail/A 2429-2026 FSC-klagomål mail.docx", "A 2429-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomålsmail/A 7770-2024 FSC-klagomål mail.docx", "A 7770-2024")</f>
         <v/>
       </c>
       <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsyn/A 2429-2026 tillsynsbegäran.docx", "A 2429-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsyn/A 7770-2024 tillsynsbegäran.docx", "A 7770-2024")</f>
         <v/>
       </c>
       <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsynsmail/A 2429-2026 tillsynsbegäran mail.docx", "A 2429-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsynsmail/A 7770-2024 tillsynsbegäran mail.docx", "A 7770-2024")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 9424-2026</t>
+          <t>A 2429-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5674,10 +5675,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46071</v>
+        <v>46036</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5690,7 +5691,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>4.3</v>
+        <v>7.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5730,42 +5731,42 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>Flotagräs</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="W48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/artfynd/A 9424-2026 artfynd.xlsx", "A 9424-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/artfynd/A 2429-2026 artfynd.xlsx", "A 2429-2026")</f>
         <v/>
       </c>
       <c r="X48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor/A 9424-2026 karta.png", "A 9424-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor/A 2429-2026 karta.png", "A 2429-2026")</f>
         <v/>
       </c>
       <c r="Y48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor_geotiff/A 9424-2026 georefererad karta.tif", "A 9424-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor_geotiff/A 2429-2026 georefererad karta.tif", "A 2429-2026")</f>
         <v/>
       </c>
       <c r="AA48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomål/A 9424-2026 FSC-klagomål.docx", "A 9424-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomål/A 2429-2026 FSC-klagomål.docx", "A 2429-2026")</f>
         <v/>
       </c>
       <c r="AB48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomålsmail/A 9424-2026 FSC-klagomål mail.docx", "A 9424-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomålsmail/A 2429-2026 FSC-klagomål mail.docx", "A 2429-2026")</f>
         <v/>
       </c>
       <c r="AC48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsyn/A 9424-2026 tillsynsbegäran.docx", "A 9424-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsyn/A 2429-2026 tillsynsbegäran.docx", "A 2429-2026")</f>
         <v/>
       </c>
       <c r="AD48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsynsmail/A 9424-2026 tillsynsbegäran mail.docx", "A 9424-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsynsmail/A 2429-2026 tillsynsbegäran mail.docx", "A 2429-2026")</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 39966-2026</t>
+          <t>A 9424-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5779,10 +5780,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46292</v>
+        <v>46071</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5794,26 +5795,21 @@
           <t>UDDEVALLA</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
         <v>1</v>
       </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0</v>
-      </c>
       <c r="N49" t="n">
         <v>0</v>
       </c>
@@ -5824,10 +5820,10 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S49" t="n">
         <v>1</v>
@@ -5840,42 +5836,42 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Flotagräs</t>
         </is>
       </c>
       <c r="W49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/artfynd/A 39966-2026 artfynd.xlsx", "A 39966-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/artfynd/A 9424-2026 artfynd.xlsx", "A 9424-2026")</f>
         <v/>
       </c>
       <c r="X49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor/A 39966-2026 karta.png", "A 39966-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor/A 9424-2026 karta.png", "A 9424-2026")</f>
         <v/>
       </c>
       <c r="Y49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor_geotiff/A 39966-2026 georefererad karta.tif", "A 39966-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor_geotiff/A 9424-2026 georefererad karta.tif", "A 9424-2026")</f>
         <v/>
       </c>
       <c r="AA49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomål/A 39966-2026 FSC-klagomål.docx", "A 39966-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomål/A 9424-2026 FSC-klagomål.docx", "A 9424-2026")</f>
         <v/>
       </c>
       <c r="AB49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomålsmail/A 39966-2026 FSC-klagomål mail.docx", "A 39966-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomålsmail/A 9424-2026 FSC-klagomål mail.docx", "A 9424-2026")</f>
         <v/>
       </c>
       <c r="AC49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsyn/A 39966-2026 tillsynsbegäran.docx", "A 39966-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsyn/A 9424-2026 tillsynsbegäran.docx", "A 9424-2026")</f>
         <v/>
       </c>
       <c r="AD49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsynsmail/A 39966-2026 tillsynsbegäran mail.docx", "A 39966-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsynsmail/A 9424-2026 tillsynsbegäran mail.docx", "A 9424-2026")</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 33812-2026</t>
+          <t>A 39966-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5889,10 +5885,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46251</v>
+        <v>46292</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5906,17 +5902,17 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.8</v>
+        <v>4.4</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -5950,42 +5946,42 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>Skogsbräsma</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/artfynd/A 33812-2026 artfynd.xlsx", "A 33812-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/artfynd/A 39966-2026 artfynd.xlsx", "A 39966-2026")</f>
         <v/>
       </c>
       <c r="X50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor/A 33812-2026 karta.png", "A 33812-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor/A 39966-2026 karta.png", "A 39966-2026")</f>
         <v/>
       </c>
       <c r="Y50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor_geotiff/A 33812-2026 georefererad karta.tif", "A 33812-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor_geotiff/A 39966-2026 georefererad karta.tif", "A 39966-2026")</f>
         <v/>
       </c>
       <c r="AA50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomål/A 33812-2026 FSC-klagomål.docx", "A 33812-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomål/A 39966-2026 FSC-klagomål.docx", "A 39966-2026")</f>
         <v/>
       </c>
       <c r="AB50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomålsmail/A 33812-2026 FSC-klagomål mail.docx", "A 33812-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomålsmail/A 39966-2026 FSC-klagomål mail.docx", "A 39966-2026")</f>
         <v/>
       </c>
       <c r="AC50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsyn/A 33812-2026 tillsynsbegäran.docx", "A 33812-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsyn/A 39966-2026 tillsynsbegäran.docx", "A 39966-2026")</f>
         <v/>
       </c>
       <c r="AD50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsynsmail/A 33812-2026 tillsynsbegäran mail.docx", "A 33812-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsynsmail/A 39966-2026 tillsynsbegäran mail.docx", "A 39966-2026")</f>
         <v/>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 42009-2026</t>
+          <t>A 33812-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5999,10 +5995,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46303</v>
+        <v>46251</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6014,14 +6010,19 @@
           <t>UDDEVALLA</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
         <v>1</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -6055,42 +6056,42 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogsbräsma</t>
         </is>
       </c>
       <c r="W51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/artfynd/A 42009-2026 artfynd.xlsx", "A 42009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/artfynd/A 33812-2026 artfynd.xlsx", "A 33812-2026")</f>
         <v/>
       </c>
       <c r="X51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor/A 42009-2026 karta.png", "A 42009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor/A 33812-2026 karta.png", "A 33812-2026")</f>
         <v/>
       </c>
       <c r="Y51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor_geotiff/A 42009-2026 georefererad karta.tif", "A 42009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor_geotiff/A 33812-2026 georefererad karta.tif", "A 33812-2026")</f>
         <v/>
       </c>
       <c r="AA51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomål/A 42009-2026 FSC-klagomål.docx", "A 42009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomål/A 33812-2026 FSC-klagomål.docx", "A 33812-2026")</f>
         <v/>
       </c>
       <c r="AB51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomålsmail/A 42009-2026 FSC-klagomål mail.docx", "A 42009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomålsmail/A 33812-2026 FSC-klagomål mail.docx", "A 33812-2026")</f>
         <v/>
       </c>
       <c r="AC51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsyn/A 42009-2026 tillsynsbegäran.docx", "A 42009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsyn/A 33812-2026 tillsynsbegäran.docx", "A 33812-2026")</f>
         <v/>
       </c>
       <c r="AD51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsynsmail/A 42009-2026 tillsynsbegäran mail.docx", "A 42009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsynsmail/A 33812-2026 tillsynsbegäran mail.docx", "A 33812-2026")</f>
         <v/>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 42008-2026</t>
+          <t>A 42009-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6107,7 +6108,7 @@
         <v>46303</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6120,7 +6121,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>12</v>
+        <v>2.4</v>
       </c>
       <c r="J52" t="n">
         <v>1</v>
@@ -6164,55 +6165,55 @@
         </is>
       </c>
       <c r="W52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/artfynd/A 42008-2026 artfynd.xlsx", "A 42008-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/artfynd/A 42009-2026 artfynd.xlsx", "A 42009-2026")</f>
         <v/>
       </c>
       <c r="X52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor/A 42008-2026 karta.png", "A 42008-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor/A 42009-2026 karta.png", "A 42009-2026")</f>
         <v/>
       </c>
       <c r="Y52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor_geotiff/A 42008-2026 georefererad karta.tif", "A 42008-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor_geotiff/A 42009-2026 georefererad karta.tif", "A 42009-2026")</f>
         <v/>
       </c>
       <c r="AA52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomål/A 42008-2026 FSC-klagomål.docx", "A 42008-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomål/A 42009-2026 FSC-klagomål.docx", "A 42009-2026")</f>
         <v/>
       </c>
       <c r="AB52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomålsmail/A 42008-2026 FSC-klagomål mail.docx", "A 42008-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomålsmail/A 42009-2026 FSC-klagomål mail.docx", "A 42009-2026")</f>
         <v/>
       </c>
       <c r="AC52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsyn/A 42008-2026 tillsynsbegäran.docx", "A 42008-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsyn/A 42009-2026 tillsynsbegäran.docx", "A 42009-2026")</f>
         <v/>
       </c>
       <c r="AD52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsynsmail/A 42008-2026 tillsynsbegäran mail.docx", "A 42008-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsynsmail/A 42009-2026 tillsynsbegäran mail.docx", "A 42009-2026")</f>
         <v/>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S 337-2024</t>
+          <t>A 42008-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45328</v>
+        <v>46303</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6225,7 +6226,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>38.5</v>
+        <v>12</v>
       </c>
       <c r="J53" t="n">
         <v>1</v>
@@ -6265,63 +6266,59 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/artfynd/S 337-2024 artfynd.xlsx", "S 337-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/artfynd/A 42008-2026 artfynd.xlsx", "A 42008-2026")</f>
         <v/>
       </c>
       <c r="X53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor/S 337-2024 karta.png", "S 337-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor/A 42008-2026 karta.png", "A 42008-2026")</f>
         <v/>
       </c>
       <c r="Y53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor_geotiff/S 337-2024 georefererad karta.tif", "S 337-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor_geotiff/A 42008-2026 georefererad karta.tif", "A 42008-2026")</f>
         <v/>
       </c>
       <c r="AA53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomål/S 337-2024 FSC-klagomål.docx", "S 337-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomål/A 42008-2026 FSC-klagomål.docx", "A 42008-2026")</f>
         <v/>
       </c>
       <c r="AB53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomålsmail/S 337-2024 FSC-klagomål mail.docx", "S 337-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomålsmail/A 42008-2026 FSC-klagomål mail.docx", "A 42008-2026")</f>
         <v/>
       </c>
       <c r="AC53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsyn/S 337-2024 tillsynsbegäran.docx", "S 337-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsyn/A 42008-2026 tillsynsbegäran.docx", "A 42008-2026")</f>
         <v/>
       </c>
       <c r="AD53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsynsmail/S 337-2024 tillsynsbegäran mail.docx", "S 337-2024")</f>
-        <v/>
-      </c>
-      <c r="AE53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1485/fåglar/S 337-2024 prioriterade fågelarter.docx", "S 337-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsynsmail/A 42008-2026 tillsynsbegäran mail.docx", "A 42008-2026")</f>
         <v/>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 41964-2022</t>
+          <t>S 337-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44830</v>
+        <v>45328</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6334,10 +6331,10 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.6</v>
+        <v>38.5</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -6364,20 +6361,56 @@
         <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U54" t="n">
         <v>0</v>
       </c>
-      <c r="V54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="W54">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/artfynd/S 337-2024 artfynd.xlsx", "S 337-2024")</f>
+        <v/>
+      </c>
+      <c r="X54">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor/S 337-2024 karta.png", "S 337-2024")</f>
+        <v/>
+      </c>
+      <c r="Y54">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/kartor_geotiff/S 337-2024 georefererad karta.tif", "S 337-2024")</f>
+        <v/>
+      </c>
+      <c r="AA54">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomål/S 337-2024 FSC-klagomål.docx", "S 337-2024")</f>
+        <v/>
+      </c>
+      <c r="AB54">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/klagomålsmail/S 337-2024 FSC-klagomål mail.docx", "S 337-2024")</f>
+        <v/>
+      </c>
+      <c r="AC54">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsyn/S 337-2024 tillsynsbegäran.docx", "S 337-2024")</f>
+        <v/>
+      </c>
+      <c r="AD54">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/tillsynsmail/S 337-2024 tillsynsbegäran mail.docx", "S 337-2024")</f>
+        <v/>
+      </c>
+      <c r="AE54">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1485/fåglar/S 337-2024 prioriterade fågelarter.docx", "S 337-2024")</f>
+        <v/>
+      </c>
     </row>
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 3607-2022</t>
+          <t>A 41964-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6391,10 +6424,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44586</v>
+        <v>44830</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6407,7 +6440,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>5.5</v>
+        <v>0.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -6450,7 +6483,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 70494-2021</t>
+          <t>A 3607-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6464,10 +6497,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44536</v>
+        <v>44586</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6480,7 +6513,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.9</v>
+        <v>5.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6523,7 +6556,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 25811-2022</t>
+          <t>A 70494-2021</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6537,10 +6570,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44733</v>
+        <v>44536</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6553,7 +6586,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>4.2</v>
+        <v>0.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6596,7 +6629,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 1861-2022</t>
+          <t>A 25811-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6606,14 +6639,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44574</v>
+        <v>44733</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6626,7 +6659,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.1</v>
+        <v>4.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6669,7 +6702,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 67260-2021</t>
+          <t>A 1861-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6679,14 +6712,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44523</v>
+        <v>44574</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6699,7 +6732,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.7</v>
+        <v>0.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6742,7 +6775,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 58933-2021</t>
+          <t>A 67260-2021</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6756,10 +6789,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44489</v>
+        <v>44523</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6772,7 +6805,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6815,7 +6848,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 3562-2022</t>
+          <t>A 58933-2021</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6829,10 +6862,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44585</v>
+        <v>44489</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6845,7 +6878,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6888,7 +6921,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 25807-2022</t>
+          <t>A 3562-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6902,10 +6935,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44733</v>
+        <v>44585</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6918,7 +6951,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>6.8</v>
+        <v>2.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6961,7 +6994,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 6063-2022</t>
+          <t>A 25807-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6975,10 +7008,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44599</v>
+        <v>44733</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6991,7 +7024,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>14.4</v>
+        <v>6.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -7034,7 +7067,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 1156-2022</t>
+          <t>A 6063-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7048,10 +7081,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44572</v>
+        <v>44599</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7063,13 +7096,8 @@
           <t>UDDEVALLA</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>4.5</v>
+        <v>14.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -7112,7 +7140,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 68702-2021</t>
+          <t>A 1156-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7126,10 +7154,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44529</v>
+        <v>44572</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7141,8 +7169,13 @@
           <t>UDDEVALLA</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -7185,7 +7218,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 8899-2022</t>
+          <t>A 68702-2021</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7199,10 +7232,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44614</v>
+        <v>44529</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7215,7 +7248,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -7258,7 +7291,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 56650-2021</t>
+          <t>A 8899-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7272,10 +7305,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44480</v>
+        <v>44614</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7288,7 +7321,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7331,7 +7364,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 61904-2021</t>
+          <t>A 56650-2021</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7345,10 +7378,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44502</v>
+        <v>44480</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7361,7 +7394,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7404,7 +7437,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 65457-2021</t>
+          <t>A 61904-2021</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7418,10 +7451,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44516</v>
+        <v>44502</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7434,7 +7467,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7477,7 +7510,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 59857-2021</t>
+          <t>A 65457-2021</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7491,10 +7524,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44494</v>
+        <v>44516</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7507,7 +7540,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.5</v>
+        <v>8.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7550,7 +7583,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 38557-2022</t>
+          <t>A 59857-2021</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7564,10 +7597,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44813</v>
+        <v>44494</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7580,7 +7613,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7623,7 +7656,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 8893-2024</t>
+          <t>A 38557-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7633,14 +7666,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45355</v>
+        <v>44813</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7652,13 +7685,8 @@
           <t>UDDEVALLA</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7701,7 +7729,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 240-2023</t>
+          <t>A 8893-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7711,14 +7739,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44928</v>
+        <v>45355</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7730,8 +7758,13 @@
           <t>UDDEVALLA</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7774,7 +7807,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 26916-2023</t>
+          <t>A 240-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7788,10 +7821,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45093</v>
+        <v>44928</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7804,7 +7837,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7847,7 +7880,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 40121-2024</t>
+          <t>A 26916-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7861,10 +7894,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45554</v>
+        <v>45093</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7877,7 +7910,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7920,7 +7953,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 11788-2024</t>
+          <t>A 40121-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7934,10 +7967,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45374</v>
+        <v>45554</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7950,7 +7983,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>8.5</v>
+        <v>1.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7993,7 +8026,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 23887-2024</t>
+          <t>A 11788-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8007,10 +8040,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45455</v>
+        <v>45374</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8023,7 +8056,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.6</v>
+        <v>8.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -8066,7 +8099,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 21581-2023</t>
+          <t>A 23887-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8080,10 +8113,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45063</v>
+        <v>45455</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8096,7 +8129,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -8139,7 +8172,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 18806-2024</t>
+          <t>A 21581-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8153,10 +8186,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45426</v>
+        <v>45063</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8169,7 +8202,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -8212,7 +8245,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 15634-2023</t>
+          <t>A 18806-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8226,10 +8259,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45021</v>
+        <v>45426</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8242,7 +8275,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8285,7 +8318,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 20137-2025</t>
+          <t>A 15634-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8299,10 +8332,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45772</v>
+        <v>45021</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8315,7 +8348,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8358,7 +8391,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 23462-2024</t>
+          <t>A 20137-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8372,10 +8405,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45453</v>
+        <v>45772</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8388,7 +8421,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8431,7 +8464,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 59474-2022</t>
+          <t>A 23462-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8445,10 +8478,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44900</v>
+        <v>45453</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8460,13 +8493,8 @@
           <t>UDDEVALLA</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8509,7 +8537,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 25469-2024</t>
+          <t>A 59474-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8523,10 +8551,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45463</v>
+        <v>44900</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8538,8 +8566,13 @@
           <t>UDDEVALLA</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8582,7 +8615,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 10585-2024</t>
+          <t>A 25469-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8596,10 +8629,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45366</v>
+        <v>45463</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8612,7 +8645,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.9</v>
+        <v>0.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8655,7 +8688,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 43276-2022</t>
+          <t>A 10585-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8669,10 +8702,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44834</v>
+        <v>45366</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8685,7 +8718,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.6</v>
+        <v>3.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8728,7 +8761,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 39559-2023</t>
+          <t>A 43276-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8742,10 +8775,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45167</v>
+        <v>44834</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8758,7 +8791,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8801,7 +8834,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 63397-2021</t>
+          <t>A 39559-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8815,10 +8848,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44508</v>
+        <v>45167</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8874,7 +8907,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 34555-2022</t>
+          <t>A 63397-2021</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8888,10 +8921,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44794</v>
+        <v>44508</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8904,7 +8937,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>5.9</v>
+        <v>1.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8947,7 +8980,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 1331-2025</t>
+          <t>A 34555-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8961,10 +8994,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45667</v>
+        <v>44794</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8977,7 +9010,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3.1</v>
+        <v>5.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -9020,7 +9053,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 59144-2023</t>
+          <t>A 1331-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9034,10 +9067,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45251</v>
+        <v>45667</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9049,13 +9082,8 @@
           <t>UDDEVALLA</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -9098,7 +9126,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 48132-2023</t>
+          <t>A 59144-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9112,10 +9140,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45205</v>
+        <v>45251</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9127,8 +9155,13 @@
           <t>UDDEVALLA</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -9171,7 +9204,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 7770-2023</t>
+          <t>A 48132-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9185,10 +9218,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44973</v>
+        <v>45205</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9201,7 +9234,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -9244,7 +9277,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 45902-2024</t>
+          <t>A 7770-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9258,10 +9291,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45580</v>
+        <v>44973</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9274,7 +9307,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9317,7 +9350,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 5557-2023</t>
+          <t>A 45902-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9331,10 +9364,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44960</v>
+        <v>45580</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9347,7 +9380,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>5.2</v>
+        <v>3.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9390,7 +9423,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 2115-2025</t>
+          <t>A 5557-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9400,14 +9433,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45672</v>
+        <v>44960</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9420,7 +9453,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>14.1</v>
+        <v>5.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9463,7 +9496,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 23395-2023</t>
+          <t>A 2115-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9473,14 +9506,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45076</v>
+        <v>45672</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9493,7 +9526,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>12.2</v>
+        <v>14.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9536,7 +9569,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 73437-2021</t>
+          <t>A 23395-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9550,10 +9583,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44551</v>
+        <v>45076</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9566,7 +9599,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>8.1</v>
+        <v>12.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9609,7 +9642,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 69198-2021</t>
+          <t>A 73437-2021</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9623,10 +9656,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44531</v>
+        <v>44551</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9639,7 +9672,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.7</v>
+        <v>8.1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9682,7 +9715,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 19849-2025</t>
+          <t>A 69198-2021</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9696,10 +9729,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45771</v>
+        <v>44531</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9712,7 +9745,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>5</v>
+        <v>0.7</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9755,7 +9788,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 39084-2022</t>
+          <t>A 19849-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9769,10 +9802,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44817</v>
+        <v>45771</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9785,7 +9818,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9828,7 +9861,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 43426-2024</t>
+          <t>A 39084-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9842,10 +9875,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45568</v>
+        <v>44817</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9858,7 +9891,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>5.2</v>
+        <v>2.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9901,7 +9934,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 58625-2024</t>
+          <t>A 43426-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9911,14 +9944,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45635</v>
+        <v>45568</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9931,7 +9964,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>14.9</v>
+        <v>5.2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9974,7 +10007,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 33293-2025</t>
+          <t>A 58625-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9984,14 +10017,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45840</v>
+        <v>45635</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10004,7 +10037,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.3</v>
+        <v>14.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -10047,7 +10080,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 1956-2023</t>
+          <t>A 33293-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10061,10 +10094,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44924</v>
+        <v>45840</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10077,7 +10110,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -10120,7 +10153,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 6364-2025</t>
+          <t>A 1956-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10134,10 +10167,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45699</v>
+        <v>44924</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10150,7 +10183,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>5.8</v>
+        <v>2.4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -10193,7 +10226,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 4037-2025</t>
+          <t>A 6364-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10207,10 +10240,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45684</v>
+        <v>45699</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10223,7 +10256,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>4</v>
+        <v>5.8</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -10266,7 +10299,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 6887-2023</t>
+          <t>A 4037-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10280,10 +10313,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44967</v>
+        <v>45684</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10296,7 +10329,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10339,7 +10372,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 36236-2023</t>
+          <t>A 6887-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10353,10 +10386,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45150</v>
+        <v>44967</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10369,7 +10402,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10412,7 +10445,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 29642-2024</t>
+          <t>A 36236-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10426,10 +10459,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45484</v>
+        <v>45150</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10442,7 +10475,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.9</v>
+        <v>5.2</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10485,7 +10518,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 33761-2023</t>
+          <t>A 29642-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10499,10 +10532,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45133</v>
+        <v>45484</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10515,7 +10548,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10558,7 +10591,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 40331-2025</t>
+          <t>A 33761-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10572,10 +10605,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45895</v>
+        <v>45133</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10588,7 +10621,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10631,7 +10664,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 44325-2023</t>
+          <t>A 40331-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10645,10 +10678,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45188</v>
+        <v>45895</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10661,7 +10694,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10704,7 +10737,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 59139-2023</t>
+          <t>A 44325-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10718,10 +10751,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45251</v>
+        <v>45188</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10733,13 +10766,8 @@
           <t>UDDEVALLA</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10782,7 +10810,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 49718-2024</t>
+          <t>A 59139-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10796,10 +10824,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45596</v>
+        <v>45251</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10811,8 +10839,13 @@
           <t>UDDEVALLA</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I115" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10855,7 +10888,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 18811-2024</t>
+          <t>A 49718-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10869,10 +10902,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45426</v>
+        <v>45596</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10885,7 +10918,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10928,7 +10961,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 41576-2025</t>
+          <t>A 18811-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10942,10 +10975,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45901</v>
+        <v>45426</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10958,7 +10991,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -11001,7 +11034,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 27524-2023</t>
+          <t>A 41576-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -11015,10 +11048,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45097</v>
+        <v>45901</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11031,7 +11064,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -11074,7 +11107,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 17139-2023</t>
+          <t>A 27524-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -11088,10 +11121,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45034</v>
+        <v>45097</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11104,7 +11137,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>5.8</v>
+        <v>0.7</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -11147,7 +11180,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 17240-2023</t>
+          <t>A 17139-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -11161,10 +11194,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45035</v>
+        <v>45034</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11177,7 +11210,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.7</v>
+        <v>5.8</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -11220,7 +11253,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 17242-2023</t>
+          <t>A 17240-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11237,7 +11270,7 @@
         <v>45035</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11250,7 +11283,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -11293,7 +11326,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 19981-2025</t>
+          <t>A 17242-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11307,10 +11340,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45771</v>
+        <v>45035</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11323,7 +11356,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>4.9</v>
+        <v>0.3</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11366,7 +11399,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 27869-2024</t>
+          <t>A 19981-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11380,10 +11413,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45475</v>
+        <v>45771</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11396,7 +11429,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1</v>
+        <v>4.9</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11439,7 +11472,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 13527-2024</t>
+          <t>A 27869-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11453,10 +11486,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45387</v>
+        <v>45475</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11469,7 +11502,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11512,7 +11545,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 1346-2022</t>
+          <t>A 13527-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11526,10 +11559,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44572</v>
+        <v>45387</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11542,7 +11575,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11585,7 +11618,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 32846-2023</t>
+          <t>A 1346-2022</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11599,10 +11632,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45112</v>
+        <v>44572</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11615,7 +11648,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>4.9</v>
+        <v>0.9</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11658,7 +11691,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 50023-2023</t>
+          <t>A 32846-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11672,10 +11705,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45215</v>
+        <v>45112</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11688,7 +11721,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2.8</v>
+        <v>4.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11731,7 +11764,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 58958-2021</t>
+          <t>A 50023-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11741,14 +11774,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44489</v>
+        <v>45215</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11761,7 +11794,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.1</v>
+        <v>2.8</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11804,7 +11837,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 59513-2024</t>
+          <t>A 58958-2021</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11814,14 +11847,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45638</v>
+        <v>44489</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11834,7 +11867,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11877,7 +11910,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 49145-2024</t>
+          <t>A 59513-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11891,10 +11924,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45594</v>
+        <v>45638</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11907,7 +11940,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11950,7 +11983,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 33092-2024</t>
+          <t>A 49145-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11964,10 +11997,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45517</v>
+        <v>45594</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11980,7 +12013,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>3.6</v>
+        <v>0.7</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -12023,7 +12056,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 39621-2023</t>
+          <t>A 33092-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -12037,10 +12070,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45167</v>
+        <v>45517</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12053,7 +12086,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -12096,7 +12129,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 60819-2024</t>
+          <t>A 39621-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -12110,10 +12143,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45644</v>
+        <v>45167</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12126,7 +12159,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -12169,7 +12202,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 21102-2025</t>
+          <t>A 60819-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -12183,10 +12216,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45777</v>
+        <v>45644</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12199,7 +12232,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>12.9</v>
+        <v>1.1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -12242,7 +12275,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 43552-2025</t>
+          <t>A 21102-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -12256,10 +12289,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45911</v>
+        <v>45777</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12272,7 +12305,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2.9</v>
+        <v>12.9</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -12315,7 +12348,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 27529-2023</t>
+          <t>A 43552-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12329,10 +12362,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45097</v>
+        <v>45911</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12345,7 +12378,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>9.699999999999999</v>
+        <v>2.9</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12388,7 +12421,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 44086-2025</t>
+          <t>A 27529-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12402,10 +12435,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45914</v>
+        <v>45097</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12418,7 +12451,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12461,7 +12494,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 44137-2025</t>
+          <t>A 44086-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12478,7 +12511,7 @@
         <v>45914</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12491,7 +12524,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12534,7 +12567,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 6650-2025</t>
+          <t>A 44137-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12548,10 +12581,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45700</v>
+        <v>45914</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12564,7 +12597,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12607,7 +12640,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 19982-2025</t>
+          <t>A 6650-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12621,10 +12654,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45771</v>
+        <v>45700</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12637,7 +12670,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12680,7 +12713,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 10426-2023</t>
+          <t>A 19982-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12694,10 +12727,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44981</v>
+        <v>45771</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12709,13 +12742,8 @@
           <t>UDDEVALLA</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12758,7 +12786,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 19980-2025</t>
+          <t>A 10426-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12772,10 +12800,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45771</v>
+        <v>44981</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12787,8 +12815,13 @@
           <t>UDDEVALLA</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>5.4</v>
+        <v>2</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12831,7 +12864,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 50879-2024</t>
+          <t>A 19980-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12845,10 +12878,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45602</v>
+        <v>45771</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12861,7 +12894,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>2.5</v>
+        <v>5.4</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12904,7 +12937,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 45157-2025</t>
+          <t>A 50879-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12918,10 +12951,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45919</v>
+        <v>45602</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12934,7 +12967,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>19.4</v>
+        <v>2.5</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12977,7 +13010,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 45567-2025</t>
+          <t>A 45157-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12991,10 +13024,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45922</v>
+        <v>45919</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13007,7 +13040,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>3.1</v>
+        <v>19.4</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -13050,7 +13083,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 39121-2024</t>
+          <t>A 45567-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -13064,10 +13097,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45548</v>
+        <v>45922</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13080,7 +13113,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -13123,7 +13156,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 7726-2024</t>
+          <t>A 39121-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -13137,10 +13170,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45349</v>
+        <v>45548</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13153,7 +13186,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -13196,7 +13229,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 46304-2025</t>
+          <t>A 7726-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -13210,10 +13243,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45925</v>
+        <v>45349</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13226,7 +13259,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -13269,7 +13302,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 14066-2025</t>
+          <t>A 46304-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -13283,10 +13316,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45740</v>
+        <v>45925</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13299,7 +13332,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>7.5</v>
+        <v>1.1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -13342,7 +13375,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 41511-2024</t>
+          <t>A 14066-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13356,10 +13389,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45560</v>
+        <v>45740</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13372,7 +13405,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.3</v>
+        <v>7.5</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -13415,7 +13448,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 3077-2022</t>
+          <t>A 41511-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13429,10 +13462,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44582</v>
+        <v>45560</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13444,13 +13477,8 @@
           <t>UDDEVALLA</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I151" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -13493,7 +13521,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 45149-2024</t>
+          <t>A 3077-2022</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13507,10 +13535,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45575</v>
+        <v>44582</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13522,8 +13550,13 @@
           <t>UDDEVALLA</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I152" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13566,7 +13599,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 2306-2022</t>
+          <t>A 45149-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13576,14 +13609,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44578</v>
+        <v>45575</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13596,7 +13629,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13639,7 +13672,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 40027-2024</t>
+          <t>A 2306-2022</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13649,14 +13682,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45553</v>
+        <v>44578</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13669,7 +13702,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13712,7 +13745,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 14021-2025</t>
+          <t>A 40027-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13726,10 +13759,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45740</v>
+        <v>45553</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13742,7 +13775,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.4</v>
+        <v>2.3</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13785,7 +13818,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 46480-2023</t>
+          <t>A 14021-2025</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13799,10 +13832,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45197</v>
+        <v>45740</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13815,7 +13848,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13858,7 +13891,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 47083-2025</t>
+          <t>A 46480-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13872,10 +13905,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45929</v>
+        <v>45197</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13888,7 +13921,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13931,7 +13964,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 47103-2025</t>
+          <t>A 47083-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13948,7 +13981,7 @@
         <v>45929</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13961,7 +13994,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.4</v>
+        <v>2.6</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -14004,7 +14037,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 36562-2024</t>
+          <t>A 47103-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -14018,10 +14051,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45537</v>
+        <v>45929</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14034,7 +14067,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>3.6</v>
+        <v>0.4</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -14077,7 +14110,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 4639-2022</t>
+          <t>A 36562-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -14087,14 +14120,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>44592</v>
+        <v>45537</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14107,7 +14140,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -14150,7 +14183,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 58385-2024</t>
+          <t>A 4639-2022</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -14160,14 +14193,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45633</v>
+        <v>44592</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14180,7 +14213,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -14223,7 +14256,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 47603-2025</t>
+          <t>A 58385-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -14237,10 +14270,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45931</v>
+        <v>45633</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14253,7 +14286,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -14296,7 +14329,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 6875-2022</t>
+          <t>A 47603-2025</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -14310,10 +14343,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44602</v>
+        <v>45931</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14326,7 +14359,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>9.6</v>
+        <v>0.8</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -14369,7 +14402,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 61629-2024</t>
+          <t>A 6875-2022</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -14383,10 +14416,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45646</v>
+        <v>44602</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14399,7 +14432,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>0.6</v>
+        <v>9.6</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -14442,7 +14475,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 60241-2024</t>
+          <t>A 61629-2024</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -14452,14 +14485,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45642</v>
+        <v>45646</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14472,7 +14505,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -14515,7 +14548,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 62055-2024</t>
+          <t>A 60241-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14525,14 +14558,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45656</v>
+        <v>45642</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14544,13 +14577,8 @@
           <t>UDDEVALLA</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I166" t="n">
-        <v>3.6</v>
+        <v>1.6</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -14593,7 +14621,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 26847-2024</t>
+          <t>A 62055-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14607,10 +14635,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45470</v>
+        <v>45656</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14628,7 +14656,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14671,7 +14699,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 62037-2024</t>
+          <t>A 26847-2024</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14685,10 +14713,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45656</v>
+        <v>45470</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14706,7 +14734,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14749,7 +14777,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 62075-2024</t>
+          <t>A 62037-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14766,7 +14794,7 @@
         <v>45656</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14784,7 +14812,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14827,7 +14855,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 21332-2024</t>
+          <t>A 62075-2024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14841,10 +14869,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45440</v>
+        <v>45656</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14856,8 +14884,13 @@
           <t>UDDEVALLA</t>
         </is>
       </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I170" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14900,7 +14933,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 62073-2024</t>
+          <t>A 21332-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14914,10 +14947,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45656</v>
+        <v>45440</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14929,13 +14962,8 @@
           <t>UDDEVALLA</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I171" t="n">
-        <v>0.9</v>
+        <v>3.3</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14978,7 +15006,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 62074-2024</t>
+          <t>A 62073-2024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14995,7 +15023,7 @@
         <v>45656</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15013,7 +15041,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -15056,7 +15084,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 62077-2024</t>
+          <t>A 62074-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -15073,7 +15101,7 @@
         <v>45656</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15091,7 +15119,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -15134,7 +15162,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 52889-2023</t>
+          <t>A 62077-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -15148,10 +15176,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45226</v>
+        <v>45656</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15163,8 +15191,13 @@
           <t>UDDEVALLA</t>
         </is>
       </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I174" t="n">
-        <v>6</v>
+        <v>2.7</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -15207,7 +15240,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 39355-2024</t>
+          <t>A 52889-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -15221,10 +15254,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45551</v>
+        <v>45226</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15237,7 +15270,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>3.7</v>
+        <v>6</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -15280,7 +15313,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 10684-2022</t>
+          <t>A 39355-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -15294,10 +15327,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44624</v>
+        <v>45551</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15310,7 +15343,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -15353,7 +15386,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 10900-2025</t>
+          <t>A 10684-2022</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -15367,10 +15400,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45722</v>
+        <v>44624</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15383,7 +15416,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -15426,7 +15459,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 23895-2024</t>
+          <t>A 10900-2025</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -15440,10 +15473,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45455</v>
+        <v>45722</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15456,7 +15489,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -15499,7 +15532,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 14604-2022</t>
+          <t>A 23895-2024</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15513,10 +15546,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44655</v>
+        <v>45455</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15529,7 +15562,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -15572,7 +15605,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 49721-2025</t>
+          <t>A 14604-2022</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15586,10 +15619,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45939</v>
+        <v>44655</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15602,7 +15635,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>8</v>
+        <v>1.6</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15645,7 +15678,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 24081-2024</t>
+          <t>A 49721-2025</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15659,10 +15692,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45456</v>
+        <v>45939</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15675,7 +15708,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.7</v>
+        <v>8</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15718,7 +15751,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 50586-2025</t>
+          <t>A 24081-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15732,10 +15765,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45945</v>
+        <v>45456</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15748,7 +15781,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>11</v>
+        <v>1.7</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15791,7 +15824,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 50609-2025</t>
+          <t>A 50586-2025</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15808,7 +15841,7 @@
         <v>45945</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15821,7 +15854,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15864,7 +15897,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 659-2025</t>
+          <t>A 50609-2025</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15878,10 +15911,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45664</v>
+        <v>45945</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15894,7 +15927,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15937,7 +15970,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 50611-2025</t>
+          <t>A 659-2025</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15951,10 +15984,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45945</v>
+        <v>45664</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15967,7 +16000,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>5.1</v>
+        <v>3.5</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -16010,7 +16043,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 50580-2025</t>
+          <t>A 50611-2025</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -16027,7 +16060,7 @@
         <v>45945</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16040,7 +16073,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -16083,7 +16116,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 15716-2025</t>
+          <t>A 50580-2025</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -16097,10 +16130,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45748</v>
+        <v>45945</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16113,7 +16146,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.6</v>
+        <v>3.6</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -16156,7 +16189,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 50617-2025</t>
+          <t>A 15716-2025</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -16170,10 +16203,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45945</v>
+        <v>45748</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16186,7 +16219,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -16229,7 +16262,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 11076-2025</t>
+          <t>A 50617-2025</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -16243,10 +16276,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45723</v>
+        <v>45945</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16259,7 +16292,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -16302,7 +16335,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 51747-2025</t>
+          <t>A 11076-2025</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -16312,14 +16345,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45950</v>
+        <v>45723</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16332,7 +16365,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -16392,7 +16425,7 @@
         <v>45940</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16465,7 +16498,7 @@
         <v>44634</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16538,7 +16571,7 @@
         <v>45255</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16611,7 +16644,7 @@
         <v>44956</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16684,7 +16717,7 @@
         <v>44991</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16757,7 +16790,7 @@
         <v>45826</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16830,7 +16863,7 @@
         <v>45826</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16903,7 +16936,7 @@
         <v>45826</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16976,7 +17009,7 @@
         <v>45826</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17049,7 +17082,7 @@
         <v>45183</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17122,7 +17155,7 @@
         <v>45572</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17195,7 +17228,7 @@
         <v>45758</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17268,7 +17301,7 @@
         <v>45631</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17341,7 +17374,7 @@
         <v>44733</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17414,7 +17447,7 @@
         <v>45162</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17487,7 +17520,7 @@
         <v>44715</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17560,7 +17593,7 @@
         <v>45239</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17633,7 +17666,7 @@
         <v>44820</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17706,7 +17739,7 @@
         <v>45965</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17779,7 +17812,7 @@
         <v>44817</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17852,7 +17885,7 @@
         <v>44998</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17925,7 +17958,7 @@
         <v>45843</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17998,7 +18031,7 @@
         <v>45972</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18071,7 +18104,7 @@
         <v>45121</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18144,7 +18177,7 @@
         <v>45314</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18217,7 +18250,7 @@
         <v>45484</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18290,7 +18323,7 @@
         <v>44973</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18363,7 +18396,7 @@
         <v>45588</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18436,7 +18469,7 @@
         <v>45455</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18509,7 +18542,7 @@
         <v>45257</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18582,7 +18615,7 @@
         <v>45975</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18655,7 +18688,7 @@
         <v>45365</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18728,7 +18761,7 @@
         <v>44823</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18801,7 +18834,7 @@
         <v>45771</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18874,7 +18907,7 @@
         <v>44509</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18947,7 +18980,7 @@
         <v>45168</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19020,7 +19053,7 @@
         <v>45212</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19093,7 +19126,7 @@
         <v>45882</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19166,7 +19199,7 @@
         <v>45764</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19239,7 +19272,7 @@
         <v>45882</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19312,7 +19345,7 @@
         <v>45071</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19385,7 +19418,7 @@
         <v>45672</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19458,7 +19491,7 @@
         <v>45986</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19531,7 +19564,7 @@
         <v>45985</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19604,7 +19637,7 @@
         <v>45238</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19677,7 +19710,7 @@
         <v>46106</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19750,7 +19783,7 @@
         <v>45754</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19823,7 +19856,7 @@
         <v>45754</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19896,7 +19929,7 @@
         <v>46113</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19969,7 +20002,7 @@
         <v>45992</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20042,7 +20075,7 @@
         <v>44984</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20115,7 +20148,7 @@
         <v>45551</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20188,7 +20221,7 @@
         <v>44551</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20261,7 +20294,7 @@
         <v>46119</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20334,7 +20367,7 @@
         <v>46120</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20407,7 +20440,7 @@
         <v>46121</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20480,7 +20513,7 @@
         <v>46125</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20558,7 +20591,7 @@
         <v>46125</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20631,7 +20664,7 @@
         <v>45999</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20704,7 +20737,7 @@
         <v>45994</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20777,7 +20810,7 @@
         <v>44683</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20850,7 +20883,7 @@
         <v>46128</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20923,7 +20956,7 @@
         <v>46128</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20996,7 +21029,7 @@
         <v>45093</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21069,7 +21102,7 @@
         <v>45302</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21142,7 +21175,7 @@
         <v>46007</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21215,7 +21248,7 @@
         <v>44536</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21288,7 +21321,7 @@
         <v>45141</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21361,7 +21394,7 @@
         <v>45889</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21434,7 +21467,7 @@
         <v>45656</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21512,7 +21545,7 @@
         <v>45907</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21585,7 +21618,7 @@
         <v>46026</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21658,7 +21691,7 @@
         <v>45365</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21731,7 +21764,7 @@
         <v>46027</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21804,7 +21837,7 @@
         <v>45553</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21877,7 +21910,7 @@
         <v>45901</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21950,7 +21983,7 @@
         <v>45919</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22023,7 +22056,7 @@
         <v>46119</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22096,7 +22129,7 @@
         <v>44959</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22169,7 +22202,7 @@
         <v>46139</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22242,7 +22275,7 @@
         <v>45028</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22315,7 +22348,7 @@
         <v>45279</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22388,7 +22421,7 @@
         <v>45583</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22461,7 +22494,7 @@
         <v>46036</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22534,7 +22567,7 @@
         <v>46036</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22607,7 +22640,7 @@
         <v>46036</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22680,7 +22713,7 @@
         <v>46036</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22753,7 +22786,7 @@
         <v>45237</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22826,7 +22859,7 @@
         <v>46044</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22899,7 +22932,7 @@
         <v>45089</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22972,7 +23005,7 @@
         <v>45554</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23045,7 +23078,7 @@
         <v>45226</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23118,7 +23151,7 @@
         <v>44550</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23191,7 +23224,7 @@
         <v>46062</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23264,7 +23297,7 @@
         <v>46062</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23337,7 +23370,7 @@
         <v>46147</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23415,7 +23448,7 @@
         <v>46071</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23488,7 +23521,7 @@
         <v>44935</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23561,7 +23594,7 @@
         <v>46076</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23634,7 +23667,7 @@
         <v>46083</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23712,7 +23745,7 @@
         <v>45953</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23790,7 +23823,7 @@
         <v>45992</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23868,7 +23901,7 @@
         <v>45971</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23946,7 +23979,7 @@
         <v>45981</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24024,7 +24057,7 @@
         <v>45400</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24102,7 +24135,7 @@
         <v>45540</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24180,7 +24213,7 @@
         <v>46090</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24253,7 +24286,7 @@
         <v>46090</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24326,7 +24359,7 @@
         <v>45309</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24399,7 +24432,7 @@
         <v>46198</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24477,7 +24510,7 @@
         <v>46164</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24550,7 +24583,7 @@
         <v>45915</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24623,7 +24656,7 @@
         <v>45495</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24696,7 +24729,7 @@
         <v>46174</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24769,7 +24802,7 @@
         <v>46177</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24842,7 +24875,7 @@
         <v>46177</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24915,7 +24948,7 @@
         <v>46177</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24988,7 +25021,7 @@
         <v>46178</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25061,7 +25094,7 @@
         <v>46206</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25134,7 +25167,7 @@
         <v>46210</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25212,7 +25245,7 @@
         <v>46210</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25290,7 +25323,7 @@
         <v>46212</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25368,7 +25401,7 @@
         <v>46222</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25446,7 +25479,7 @@
         <v>46266</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25519,7 +25552,7 @@
         <v>46267</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25597,7 +25630,7 @@
         <v>46267</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25670,7 +25703,7 @@
         <v>46267</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25748,7 +25781,7 @@
         <v>46267</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25826,7 +25859,7 @@
         <v>45847</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25899,7 +25932,7 @@
         <v>46288</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25972,7 +26005,7 @@
         <v>46141</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26045,7 +26078,7 @@
         <v>46036</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26118,7 +26151,7 @@
         <v>46293</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26191,7 +26224,7 @@
         <v>46251</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26264,7 +26297,7 @@
         <v>46174</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26337,7 +26370,7 @@
         <v>46211</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26410,7 +26443,7 @@
         <v>45127</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26483,7 +26516,7 @@
         <v>46148</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26556,7 +26589,7 @@
         <v>46302</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26629,7 +26662,7 @@
         <v>46258</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26702,7 +26735,7 @@
         <v>46303</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26775,7 +26808,7 @@
         <v>46303</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26848,7 +26881,7 @@
         <v>45328</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26921,7 +26954,7 @@
         <v>45526</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26994,7 +27027,7 @@
         <v>46129</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>

--- a/Översikt UDDEVALLA.xlsx
+++ b/Översikt UDDEVALLA.xlsx
@@ -601,7 +601,7 @@
         <v>46266</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45656</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>45432</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         <v>45677</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>45656</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>45107</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>45728</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>45317</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>45656</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>45751</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>46253</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>45317</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>45922</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>45740</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>45799</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>45656</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>45990</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>46174</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>45754</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>44825</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>45288</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>45352</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>45513</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>45950</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>45981</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>46124</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>45513</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>45317</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>46273</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>46241</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>45653</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>46253</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4178,7 +4178,7 @@
         <v>44733</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>44627</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>45107</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         <v>44928</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>45076</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         <v>45135</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>44930</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>45791</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         <v>45071</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>45832</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>45303</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>45237</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5459,7 +5459,7 @@
         <v>45600</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>45348</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>46036</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         <v>46071</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5888,7 +5888,7 @@
         <v>46292</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5998,7 +5998,7 @@
         <v>46251</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6108,7 +6108,7 @@
         <v>46303</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         <v>46303</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>45328</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6427,7 +6427,7 @@
         <v>44830</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         <v>44586</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         <v>44536</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>44733</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         <v>44574</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>44523</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         <v>44489</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         <v>44585</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         <v>44733</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7084,7 +7084,7 @@
         <v>44599</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
         <v>44572</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         <v>44529</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>44614</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         <v>44480</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7454,7 +7454,7 @@
         <v>44502</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>44516</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         <v>44494</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>44813</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7746,7 +7746,7 @@
         <v>45355</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7824,7 +7824,7 @@
         <v>44928</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>45093</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7970,7 +7970,7 @@
         <v>45554</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>45374</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8116,7 +8116,7 @@
         <v>45455</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8189,7 +8189,7 @@
         <v>45063</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         <v>45426</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>45021</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8408,7 +8408,7 @@
         <v>45772</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8481,7 +8481,7 @@
         <v>45453</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8554,7 +8554,7 @@
         <v>44900</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8632,7 +8632,7 @@
         <v>45463</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         <v>45366</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
         <v>44834</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         <v>45167</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8924,7 +8924,7 @@
         <v>44508</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         <v>44794</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9070,7 +9070,7 @@
         <v>45667</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9143,7 +9143,7 @@
         <v>45251</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9221,7 +9221,7 @@
         <v>45205</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>44973</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>45580</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         <v>44960</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9513,7 +9513,7 @@
         <v>45672</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>45076</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>44551</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9732,7 +9732,7 @@
         <v>44531</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>45771</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
         <v>44817</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         <v>45568</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>45635</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10097,7 +10097,7 @@
         <v>45840</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>44924</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10243,7 +10243,7 @@
         <v>45699</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>45684</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>44967</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>45150</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10535,7 +10535,7 @@
         <v>45484</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10608,7 +10608,7 @@
         <v>45133</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10681,7 +10681,7 @@
         <v>45895</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>45188</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>45251</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10905,7 +10905,7 @@
         <v>45596</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>45426</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>45901</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11124,7 +11124,7 @@
         <v>45097</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11197,7 +11197,7 @@
         <v>45034</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11270,7 +11270,7 @@
         <v>45035</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>45035</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>45771</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11489,7 +11489,7 @@
         <v>45475</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11562,7 +11562,7 @@
         <v>45387</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>44572</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11708,7 +11708,7 @@
         <v>45112</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11781,7 +11781,7 @@
         <v>45215</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11854,7 +11854,7 @@
         <v>44489</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         <v>45638</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
         <v>45594</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12073,7 +12073,7 @@
         <v>45517</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12146,7 +12146,7 @@
         <v>45167</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12219,7 +12219,7 @@
         <v>45644</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>45777</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12365,7 +12365,7 @@
         <v>45911</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
         <v>45097</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>45914</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>45914</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12657,7 +12657,7 @@
         <v>45700</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12730,7 +12730,7 @@
         <v>45771</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12803,7 +12803,7 @@
         <v>44981</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12881,7 +12881,7 @@
         <v>45771</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12954,7 +12954,7 @@
         <v>45602</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13027,7 +13027,7 @@
         <v>45919</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13100,7 +13100,7 @@
         <v>45922</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13173,7 +13173,7 @@
         <v>45548</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
         <v>45349</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13319,7 +13319,7 @@
         <v>45925</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13392,7 +13392,7 @@
         <v>45740</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13465,7 +13465,7 @@
         <v>45560</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13538,7 +13538,7 @@
         <v>44582</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13616,7 +13616,7 @@
         <v>45575</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
         <v>44578</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13762,7 +13762,7 @@
         <v>45553</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13835,7 +13835,7 @@
         <v>45740</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13908,7 +13908,7 @@
         <v>45197</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13981,7 +13981,7 @@
         <v>45929</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14054,7 +14054,7 @@
         <v>45929</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14127,7 +14127,7 @@
         <v>45537</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14200,7 +14200,7 @@
         <v>44592</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14273,7 +14273,7 @@
         <v>45633</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14346,7 +14346,7 @@
         <v>45931</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14419,7 +14419,7 @@
         <v>44602</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14492,7 +14492,7 @@
         <v>45646</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14565,7 +14565,7 @@
         <v>45642</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14638,7 +14638,7 @@
         <v>45656</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14716,7 +14716,7 @@
         <v>45470</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>45656</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14872,7 +14872,7 @@
         <v>45656</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14950,7 +14950,7 @@
         <v>45440</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>45656</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15101,7 +15101,7 @@
         <v>45656</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15179,7 +15179,7 @@
         <v>45656</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15257,7 +15257,7 @@
         <v>45226</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15330,7 +15330,7 @@
         <v>45551</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15403,7 +15403,7 @@
         <v>44624</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15476,7 +15476,7 @@
         <v>45722</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15549,7 +15549,7 @@
         <v>45455</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15622,7 +15622,7 @@
         <v>44655</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15695,7 +15695,7 @@
         <v>45939</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15768,7 +15768,7 @@
         <v>45456</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15841,7 +15841,7 @@
         <v>45945</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15914,7 +15914,7 @@
         <v>45945</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15987,7 +15987,7 @@
         <v>45664</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16060,7 +16060,7 @@
         <v>45945</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16133,7 +16133,7 @@
         <v>45945</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16206,7 +16206,7 @@
         <v>45748</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16279,7 +16279,7 @@
         <v>45945</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16352,7 +16352,7 @@
         <v>45723</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16425,7 +16425,7 @@
         <v>45940</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16498,7 +16498,7 @@
         <v>44634</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16571,7 +16571,7 @@
         <v>45255</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16644,7 +16644,7 @@
         <v>44956</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16717,7 +16717,7 @@
         <v>44991</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16790,7 +16790,7 @@
         <v>45826</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16863,7 +16863,7 @@
         <v>45826</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16936,7 +16936,7 @@
         <v>45826</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17009,7 +17009,7 @@
         <v>45826</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17082,7 +17082,7 @@
         <v>45183</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17155,7 +17155,7 @@
         <v>45572</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17228,7 +17228,7 @@
         <v>45758</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17301,7 +17301,7 @@
         <v>45631</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17374,7 +17374,7 @@
         <v>44733</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         <v>45162</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17520,7 +17520,7 @@
         <v>44715</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17593,7 +17593,7 @@
         <v>45239</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17666,7 +17666,7 @@
         <v>44820</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17739,7 +17739,7 @@
         <v>45965</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17812,7 +17812,7 @@
         <v>44817</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17885,7 +17885,7 @@
         <v>44998</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17958,7 +17958,7 @@
         <v>45843</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18031,7 +18031,7 @@
         <v>45972</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18104,7 +18104,7 @@
         <v>45121</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18177,7 +18177,7 @@
         <v>45314</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18250,7 +18250,7 @@
         <v>45484</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18323,7 +18323,7 @@
         <v>44973</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18396,7 +18396,7 @@
         <v>45588</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18469,7 +18469,7 @@
         <v>45455</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18542,7 +18542,7 @@
         <v>45257</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18615,7 +18615,7 @@
         <v>45975</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18688,7 +18688,7 @@
         <v>45365</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18761,7 +18761,7 @@
         <v>44823</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18834,7 +18834,7 @@
         <v>45771</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18907,7 +18907,7 @@
         <v>44509</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18980,7 +18980,7 @@
         <v>45168</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19053,7 +19053,7 @@
         <v>45212</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19126,7 +19126,7 @@
         <v>45882</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19199,7 +19199,7 @@
         <v>45764</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19272,7 +19272,7 @@
         <v>45882</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19345,7 +19345,7 @@
         <v>45071</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19418,7 +19418,7 @@
         <v>45672</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19491,7 +19491,7 @@
         <v>45986</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19564,7 +19564,7 @@
         <v>45985</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19637,7 +19637,7 @@
         <v>45238</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19710,7 +19710,7 @@
         <v>46106</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19783,7 +19783,7 @@
         <v>45754</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19856,7 +19856,7 @@
         <v>45754</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19929,7 +19929,7 @@
         <v>46113</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20002,7 +20002,7 @@
         <v>45992</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20075,7 +20075,7 @@
         <v>44984</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20148,7 +20148,7 @@
         <v>45551</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20221,7 +20221,7 @@
         <v>44551</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20294,7 +20294,7 @@
         <v>46119</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20367,7 +20367,7 @@
         <v>46120</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20440,7 +20440,7 @@
         <v>46121</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20513,7 +20513,7 @@
         <v>46125</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20591,7 +20591,7 @@
         <v>46125</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20664,7 +20664,7 @@
         <v>45999</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20737,7 +20737,7 @@
         <v>45994</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20810,7 +20810,7 @@
         <v>44683</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20883,7 +20883,7 @@
         <v>46128</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20956,7 +20956,7 @@
         <v>46128</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21029,7 +21029,7 @@
         <v>45093</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21102,7 +21102,7 @@
         <v>45302</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21175,7 +21175,7 @@
         <v>46007</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21248,7 +21248,7 @@
         <v>44536</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21321,7 +21321,7 @@
         <v>45141</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21394,7 +21394,7 @@
         <v>45889</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21467,7 +21467,7 @@
         <v>45656</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21545,7 +21545,7 @@
         <v>45907</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21618,7 +21618,7 @@
         <v>46026</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21691,7 +21691,7 @@
         <v>45365</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21764,7 +21764,7 @@
         <v>46027</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21837,7 +21837,7 @@
         <v>45553</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>45901</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21983,7 +21983,7 @@
         <v>45919</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22056,7 +22056,7 @@
         <v>46119</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22129,7 +22129,7 @@
         <v>44959</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22202,7 +22202,7 @@
         <v>46139</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22275,7 +22275,7 @@
         <v>45028</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22348,7 +22348,7 @@
         <v>45279</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22421,7 +22421,7 @@
         <v>45583</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22494,7 +22494,7 @@
         <v>46036</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22567,7 +22567,7 @@
         <v>46036</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22640,7 +22640,7 @@
         <v>46036</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         <v>46036</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22786,7 +22786,7 @@
         <v>45237</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22859,7 +22859,7 @@
         <v>46044</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22932,7 +22932,7 @@
         <v>45089</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23005,7 +23005,7 @@
         <v>45554</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23078,7 +23078,7 @@
         <v>45226</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23151,7 +23151,7 @@
         <v>44550</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23224,7 +23224,7 @@
         <v>46062</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23297,7 +23297,7 @@
         <v>46062</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23370,7 +23370,7 @@
         <v>46147</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23448,7 +23448,7 @@
         <v>46071</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23521,7 +23521,7 @@
         <v>44935</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23594,7 +23594,7 @@
         <v>46076</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23667,7 +23667,7 @@
         <v>46083</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23745,7 +23745,7 @@
         <v>45953</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23823,7 +23823,7 @@
         <v>45992</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23901,7 +23901,7 @@
         <v>45971</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23979,7 +23979,7 @@
         <v>45981</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24057,7 +24057,7 @@
         <v>45400</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24135,7 +24135,7 @@
         <v>45540</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24213,7 +24213,7 @@
         <v>46090</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24286,7 +24286,7 @@
         <v>46090</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24359,7 +24359,7 @@
         <v>45309</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24432,7 +24432,7 @@
         <v>46198</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24510,7 +24510,7 @@
         <v>46164</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24583,7 +24583,7 @@
         <v>45915</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24656,7 +24656,7 @@
         <v>45495</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24729,7 +24729,7 @@
         <v>46174</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24802,7 +24802,7 @@
         <v>46177</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24875,7 +24875,7 @@
         <v>46177</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24948,7 +24948,7 @@
         <v>46177</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25021,7 +25021,7 @@
         <v>46178</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25094,7 +25094,7 @@
         <v>46206</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25167,7 +25167,7 @@
         <v>46210</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25245,7 +25245,7 @@
         <v>46210</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25323,7 +25323,7 @@
         <v>46212</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25401,7 +25401,7 @@
         <v>46222</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25479,7 +25479,7 @@
         <v>46266</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25552,7 +25552,7 @@
         <v>46267</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25630,7 +25630,7 @@
         <v>46267</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25703,7 +25703,7 @@
         <v>46267</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25781,7 +25781,7 @@
         <v>46267</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25859,7 +25859,7 @@
         <v>45847</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25932,7 +25932,7 @@
         <v>46288</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26005,7 +26005,7 @@
         <v>46141</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26078,7 +26078,7 @@
         <v>46036</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26151,7 +26151,7 @@
         <v>46293</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26224,7 +26224,7 @@
         <v>46251</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26297,7 +26297,7 @@
         <v>46174</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26370,7 +26370,7 @@
         <v>46211</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26443,7 +26443,7 @@
         <v>45127</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26516,7 +26516,7 @@
         <v>46148</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26589,7 +26589,7 @@
         <v>46302</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26662,7 +26662,7 @@
         <v>46258</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26735,7 +26735,7 @@
         <v>46303</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26808,7 +26808,7 @@
         <v>46303</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26881,7 +26881,7 @@
         <v>45328</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26954,7 +26954,7 @@
         <v>45526</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27027,7 +27027,7 @@
         <v>46129</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>

--- a/Översikt UDDEVALLA.xlsx
+++ b/Översikt UDDEVALLA.xlsx
@@ -601,7 +601,7 @@
         <v>46266</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45656</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>45432</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         <v>45677</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>45656</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>45107</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>45317</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>45728</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>45656</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>45751</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>46308</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>46253</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>45922</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>45656</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>45799</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>45990</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>46174</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>45317</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>45740</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2772,7 +2772,7 @@
         <v>45317</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>45288</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>45950</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         <v>45981</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         <v>45513</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>45754</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>44825</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>46124</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>46273</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>45513</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>46241</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>45352</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>46253</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>45653</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>44733</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>44930</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         <v>45071</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>44928</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>44627</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>45237</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>45600</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>45076</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
         <v>46036</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>45303</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         <v>45135</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>45107</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>45348</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>46071</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         <v>46292</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>46251</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6003,7 +6003,7 @@
         <v>46303</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6108,7 +6108,7 @@
         <v>46303</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         <v>45791</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         <v>45832</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6427,7 +6427,7 @@
         <v>45328</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6536,7 +6536,7 @@
         <v>44830</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6609,7 +6609,7 @@
         <v>44586</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>44536</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
         <v>44733</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>44574</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         <v>44523</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
         <v>44489</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
         <v>44585</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         <v>44733</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         <v>44599</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         <v>44529</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         <v>44572</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7417,7 +7417,7 @@
         <v>44614</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>44516</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>44502</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7636,7 +7636,7 @@
         <v>44494</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>45633</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>45602</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>45212</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         <v>45554</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8001,7 +8001,7 @@
         <v>44900</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8079,7 +8079,7 @@
         <v>45093</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8152,7 +8152,7 @@
         <v>45089</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8225,7 +8225,7 @@
         <v>45684</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>44536</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>45183</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8444,7 +8444,7 @@
         <v>45548</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
         <v>44960</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8590,7 +8590,7 @@
         <v>45365</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         <v>45162</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
         <v>45568</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8809,7 +8809,7 @@
         <v>44634</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
         <v>45551</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8955,7 +8955,7 @@
         <v>45596</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9028,7 +9028,7 @@
         <v>45754</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         <v>44817</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9174,7 +9174,7 @@
         <v>45226</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9247,7 +9247,7 @@
         <v>44572</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>45455</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9393,7 +9393,7 @@
         <v>44592</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>45748</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9539,7 +9539,7 @@
         <v>45426</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9612,7 +9612,7 @@
         <v>44981</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9690,7 +9690,7 @@
         <v>44820</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9763,7 +9763,7 @@
         <v>45631</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
         <v>45572</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9909,7 +9909,7 @@
         <v>44991</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9982,7 +9982,7 @@
         <v>45594</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10055,7 +10055,7 @@
         <v>44489</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10128,7 +10128,7 @@
         <v>45772</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10201,7 +10201,7 @@
         <v>44508</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10274,7 +10274,7 @@
         <v>45150</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10347,7 +10347,7 @@
         <v>45882</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10420,7 +10420,7 @@
         <v>45279</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10493,7 +10493,7 @@
         <v>46119</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10566,7 +10566,7 @@
         <v>45656</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10644,7 +10644,7 @@
         <v>45901</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10717,7 +10717,7 @@
         <v>44834</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10790,7 +10790,7 @@
         <v>44551</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10863,7 +10863,7 @@
         <v>45560</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10936,7 +10936,7 @@
         <v>45889</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11009,7 +11009,7 @@
         <v>45699</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>45840</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
         <v>45302</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
         <v>45895</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11301,7 +11301,7 @@
         <v>45583</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>45112</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
         <v>46139</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11520,7 +11520,7 @@
         <v>45226</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11593,7 +11593,7 @@
         <v>44715</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11666,7 +11666,7 @@
         <v>45901</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11739,7 +11739,7 @@
         <v>44550</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11812,7 +11812,7 @@
         <v>45911</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11885,7 +11885,7 @@
         <v>44998</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11958,7 +11958,7 @@
         <v>45914</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12031,7 +12031,7 @@
         <v>45914</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12104,7 +12104,7 @@
         <v>45580</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>45919</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>45922</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12323,7 +12323,7 @@
         <v>45638</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12396,7 +12396,7 @@
         <v>46147</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12474,7 +12474,7 @@
         <v>45771</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12547,7 +12547,7 @@
         <v>45925</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         <v>45929</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12693,7 +12693,7 @@
         <v>45929</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12766,7 +12766,7 @@
         <v>45931</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12839,7 +12839,7 @@
         <v>45656</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12917,7 +12917,7 @@
         <v>45656</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12995,7 +12995,7 @@
         <v>45440</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13068,7 +13068,7 @@
         <v>45656</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13146,7 +13146,7 @@
         <v>45656</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13224,7 +13224,7 @@
         <v>45656</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13302,7 +13302,7 @@
         <v>45646</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13375,7 +13375,7 @@
         <v>45642</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13448,7 +13448,7 @@
         <v>45470</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         <v>45656</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13604,7 +13604,7 @@
         <v>45575</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13677,7 +13677,7 @@
         <v>45553</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13750,7 +13750,7 @@
         <v>45257</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>45939</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13896,7 +13896,7 @@
         <v>45945</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13969,7 +13969,7 @@
         <v>45945</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14042,7 +14042,7 @@
         <v>45945</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14115,7 +14115,7 @@
         <v>45771</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14188,7 +14188,7 @@
         <v>45945</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14261,7 +14261,7 @@
         <v>45945</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>44683</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         <v>45237</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14480,7 +14480,7 @@
         <v>45940</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14553,7 +14553,7 @@
         <v>45667</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>45309</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14699,7 +14699,7 @@
         <v>45965</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14772,7 +14772,7 @@
         <v>45167</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14845,7 +14845,7 @@
         <v>45972</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14918,7 +14918,7 @@
         <v>46198</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14996,7 +14996,7 @@
         <v>45975</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15069,7 +15069,7 @@
         <v>45672</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>45664</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15215,7 +15215,7 @@
         <v>46164</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15288,7 +15288,7 @@
         <v>45985</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15361,7 +15361,7 @@
         <v>45986</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15434,7 +15434,7 @@
         <v>44973</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15507,7 +15507,7 @@
         <v>45764</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15580,7 +15580,7 @@
         <v>45992</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15653,7 +15653,7 @@
         <v>45314</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15726,7 +15726,7 @@
         <v>45374</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15799,7 +15799,7 @@
         <v>45999</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15872,7 +15872,7 @@
         <v>44928</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15945,7 +15945,7 @@
         <v>45994</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16018,7 +16018,7 @@
         <v>45456</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16091,7 +16091,7 @@
         <v>44813</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16164,7 +16164,7 @@
         <v>45021</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16237,7 +16237,7 @@
         <v>45495</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16310,7 +16310,7 @@
         <v>46007</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16383,7 +16383,7 @@
         <v>46174</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16456,7 +16456,7 @@
         <v>45239</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16529,7 +16529,7 @@
         <v>44551</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16602,7 +16602,7 @@
         <v>44924</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16675,7 +16675,7 @@
         <v>45915</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>46026</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16821,7 +16821,7 @@
         <v>46027</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16894,7 +16894,7 @@
         <v>45141</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16967,7 +16967,7 @@
         <v>46036</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17040,7 +17040,7 @@
         <v>46177</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17113,7 +17113,7 @@
         <v>46036</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17186,7 +17186,7 @@
         <v>46036</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17259,7 +17259,7 @@
         <v>46036</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17332,7 +17332,7 @@
         <v>46177</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17405,7 +17405,7 @@
         <v>46178</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17478,7 +17478,7 @@
         <v>46177</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17551,7 +17551,7 @@
         <v>46044</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17624,7 +17624,7 @@
         <v>45133</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17697,7 +17697,7 @@
         <v>45355</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17775,7 +17775,7 @@
         <v>46062</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17848,7 +17848,7 @@
         <v>46062</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17921,7 +17921,7 @@
         <v>44578</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17994,7 +17994,7 @@
         <v>44935</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18067,7 +18067,7 @@
         <v>46071</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18140,7 +18140,7 @@
         <v>45463</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18213,7 +18213,7 @@
         <v>46076</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>45063</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18359,7 +18359,7 @@
         <v>46083</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18437,7 +18437,7 @@
         <v>45953</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18515,7 +18515,7 @@
         <v>46090</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18588,7 +18588,7 @@
         <v>45097</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18661,7 +18661,7 @@
         <v>45971</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18739,7 +18739,7 @@
         <v>45992</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>45400</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18895,7 +18895,7 @@
         <v>45540</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18973,7 +18973,7 @@
         <v>45981</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19051,7 +19051,7 @@
         <v>46090</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19124,7 +19124,7 @@
         <v>45349</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19197,7 +19197,7 @@
         <v>45168</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19270,7 +19270,7 @@
         <v>45097</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19343,7 +19343,7 @@
         <v>46106</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19416,7 +19416,7 @@
         <v>44956</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19489,7 +19489,7 @@
         <v>46113</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19562,7 +19562,7 @@
         <v>46119</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19635,7 +19635,7 @@
         <v>46120</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19708,7 +19708,7 @@
         <v>45071</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19781,7 +19781,7 @@
         <v>46121</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19854,7 +19854,7 @@
         <v>46125</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19932,7 +19932,7 @@
         <v>45517</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20005,7 +20005,7 @@
         <v>44733</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20078,7 +20078,7 @@
         <v>46125</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20151,7 +20151,7 @@
         <v>46128</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20224,7 +20224,7 @@
         <v>46128</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20297,7 +20297,7 @@
         <v>45919</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20370,7 +20370,7 @@
         <v>45907</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>44509</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20516,7 +20516,7 @@
         <v>46206</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20589,7 +20589,7 @@
         <v>46210</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20667,7 +20667,7 @@
         <v>46210</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20745,7 +20745,7 @@
         <v>46212</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20823,7 +20823,7 @@
         <v>44602</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20896,7 +20896,7 @@
         <v>45035</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20969,7 +20969,7 @@
         <v>45035</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21042,7 +21042,7 @@
         <v>46222</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21120,7 +21120,7 @@
         <v>45365</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21193,7 +21193,7 @@
         <v>45251</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
         <v>45847</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21344,7 +21344,7 @@
         <v>45215</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21417,7 +21417,7 @@
         <v>45754</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21490,7 +21490,7 @@
         <v>45635</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21563,7 +21563,7 @@
         <v>45758</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21636,7 +21636,7 @@
         <v>44817</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21709,7 +21709,7 @@
         <v>45167</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21782,7 +21782,7 @@
         <v>45251</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21860,7 +21860,7 @@
         <v>44655</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21933,7 +21933,7 @@
         <v>45238</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22006,7 +22006,7 @@
         <v>45771</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22079,7 +22079,7 @@
         <v>45076</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22152,7 +22152,7 @@
         <v>44984</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22225,7 +22225,7 @@
         <v>45034</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22298,7 +22298,7 @@
         <v>45093</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22371,7 +22371,7 @@
         <v>45475</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22444,7 +22444,7 @@
         <v>46141</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22517,7 +22517,7 @@
         <v>44531</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22590,7 +22590,7 @@
         <v>45554</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22663,7 +22663,7 @@
         <v>45028</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22736,7 +22736,7 @@
         <v>45255</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22809,7 +22809,7 @@
         <v>45121</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
         <v>45366</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22955,7 +22955,7 @@
         <v>46036</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23028,7 +23028,7 @@
         <v>46288</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23101,7 +23101,7 @@
         <v>45205</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23174,7 +23174,7 @@
         <v>45426</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23247,7 +23247,7 @@
         <v>45484</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23320,7 +23320,7 @@
         <v>46251</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23393,7 +23393,7 @@
         <v>44973</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23466,7 +23466,7 @@
         <v>44967</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23539,7 +23539,7 @@
         <v>46293</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23612,7 +23612,7 @@
         <v>44794</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23685,7 +23685,7 @@
         <v>45188</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23758,7 +23758,7 @@
         <v>45197</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23831,7 +23831,7 @@
         <v>44582</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23909,7 +23909,7 @@
         <v>45484</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23982,7 +23982,7 @@
         <v>45387</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24055,7 +24055,7 @@
         <v>45453</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24128,7 +24128,7 @@
         <v>45771</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24201,7 +24201,7 @@
         <v>45553</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24274,7 +24274,7 @@
         <v>45127</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24347,7 +24347,7 @@
         <v>44959</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24420,7 +24420,7 @@
         <v>44823</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24493,7 +24493,7 @@
         <v>46258</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24566,7 +24566,7 @@
         <v>45644</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
         <v>45777</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24712,7 +24712,7 @@
         <v>45700</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24785,7 +24785,7 @@
         <v>46148</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24858,7 +24858,7 @@
         <v>46174</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24931,7 +24931,7 @@
         <v>46302</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25004,7 +25004,7 @@
         <v>45740</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25077,7 +25077,7 @@
         <v>45740</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25150,7 +25150,7 @@
         <v>46303</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25223,7 +25223,7 @@
         <v>45537</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25296,7 +25296,7 @@
         <v>46266</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25369,7 +25369,7 @@
         <v>44624</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25442,7 +25442,7 @@
         <v>45722</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25515,7 +25515,7 @@
         <v>45551</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25588,7 +25588,7 @@
         <v>45455</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25661,7 +25661,7 @@
         <v>46303</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25734,7 +25734,7 @@
         <v>45723</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25807,7 +25807,7 @@
         <v>46267</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25880,7 +25880,7 @@
         <v>46211</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
         <v>46311</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26026,7 +26026,7 @@
         <v>46267</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26104,7 +26104,7 @@
         <v>46267</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26182,7 +26182,7 @@
         <v>45826</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26255,7 +26255,7 @@
         <v>46267</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26333,7 +26333,7 @@
         <v>45826</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26406,7 +26406,7 @@
         <v>45826</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26479,7 +26479,7 @@
         <v>45826</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26552,7 +26552,7 @@
         <v>45843</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26625,7 +26625,7 @@
         <v>45588</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26698,7 +26698,7 @@
         <v>45455</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26771,7 +26771,7 @@
         <v>45882</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26844,7 +26844,7 @@
         <v>45672</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26917,7 +26917,7 @@
         <v>45771</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26990,7 +26990,7 @@
         <v>45328</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27063,7 +27063,7 @@
         <v>45526</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27136,7 +27136,7 @@
         <v>46129</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>

--- a/Översikt UDDEVALLA.xlsx
+++ b/Översikt UDDEVALLA.xlsx
@@ -601,7 +601,7 @@
         <v>46266</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45656</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>45432</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         <v>45677</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>45656</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>45107</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>45317</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>45728</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>45656</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>45751</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>46308</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>46253</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>45922</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>45656</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>45799</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>45990</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>46174</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>45317</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>45740</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2772,7 +2772,7 @@
         <v>45317</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>45288</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>45950</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         <v>45981</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         <v>45513</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>45754</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>44825</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>46124</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>46273</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>45513</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>46241</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>45352</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>46253</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>45653</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>44733</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>44930</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         <v>45071</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>44928</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>44627</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>45237</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>45600</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>45076</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
         <v>46036</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>45303</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         <v>45135</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>45107</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>45348</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>46071</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         <v>46292</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>46251</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6003,7 +6003,7 @@
         <v>46303</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6108,7 +6108,7 @@
         <v>46303</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         <v>45791</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         <v>45832</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6427,7 +6427,7 @@
         <v>45328</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6536,7 +6536,7 @@
         <v>44830</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6609,7 +6609,7 @@
         <v>44586</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>44536</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
         <v>44733</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>44574</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         <v>44523</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
         <v>44489</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
         <v>44585</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         <v>44733</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         <v>44599</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         <v>44529</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         <v>44572</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7417,7 +7417,7 @@
         <v>44614</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>44516</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>44502</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7636,7 +7636,7 @@
         <v>44494</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>45633</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>45602</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>45212</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         <v>45554</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8001,7 +8001,7 @@
         <v>44900</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8079,7 +8079,7 @@
         <v>45093</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8152,7 +8152,7 @@
         <v>45089</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8225,7 +8225,7 @@
         <v>45684</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>44536</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>45183</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8444,7 +8444,7 @@
         <v>45548</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
         <v>44960</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8590,7 +8590,7 @@
         <v>45365</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         <v>45162</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
         <v>45568</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8809,7 +8809,7 @@
         <v>44634</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
         <v>45551</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8955,7 +8955,7 @@
         <v>45596</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9028,7 +9028,7 @@
         <v>45754</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         <v>44817</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9174,7 +9174,7 @@
         <v>45226</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9247,7 +9247,7 @@
         <v>44572</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>45455</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9393,7 +9393,7 @@
         <v>44592</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>45748</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9539,7 +9539,7 @@
         <v>45426</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9612,7 +9612,7 @@
         <v>44981</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9690,7 +9690,7 @@
         <v>44820</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9763,7 +9763,7 @@
         <v>45631</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
         <v>45572</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9909,7 +9909,7 @@
         <v>44991</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9982,7 +9982,7 @@
         <v>45594</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10055,7 +10055,7 @@
         <v>44489</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10128,7 +10128,7 @@
         <v>45772</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10201,7 +10201,7 @@
         <v>44508</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10274,7 +10274,7 @@
         <v>45150</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10347,7 +10347,7 @@
         <v>45882</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10420,7 +10420,7 @@
         <v>45279</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10493,7 +10493,7 @@
         <v>46119</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10566,7 +10566,7 @@
         <v>45656</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10644,7 +10644,7 @@
         <v>45901</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10717,7 +10717,7 @@
         <v>44834</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10790,7 +10790,7 @@
         <v>44551</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10863,7 +10863,7 @@
         <v>45560</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10936,7 +10936,7 @@
         <v>45889</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11009,7 +11009,7 @@
         <v>45699</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>45840</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
         <v>45302</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
         <v>45895</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11301,7 +11301,7 @@
         <v>45583</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>45112</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
         <v>46139</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11520,7 +11520,7 @@
         <v>45226</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11593,7 +11593,7 @@
         <v>44715</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11666,7 +11666,7 @@
         <v>45901</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11739,7 +11739,7 @@
         <v>44550</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11812,7 +11812,7 @@
         <v>45911</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11885,7 +11885,7 @@
         <v>44998</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11958,7 +11958,7 @@
         <v>45914</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12031,7 +12031,7 @@
         <v>45914</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12104,7 +12104,7 @@
         <v>45580</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>45919</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>45922</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12323,7 +12323,7 @@
         <v>45638</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12396,7 +12396,7 @@
         <v>46147</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12474,7 +12474,7 @@
         <v>45771</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12547,7 +12547,7 @@
         <v>45925</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         <v>45929</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12693,7 +12693,7 @@
         <v>45929</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12766,7 +12766,7 @@
         <v>45931</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12839,7 +12839,7 @@
         <v>45656</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12917,7 +12917,7 @@
         <v>45656</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12995,7 +12995,7 @@
         <v>45440</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13068,7 +13068,7 @@
         <v>45656</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13146,7 +13146,7 @@
         <v>45656</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13224,7 +13224,7 @@
         <v>45656</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13302,7 +13302,7 @@
         <v>45646</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13375,7 +13375,7 @@
         <v>45642</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13448,7 +13448,7 @@
         <v>45470</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         <v>45656</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13604,7 +13604,7 @@
         <v>45575</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13677,7 +13677,7 @@
         <v>45553</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13750,7 +13750,7 @@
         <v>45257</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>45939</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13896,7 +13896,7 @@
         <v>45945</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13969,7 +13969,7 @@
         <v>45945</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14042,7 +14042,7 @@
         <v>45945</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14115,7 +14115,7 @@
         <v>45771</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14188,7 +14188,7 @@
         <v>45945</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14261,7 +14261,7 @@
         <v>45945</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>44683</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         <v>45237</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14480,7 +14480,7 @@
         <v>45940</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14553,7 +14553,7 @@
         <v>45667</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>45309</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14699,7 +14699,7 @@
         <v>45965</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14772,7 +14772,7 @@
         <v>45167</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14845,7 +14845,7 @@
         <v>45972</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14918,7 +14918,7 @@
         <v>46198</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14996,7 +14996,7 @@
         <v>45975</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15069,7 +15069,7 @@
         <v>45672</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>45664</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15215,7 +15215,7 @@
         <v>46164</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15288,7 +15288,7 @@
         <v>45985</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15361,7 +15361,7 @@
         <v>45986</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15434,7 +15434,7 @@
         <v>44973</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15507,7 +15507,7 @@
         <v>45764</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15580,7 +15580,7 @@
         <v>45992</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15653,7 +15653,7 @@
         <v>45314</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15726,7 +15726,7 @@
         <v>45374</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15799,7 +15799,7 @@
         <v>45999</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15872,7 +15872,7 @@
         <v>44928</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15945,7 +15945,7 @@
         <v>45994</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16018,7 +16018,7 @@
         <v>45456</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16091,7 +16091,7 @@
         <v>44813</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16164,7 +16164,7 @@
         <v>45021</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16237,7 +16237,7 @@
         <v>45495</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16310,7 +16310,7 @@
         <v>46007</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16383,7 +16383,7 @@
         <v>46174</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16456,7 +16456,7 @@
         <v>45239</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16529,7 +16529,7 @@
         <v>44551</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16602,7 +16602,7 @@
         <v>44924</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16675,7 +16675,7 @@
         <v>45915</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>46026</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16821,7 +16821,7 @@
         <v>46027</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16894,7 +16894,7 @@
         <v>45141</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16967,7 +16967,7 @@
         <v>46036</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17040,7 +17040,7 @@
         <v>46177</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17113,7 +17113,7 @@
         <v>46036</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17186,7 +17186,7 @@
         <v>46036</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17259,7 +17259,7 @@
         <v>46036</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17332,7 +17332,7 @@
         <v>46177</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17405,7 +17405,7 @@
         <v>46178</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17478,7 +17478,7 @@
         <v>46177</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17551,7 +17551,7 @@
         <v>46044</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17624,7 +17624,7 @@
         <v>45133</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17697,7 +17697,7 @@
         <v>45355</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17775,7 +17775,7 @@
         <v>46062</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17848,7 +17848,7 @@
         <v>46062</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17921,7 +17921,7 @@
         <v>44578</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17994,7 +17994,7 @@
         <v>44935</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18067,7 +18067,7 @@
         <v>46071</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18140,7 +18140,7 @@
         <v>45463</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18213,7 +18213,7 @@
         <v>46076</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>45063</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18359,7 +18359,7 @@
         <v>46083</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18437,7 +18437,7 @@
         <v>45953</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18515,7 +18515,7 @@
         <v>46090</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18588,7 +18588,7 @@
         <v>45097</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18661,7 +18661,7 @@
         <v>45971</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18739,7 +18739,7 @@
         <v>45992</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>45400</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18895,7 +18895,7 @@
         <v>45540</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18973,7 +18973,7 @@
         <v>45981</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19051,7 +19051,7 @@
         <v>46090</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19124,7 +19124,7 @@
         <v>45349</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19197,7 +19197,7 @@
         <v>45168</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19270,7 +19270,7 @@
         <v>45097</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19343,7 +19343,7 @@
         <v>46106</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19416,7 +19416,7 @@
         <v>44956</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19489,7 +19489,7 @@
         <v>46113</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19562,7 +19562,7 @@
         <v>46119</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19635,7 +19635,7 @@
         <v>46120</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19708,7 +19708,7 @@
         <v>45071</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19781,7 +19781,7 @@
         <v>46121</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19854,7 +19854,7 @@
         <v>46125</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19932,7 +19932,7 @@
         <v>45517</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20005,7 +20005,7 @@
         <v>44733</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20078,7 +20078,7 @@
         <v>46125</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20151,7 +20151,7 @@
         <v>46128</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20224,7 +20224,7 @@
         <v>46128</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20297,7 +20297,7 @@
         <v>45919</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20370,7 +20370,7 @@
         <v>45907</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>44509</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20516,7 +20516,7 @@
         <v>46206</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20589,7 +20589,7 @@
         <v>46210</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20667,7 +20667,7 @@
         <v>46210</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20745,7 +20745,7 @@
         <v>46212</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20823,7 +20823,7 @@
         <v>44602</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20896,7 +20896,7 @@
         <v>45035</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20969,7 +20969,7 @@
         <v>45035</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21042,7 +21042,7 @@
         <v>46222</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21120,7 +21120,7 @@
         <v>45365</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21193,7 +21193,7 @@
         <v>45251</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
         <v>45847</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21344,7 +21344,7 @@
         <v>45215</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21417,7 +21417,7 @@
         <v>45754</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21490,7 +21490,7 @@
         <v>45635</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21563,7 +21563,7 @@
         <v>45758</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21636,7 +21636,7 @@
         <v>44817</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21709,7 +21709,7 @@
         <v>45167</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21782,7 +21782,7 @@
         <v>45251</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21860,7 +21860,7 @@
         <v>44655</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21933,7 +21933,7 @@
         <v>45238</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22006,7 +22006,7 @@
         <v>45771</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22079,7 +22079,7 @@
         <v>45076</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22152,7 +22152,7 @@
         <v>44984</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22225,7 +22225,7 @@
         <v>45034</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22298,7 +22298,7 @@
         <v>45093</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22371,7 +22371,7 @@
         <v>45475</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22444,7 +22444,7 @@
         <v>46141</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22517,7 +22517,7 @@
         <v>44531</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22590,7 +22590,7 @@
         <v>45554</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22663,7 +22663,7 @@
         <v>45028</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22736,7 +22736,7 @@
         <v>45255</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22809,7 +22809,7 @@
         <v>45121</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
         <v>45366</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22955,7 +22955,7 @@
         <v>46036</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23028,7 +23028,7 @@
         <v>46288</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23101,7 +23101,7 @@
         <v>45205</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23174,7 +23174,7 @@
         <v>45426</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23247,7 +23247,7 @@
         <v>45484</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23320,7 +23320,7 @@
         <v>46251</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23393,7 +23393,7 @@
         <v>44973</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23466,7 +23466,7 @@
         <v>44967</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23539,7 +23539,7 @@
         <v>46293</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23612,7 +23612,7 @@
         <v>44794</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23685,7 +23685,7 @@
         <v>45188</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23758,7 +23758,7 @@
         <v>45197</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23831,7 +23831,7 @@
         <v>44582</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23909,7 +23909,7 @@
         <v>45484</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23982,7 +23982,7 @@
         <v>45387</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24055,7 +24055,7 @@
         <v>45453</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24128,7 +24128,7 @@
         <v>45771</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24201,7 +24201,7 @@
         <v>45553</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24274,7 +24274,7 @@
         <v>45127</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24347,7 +24347,7 @@
         <v>44959</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24420,7 +24420,7 @@
         <v>44823</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24493,7 +24493,7 @@
         <v>46258</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24566,7 +24566,7 @@
         <v>45644</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
         <v>45777</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24712,7 +24712,7 @@
         <v>45700</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24785,7 +24785,7 @@
         <v>46148</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24858,7 +24858,7 @@
         <v>46174</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24931,7 +24931,7 @@
         <v>46302</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25004,7 +25004,7 @@
         <v>45740</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25077,7 +25077,7 @@
         <v>45740</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25150,7 +25150,7 @@
         <v>46303</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25223,7 +25223,7 @@
         <v>45537</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25296,7 +25296,7 @@
         <v>46266</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25369,7 +25369,7 @@
         <v>44624</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25442,7 +25442,7 @@
         <v>45722</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25515,7 +25515,7 @@
         <v>45551</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25588,7 +25588,7 @@
         <v>45455</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25661,7 +25661,7 @@
         <v>46303</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25734,7 +25734,7 @@
         <v>45723</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25807,7 +25807,7 @@
         <v>46267</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25880,7 +25880,7 @@
         <v>46211</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
         <v>46311</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26026,7 +26026,7 @@
         <v>46267</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26104,7 +26104,7 @@
         <v>46267</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26182,7 +26182,7 @@
         <v>45826</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26255,7 +26255,7 @@
         <v>46267</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26333,7 +26333,7 @@
         <v>45826</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26406,7 +26406,7 @@
         <v>45826</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26479,7 +26479,7 @@
         <v>45826</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26552,7 +26552,7 @@
         <v>45843</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26625,7 +26625,7 @@
         <v>45588</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26698,7 +26698,7 @@
         <v>45455</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26771,7 +26771,7 @@
         <v>45882</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26844,7 +26844,7 @@
         <v>45672</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26917,7 +26917,7 @@
         <v>45771</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26990,7 +26990,7 @@
         <v>45328</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27063,7 +27063,7 @@
         <v>45526</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27136,7 +27136,7 @@
         <v>46129</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>

--- a/Översikt UDDEVALLA.xlsx
+++ b/Översikt UDDEVALLA.xlsx
@@ -601,7 +601,7 @@
         <v>46266</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45656</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>45432</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         <v>45677</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>45656</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>45107</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>45728</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>45317</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>45656</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>46308</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>45751</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>46253</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>45922</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>45799</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>45656</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>46174</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>45990</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>45740</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>45317</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>45513</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>45754</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>44825</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>45950</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>45981</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>45288</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>45352</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>46241</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>46253</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>46124</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>45653</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>45317</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>46273</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>45513</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>44733</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4397,7 +4397,7 @@
         <v>46036</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         <v>44928</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>45076</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         <v>46071</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>45791</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>45135</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
         <v>46292</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         <v>45832</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         <v>45348</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         <v>46251</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>46303</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
         <v>46303</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
         <v>44930</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5790,7 +5790,7 @@
         <v>45600</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5899,7 +5899,7 @@
         <v>46316</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6004,7 +6004,7 @@
         <v>44627</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6109,7 +6109,7 @@
         <v>45107</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6214,7 +6214,7 @@
         <v>45071</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
         <v>45303</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6428,7 +6428,7 @@
         <v>45237</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>45328</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
         <v>44586</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6715,7 +6715,7 @@
         <v>44830</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6788,7 +6788,7 @@
         <v>44536</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>44733</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6934,7 +6934,7 @@
         <v>44574</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>44523</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7080,7 +7080,7 @@
         <v>44585</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         <v>44733</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7226,7 +7226,7 @@
         <v>44599</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         <v>44529</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>44572</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>44614</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>44516</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7596,7 +7596,7 @@
         <v>44502</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7669,7 +7669,7 @@
         <v>44494</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7742,7 +7742,7 @@
         <v>45840</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         <v>45699</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7888,7 +7888,7 @@
         <v>45672</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         <v>44536</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8034,7 +8034,7 @@
         <v>45895</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>44551</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8180,7 +8180,7 @@
         <v>44834</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         <v>45141</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8326,7 +8326,7 @@
         <v>45771</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8399,7 +8399,7 @@
         <v>44794</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8472,7 +8472,7 @@
         <v>44813</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8545,7 +8545,7 @@
         <v>45901</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8618,7 +8618,7 @@
         <v>45365</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8691,7 +8691,7 @@
         <v>45309</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>45553</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>46198</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         <v>45911</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         <v>44959</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>45914</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         <v>45914</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>46164</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9280,7 +9280,7 @@
         <v>45028</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9353,7 +9353,7 @@
         <v>45919</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>45922</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>45925</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>45237</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>45929</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>45929</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>45915</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
         <v>45495</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>45931</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>45089</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>45646</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10156,7 +10156,7 @@
         <v>45642</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10229,7 +10229,7 @@
         <v>45656</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>45554</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>45470</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10458,7 +10458,7 @@
         <v>45656</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
         <v>45656</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>45440</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10687,7 +10687,7 @@
         <v>45656</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>45656</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10843,7 +10843,7 @@
         <v>45656</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>44928</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
         <v>45939</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11067,7 +11067,7 @@
         <v>46174</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>45093</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11213,7 +11213,7 @@
         <v>45374</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>46177</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11359,7 +11359,7 @@
         <v>46177</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11432,7 +11432,7 @@
         <v>45426</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11505,7 +11505,7 @@
         <v>45945</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         <v>46177</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11651,7 +11651,7 @@
         <v>45772</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11724,7 +11724,7 @@
         <v>45945</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11797,7 +11797,7 @@
         <v>45945</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11870,7 +11870,7 @@
         <v>45453</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11943,7 +11943,7 @@
         <v>45355</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12021,7 +12021,7 @@
         <v>45945</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12094,7 +12094,7 @@
         <v>45463</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12167,7 +12167,7 @@
         <v>45366</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12240,7 +12240,7 @@
         <v>45945</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12313,7 +12313,7 @@
         <v>46178</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>45940</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12459,7 +12459,7 @@
         <v>45554</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>45965</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>45167</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12678,7 +12678,7 @@
         <v>45667</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12751,7 +12751,7 @@
         <v>45251</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12829,7 +12829,7 @@
         <v>45972</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12902,7 +12902,7 @@
         <v>45205</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12975,7 +12975,7 @@
         <v>45580</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13048,7 +13048,7 @@
         <v>44960</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
         <v>45076</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13194,7 +13194,7 @@
         <v>45975</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13267,7 +13267,7 @@
         <v>45568</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>45635</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
         <v>44924</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13486,7 +13486,7 @@
         <v>45684</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13559,7 +13559,7 @@
         <v>45986</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13632,7 +13632,7 @@
         <v>45985</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13705,7 +13705,7 @@
         <v>46206</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13778,7 +13778,7 @@
         <v>45188</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13851,7 +13851,7 @@
         <v>45251</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13929,7 +13929,7 @@
         <v>45596</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>45426</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14075,7 +14075,7 @@
         <v>46210</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         <v>45992</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14226,7 +14226,7 @@
         <v>46210</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>46212</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14382,7 +14382,7 @@
         <v>45771</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>45215</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
         <v>45999</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14601,7 +14601,7 @@
         <v>45994</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14674,7 +14674,7 @@
         <v>46222</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14752,7 +14752,7 @@
         <v>45644</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14825,7 +14825,7 @@
         <v>45777</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14898,7 +14898,7 @@
         <v>45847</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>46007</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15044,7 +15044,7 @@
         <v>45700</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15117,7 +15117,7 @@
         <v>46026</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15190,7 +15190,7 @@
         <v>46027</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15263,7 +15263,7 @@
         <v>44817</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15336,7 +15336,7 @@
         <v>45740</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15409,7 +15409,7 @@
         <v>45740</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15482,7 +15482,7 @@
         <v>46036</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15555,7 +15555,7 @@
         <v>46036</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15628,7 +15628,7 @@
         <v>45537</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15701,7 +15701,7 @@
         <v>46036</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>46036</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15847,7 +15847,7 @@
         <v>46044</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15920,7 +15920,7 @@
         <v>46288</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15993,7 +15993,7 @@
         <v>46141</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16066,7 +16066,7 @@
         <v>46036</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16139,7 +16139,7 @@
         <v>45551</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16212,7 +16212,7 @@
         <v>44624</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16285,7 +16285,7 @@
         <v>45722</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16358,7 +16358,7 @@
         <v>45455</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16431,7 +16431,7 @@
         <v>46062</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16504,7 +16504,7 @@
         <v>46062</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16577,7 +16577,7 @@
         <v>45723</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16650,7 +16650,7 @@
         <v>46293</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16723,7 +16723,7 @@
         <v>46251</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16796,7 +16796,7 @@
         <v>46071</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16869,7 +16869,7 @@
         <v>44935</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16942,7 +16942,7 @@
         <v>46076</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17015,7 +17015,7 @@
         <v>45826</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17088,7 +17088,7 @@
         <v>45826</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17161,7 +17161,7 @@
         <v>45826</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17234,7 +17234,7 @@
         <v>45826</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17307,7 +17307,7 @@
         <v>46083</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17385,7 +17385,7 @@
         <v>46174</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17458,7 +17458,7 @@
         <v>45953</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
         <v>45992</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17614,7 +17614,7 @@
         <v>45971</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17692,7 +17692,7 @@
         <v>45981</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17770,7 +17770,7 @@
         <v>45400</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17848,7 +17848,7 @@
         <v>45540</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17926,7 +17926,7 @@
         <v>46090</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17999,7 +17999,7 @@
         <v>46090</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18072,7 +18072,7 @@
         <v>45484</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18145,7 +18145,7 @@
         <v>45843</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18218,7 +18218,7 @@
         <v>45127</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18291,7 +18291,7 @@
         <v>46148</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18364,7 +18364,7 @@
         <v>46302</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18437,7 +18437,7 @@
         <v>46106</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18510,7 +18510,7 @@
         <v>46113</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18583,7 +18583,7 @@
         <v>46258</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18656,7 +18656,7 @@
         <v>45588</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18729,7 +18729,7 @@
         <v>45455</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18802,7 +18802,7 @@
         <v>46119</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18875,7 +18875,7 @@
         <v>45034</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18948,7 +18948,7 @@
         <v>45035</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19021,7 +19021,7 @@
         <v>45035</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19094,7 +19094,7 @@
         <v>46120</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19167,7 +19167,7 @@
         <v>46121</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19240,7 +19240,7 @@
         <v>46303</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19313,7 +19313,7 @@
         <v>46125</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19391,7 +19391,7 @@
         <v>46125</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19464,7 +19464,7 @@
         <v>46128</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19537,7 +19537,7 @@
         <v>46128</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19610,7 +19610,7 @@
         <v>45882</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19683,7 +19683,7 @@
         <v>45882</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19756,7 +19756,7 @@
         <v>45638</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19829,7 +19829,7 @@
         <v>45594</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19902,7 +19902,7 @@
         <v>45517</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19975,7 +19975,7 @@
         <v>45302</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20048,7 +20048,7 @@
         <v>45097</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>46267</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20199,7 +20199,7 @@
         <v>46267</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20277,7 +20277,7 @@
         <v>46267</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20355,7 +20355,7 @@
         <v>46267</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         <v>46211</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20501,7 +20501,7 @@
         <v>45602</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20574,7 +20574,7 @@
         <v>45889</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20647,7 +20647,7 @@
         <v>45656</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20725,7 +20725,7 @@
         <v>45907</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20798,7 +20798,7 @@
         <v>46311</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20871,7 +20871,7 @@
         <v>45901</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20944,7 +20944,7 @@
         <v>45919</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21017,7 +21017,7 @@
         <v>46119</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21090,7 +21090,7 @@
         <v>46266</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21163,7 +21163,7 @@
         <v>45548</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21236,7 +21236,7 @@
         <v>46139</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21309,7 +21309,7 @@
         <v>45279</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21382,7 +21382,7 @@
         <v>45583</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21455,7 +21455,7 @@
         <v>45560</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21528,7 +21528,7 @@
         <v>45197</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21601,7 +21601,7 @@
         <v>44592</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21674,7 +21674,7 @@
         <v>46303</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21747,7 +21747,7 @@
         <v>46316</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21820,7 +21820,7 @@
         <v>45226</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21893,7 +21893,7 @@
         <v>45633</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21966,7 +21966,7 @@
         <v>44550</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22039,7 +22039,7 @@
         <v>46147</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22117,7 +22117,7 @@
         <v>45226</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22190,7 +22190,7 @@
         <v>45748</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22263,7 +22263,7 @@
         <v>44634</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22336,7 +22336,7 @@
         <v>45255</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22409,7 +22409,7 @@
         <v>44956</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22482,7 +22482,7 @@
         <v>44991</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22555,7 +22555,7 @@
         <v>45162</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22628,7 +22628,7 @@
         <v>44998</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22701,7 +22701,7 @@
         <v>45121</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22774,7 +22774,7 @@
         <v>45484</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22847,7 +22847,7 @@
         <v>44823</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22920,7 +22920,7 @@
         <v>45771</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22993,7 +22993,7 @@
         <v>44509</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23066,7 +23066,7 @@
         <v>45168</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23139,7 +23139,7 @@
         <v>45212</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23212,7 +23212,7 @@
         <v>45764</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23285,7 +23285,7 @@
         <v>45071</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23358,7 +23358,7 @@
         <v>45672</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23431,7 +23431,7 @@
         <v>45238</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23504,7 +23504,7 @@
         <v>45754</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23577,7 +23577,7 @@
         <v>45754</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23650,7 +23650,7 @@
         <v>45551</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23723,7 +23723,7 @@
         <v>44551</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23796,7 +23796,7 @@
         <v>45455</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23869,7 +23869,7 @@
         <v>45063</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23942,7 +23942,7 @@
         <v>45021</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24015,7 +24015,7 @@
         <v>44900</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24093,7 +24093,7 @@
         <v>44508</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24166,7 +24166,7 @@
         <v>44973</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24239,7 +24239,7 @@
         <v>44531</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24312,7 +24312,7 @@
         <v>44967</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24385,7 +24385,7 @@
         <v>45150</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24458,7 +24458,7 @@
         <v>45133</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24531,7 +24531,7 @@
         <v>45097</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24604,7 +24604,7 @@
         <v>45475</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24677,7 +24677,7 @@
         <v>45387</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24750,7 +24750,7 @@
         <v>44572</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24823,7 +24823,7 @@
         <v>45112</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24896,7 +24896,7 @@
         <v>45167</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24969,7 +24969,7 @@
         <v>45771</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25042,7 +25042,7 @@
         <v>44981</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25120,7 +25120,7 @@
         <v>45771</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25193,7 +25193,7 @@
         <v>45349</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25266,7 +25266,7 @@
         <v>44582</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25344,7 +25344,7 @@
         <v>45575</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25417,7 +25417,7 @@
         <v>44578</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25490,7 +25490,7 @@
         <v>45553</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25563,7 +25563,7 @@
         <v>44602</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25636,7 +25636,7 @@
         <v>44655</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25709,7 +25709,7 @@
         <v>45456</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25782,7 +25782,7 @@
         <v>45664</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25855,7 +25855,7 @@
         <v>45183</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25928,7 +25928,7 @@
         <v>45572</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26001,7 +26001,7 @@
         <v>45758</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26074,7 +26074,7 @@
         <v>45631</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26147,7 +26147,7 @@
         <v>44733</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26220,7 +26220,7 @@
         <v>44715</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26293,7 +26293,7 @@
         <v>45239</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26366,7 +26366,7 @@
         <v>44820</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26439,7 +26439,7 @@
         <v>44817</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26512,7 +26512,7 @@
         <v>45314</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26585,7 +26585,7 @@
         <v>44973</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26658,7 +26658,7 @@
         <v>45257</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26731,7 +26731,7 @@
         <v>45365</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26804,7 +26804,7 @@
         <v>44984</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26877,7 +26877,7 @@
         <v>44683</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26950,7 +26950,7 @@
         <v>45093</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27023,7 +27023,7 @@
         <v>45328</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27096,7 +27096,7 @@
         <v>45526</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27169,7 +27169,7 @@
         <v>46129</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>

--- a/Översikt UDDEVALLA.xlsx
+++ b/Översikt UDDEVALLA.xlsx
@@ -601,7 +601,7 @@
         <v>46266</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45656</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>45432</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         <v>45677</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>45656</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>45107</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>45728</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>45317</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>45656</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>46308</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>45751</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>46253</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>45922</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>45799</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>45656</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>46174</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>45990</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>45740</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>45317</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>45513</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>45754</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>44825</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>45950</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>45981</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>45288</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>45352</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>46241</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>46253</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>46124</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>45653</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>45317</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>46273</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>45513</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>44733</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4397,7 +4397,7 @@
         <v>46036</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         <v>44928</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>45076</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         <v>46071</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>45791</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>45135</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
         <v>46292</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         <v>45832</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         <v>45348</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         <v>46251</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>46303</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
         <v>46303</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
         <v>44930</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5790,7 +5790,7 @@
         <v>45600</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5899,7 +5899,7 @@
         <v>46316</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6004,7 +6004,7 @@
         <v>44627</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6109,7 +6109,7 @@
         <v>45107</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6214,7 +6214,7 @@
         <v>45071</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
         <v>45303</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6428,7 +6428,7 @@
         <v>45237</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>45328</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
         <v>44586</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6715,7 +6715,7 @@
         <v>44830</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6788,7 +6788,7 @@
         <v>44536</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>44733</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6934,7 +6934,7 @@
         <v>44574</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>44523</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7080,7 +7080,7 @@
         <v>44585</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         <v>44733</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7226,7 +7226,7 @@
         <v>44599</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         <v>44529</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>44572</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>44614</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>44516</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7596,7 +7596,7 @@
         <v>44502</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7669,7 +7669,7 @@
         <v>44494</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7742,7 +7742,7 @@
         <v>45840</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         <v>45699</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7888,7 +7888,7 @@
         <v>45672</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         <v>44536</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8034,7 +8034,7 @@
         <v>45895</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>44551</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8180,7 +8180,7 @@
         <v>44834</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         <v>45141</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8326,7 +8326,7 @@
         <v>45771</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8399,7 +8399,7 @@
         <v>44794</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8472,7 +8472,7 @@
         <v>44813</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8545,7 +8545,7 @@
         <v>45901</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8618,7 +8618,7 @@
         <v>45365</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8691,7 +8691,7 @@
         <v>45309</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>45553</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>46198</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         <v>45911</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         <v>44959</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>45914</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         <v>45914</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>46164</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9280,7 +9280,7 @@
         <v>45028</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9353,7 +9353,7 @@
         <v>45919</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>45922</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>45925</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>45237</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>45929</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>45929</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>45915</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
         <v>45495</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>45931</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>45089</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>45646</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10156,7 +10156,7 @@
         <v>45642</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10229,7 +10229,7 @@
         <v>45656</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>45554</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>45470</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10458,7 +10458,7 @@
         <v>45656</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
         <v>45656</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>45440</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10687,7 +10687,7 @@
         <v>45656</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>45656</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10843,7 +10843,7 @@
         <v>45656</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>44928</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
         <v>45939</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11067,7 +11067,7 @@
         <v>46174</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>45093</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11213,7 +11213,7 @@
         <v>45374</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>46177</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11359,7 +11359,7 @@
         <v>46177</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11432,7 +11432,7 @@
         <v>45426</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11505,7 +11505,7 @@
         <v>45945</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         <v>46177</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11651,7 +11651,7 @@
         <v>45772</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11724,7 +11724,7 @@
         <v>45945</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11797,7 +11797,7 @@
         <v>45945</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11870,7 +11870,7 @@
         <v>45453</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11943,7 +11943,7 @@
         <v>45355</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12021,7 +12021,7 @@
         <v>45945</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12094,7 +12094,7 @@
         <v>45463</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12167,7 +12167,7 @@
         <v>45366</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12240,7 +12240,7 @@
         <v>45945</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12313,7 +12313,7 @@
         <v>46178</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>45940</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12459,7 +12459,7 @@
         <v>45554</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>45965</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>45167</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12678,7 +12678,7 @@
         <v>45667</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12751,7 +12751,7 @@
         <v>45251</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12829,7 +12829,7 @@
         <v>45972</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12902,7 +12902,7 @@
         <v>45205</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12975,7 +12975,7 @@
         <v>45580</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13048,7 +13048,7 @@
         <v>44960</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
         <v>45076</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13194,7 +13194,7 @@
         <v>45975</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13267,7 +13267,7 @@
         <v>45568</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>45635</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
         <v>44924</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13486,7 +13486,7 @@
         <v>45684</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13559,7 +13559,7 @@
         <v>45986</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13632,7 +13632,7 @@
         <v>45985</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13705,7 +13705,7 @@
         <v>46206</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13778,7 +13778,7 @@
         <v>45188</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13851,7 +13851,7 @@
         <v>45251</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13929,7 +13929,7 @@
         <v>45596</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>45426</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14075,7 +14075,7 @@
         <v>46210</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         <v>45992</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14226,7 +14226,7 @@
         <v>46210</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>46212</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14382,7 +14382,7 @@
         <v>45771</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>45215</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
         <v>45999</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14601,7 +14601,7 @@
         <v>45994</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14674,7 +14674,7 @@
         <v>46222</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14752,7 +14752,7 @@
         <v>45644</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14825,7 +14825,7 @@
         <v>45777</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14898,7 +14898,7 @@
         <v>45847</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>46007</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15044,7 +15044,7 @@
         <v>45700</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15117,7 +15117,7 @@
         <v>46026</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15190,7 +15190,7 @@
         <v>46027</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15263,7 +15263,7 @@
         <v>44817</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15336,7 +15336,7 @@
         <v>45740</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15409,7 +15409,7 @@
         <v>45740</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15482,7 +15482,7 @@
         <v>46036</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15555,7 +15555,7 @@
         <v>46036</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15628,7 +15628,7 @@
         <v>45537</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15701,7 +15701,7 @@
         <v>46036</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>46036</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15847,7 +15847,7 @@
         <v>46044</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15920,7 +15920,7 @@
         <v>46288</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15993,7 +15993,7 @@
         <v>46141</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16066,7 +16066,7 @@
         <v>46036</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16139,7 +16139,7 @@
         <v>45551</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16212,7 +16212,7 @@
         <v>44624</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16285,7 +16285,7 @@
         <v>45722</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16358,7 +16358,7 @@
         <v>45455</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16431,7 +16431,7 @@
         <v>46062</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16504,7 +16504,7 @@
         <v>46062</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16577,7 +16577,7 @@
         <v>45723</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16650,7 +16650,7 @@
         <v>46293</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16723,7 +16723,7 @@
         <v>46251</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16796,7 +16796,7 @@
         <v>46071</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16869,7 +16869,7 @@
         <v>44935</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16942,7 +16942,7 @@
         <v>46076</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17015,7 +17015,7 @@
         <v>45826</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17088,7 +17088,7 @@
         <v>45826</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17161,7 +17161,7 @@
         <v>45826</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17234,7 +17234,7 @@
         <v>45826</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17307,7 +17307,7 @@
         <v>46083</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17385,7 +17385,7 @@
         <v>46174</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17458,7 +17458,7 @@
         <v>45953</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
         <v>45992</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17614,7 +17614,7 @@
         <v>45971</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17692,7 +17692,7 @@
         <v>45981</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17770,7 +17770,7 @@
         <v>45400</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17848,7 +17848,7 @@
         <v>45540</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17926,7 +17926,7 @@
         <v>46090</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17999,7 +17999,7 @@
         <v>46090</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18072,7 +18072,7 @@
         <v>45484</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18145,7 +18145,7 @@
         <v>45843</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18218,7 +18218,7 @@
         <v>45127</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18291,7 +18291,7 @@
         <v>46148</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18364,7 +18364,7 @@
         <v>46302</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18437,7 +18437,7 @@
         <v>46106</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18510,7 +18510,7 @@
         <v>46113</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18583,7 +18583,7 @@
         <v>46258</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18656,7 +18656,7 @@
         <v>45588</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18729,7 +18729,7 @@
         <v>45455</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18802,7 +18802,7 @@
         <v>46119</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18875,7 +18875,7 @@
         <v>45034</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18948,7 +18948,7 @@
         <v>45035</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19021,7 +19021,7 @@
         <v>45035</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19094,7 +19094,7 @@
         <v>46120</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19167,7 +19167,7 @@
         <v>46121</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19240,7 +19240,7 @@
         <v>46303</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19313,7 +19313,7 @@
         <v>46125</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19391,7 +19391,7 @@
         <v>46125</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19464,7 +19464,7 @@
         <v>46128</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19537,7 +19537,7 @@
         <v>46128</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19610,7 +19610,7 @@
         <v>45882</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19683,7 +19683,7 @@
         <v>45882</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19756,7 +19756,7 @@
         <v>45638</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19829,7 +19829,7 @@
         <v>45594</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19902,7 +19902,7 @@
         <v>45517</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19975,7 +19975,7 @@
         <v>45302</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20048,7 +20048,7 @@
         <v>45097</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>46267</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20199,7 +20199,7 @@
         <v>46267</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20277,7 +20277,7 @@
         <v>46267</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20355,7 +20355,7 @@
         <v>46267</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         <v>46211</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20501,7 +20501,7 @@
         <v>45602</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20574,7 +20574,7 @@
         <v>45889</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20647,7 +20647,7 @@
         <v>45656</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20725,7 +20725,7 @@
         <v>45907</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20798,7 +20798,7 @@
         <v>46311</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20871,7 +20871,7 @@
         <v>45901</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20944,7 +20944,7 @@
         <v>45919</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21017,7 +21017,7 @@
         <v>46119</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21090,7 +21090,7 @@
         <v>46266</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21163,7 +21163,7 @@
         <v>45548</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21236,7 +21236,7 @@
         <v>46139</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21309,7 +21309,7 @@
         <v>45279</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21382,7 +21382,7 @@
         <v>45583</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21455,7 +21455,7 @@
         <v>45560</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21528,7 +21528,7 @@
         <v>45197</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21601,7 +21601,7 @@
         <v>44592</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21674,7 +21674,7 @@
         <v>46303</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21747,7 +21747,7 @@
         <v>46316</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21820,7 +21820,7 @@
         <v>45226</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21893,7 +21893,7 @@
         <v>45633</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21966,7 +21966,7 @@
         <v>44550</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22039,7 +22039,7 @@
         <v>46147</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22117,7 +22117,7 @@
         <v>45226</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22190,7 +22190,7 @@
         <v>45748</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22263,7 +22263,7 @@
         <v>44634</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22336,7 +22336,7 @@
         <v>45255</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22409,7 +22409,7 @@
         <v>44956</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22482,7 +22482,7 @@
         <v>44991</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22555,7 +22555,7 @@
         <v>45162</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22628,7 +22628,7 @@
         <v>44998</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22701,7 +22701,7 @@
         <v>45121</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22774,7 +22774,7 @@
         <v>45484</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22847,7 +22847,7 @@
         <v>44823</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22920,7 +22920,7 @@
         <v>45771</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22993,7 +22993,7 @@
         <v>44509</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23066,7 +23066,7 @@
         <v>45168</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23139,7 +23139,7 @@
         <v>45212</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23212,7 +23212,7 @@
         <v>45764</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23285,7 +23285,7 @@
         <v>45071</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23358,7 +23358,7 @@
         <v>45672</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23431,7 +23431,7 @@
         <v>45238</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23504,7 +23504,7 @@
         <v>45754</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23577,7 +23577,7 @@
         <v>45754</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23650,7 +23650,7 @@
         <v>45551</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23723,7 +23723,7 @@
         <v>44551</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23796,7 +23796,7 @@
         <v>45455</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23869,7 +23869,7 @@
         <v>45063</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23942,7 +23942,7 @@
         <v>45021</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24015,7 +24015,7 @@
         <v>44900</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24093,7 +24093,7 @@
         <v>44508</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24166,7 +24166,7 @@
         <v>44973</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24239,7 +24239,7 @@
         <v>44531</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24312,7 +24312,7 @@
         <v>44967</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24385,7 +24385,7 @@
         <v>45150</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24458,7 +24458,7 @@
         <v>45133</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24531,7 +24531,7 @@
         <v>45097</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24604,7 +24604,7 @@
         <v>45475</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24677,7 +24677,7 @@
         <v>45387</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24750,7 +24750,7 @@
         <v>44572</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24823,7 +24823,7 @@
         <v>45112</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24896,7 +24896,7 @@
         <v>45167</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24969,7 +24969,7 @@
         <v>45771</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25042,7 +25042,7 @@
         <v>44981</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25120,7 +25120,7 @@
         <v>45771</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25193,7 +25193,7 @@
         <v>45349</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25266,7 +25266,7 @@
         <v>44582</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25344,7 +25344,7 @@
         <v>45575</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25417,7 +25417,7 @@
         <v>44578</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25490,7 +25490,7 @@
         <v>45553</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25563,7 +25563,7 @@
         <v>44602</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25636,7 +25636,7 @@
         <v>44655</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25709,7 +25709,7 @@
         <v>45456</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25782,7 +25782,7 @@
         <v>45664</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25855,7 +25855,7 @@
         <v>45183</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25928,7 +25928,7 @@
         <v>45572</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26001,7 +26001,7 @@
         <v>45758</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26074,7 +26074,7 @@
         <v>45631</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26147,7 +26147,7 @@
         <v>44733</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26220,7 +26220,7 @@
         <v>44715</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26293,7 +26293,7 @@
         <v>45239</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26366,7 +26366,7 @@
         <v>44820</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26439,7 +26439,7 @@
         <v>44817</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26512,7 +26512,7 @@
         <v>45314</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26585,7 +26585,7 @@
         <v>44973</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26658,7 +26658,7 @@
         <v>45257</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26731,7 +26731,7 @@
         <v>45365</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26804,7 +26804,7 @@
         <v>44984</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26877,7 +26877,7 @@
         <v>44683</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26950,7 +26950,7 @@
         <v>45093</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27023,7 +27023,7 @@
         <v>45328</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27096,7 +27096,7 @@
         <v>45526</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27169,7 +27169,7 @@
         <v>46129</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
